--- a/Data/FlightPlan/FPL_26AUG26.xlsx
+++ b/Data/FlightPlan/FPL_26AUG26.xlsx
@@ -467,6 +467,36 @@
     <t>01:35</t>
   </si>
   <si>
+    <t>VN-A535</t>
+  </si>
+  <si>
+    <t>11:40</t>
+  </si>
+  <si>
+    <t>13:25</t>
+  </si>
+  <si>
+    <t>16:05</t>
+  </si>
+  <si>
+    <t>17:35</t>
+  </si>
+  <si>
+    <t>19:45</t>
+  </si>
+  <si>
+    <t>20:20</t>
+  </si>
+  <si>
+    <t>22:30</t>
+  </si>
+  <si>
+    <t>01:40</t>
+  </si>
+  <si>
+    <t>07:55</t>
+  </si>
+  <si>
     <t>VN-A536</t>
   </si>
   <si>
@@ -515,36 +545,6 @@
     <t>18:45</t>
   </si>
   <si>
-    <t>VN-A542</t>
-  </si>
-  <si>
-    <t>11:40</t>
-  </si>
-  <si>
-    <t>13:25</t>
-  </si>
-  <si>
-    <t>16:05</t>
-  </si>
-  <si>
-    <t>17:35</t>
-  </si>
-  <si>
-    <t>19:45</t>
-  </si>
-  <si>
-    <t>20:20</t>
-  </si>
-  <si>
-    <t>22:30</t>
-  </si>
-  <si>
-    <t>01:40</t>
-  </si>
-  <si>
-    <t>07:55</t>
-  </si>
-  <si>
     <t>VN-A543</t>
   </si>
   <si>
@@ -1220,7 +1220,7 @@
     <t>Total Record(s): 390</t>
   </si>
   <si>
-    <t xml:space="preserve">Generated on  Aug 26, 2026 03:17</t>
+    <t xml:space="preserve">Generated on  Aug 26, 2026 03:35</t>
   </si>
   <si>
     <t>Page 1 of 1</t>
@@ -3988,7 +3988,7 @@
         <v>13</v>
       </c>
       <c r="B81" s="7">
-        <v>1242</v>
+        <v>339</v>
       </c>
       <c t="s" r="C81" s="7">
         <v>14</v>
@@ -4004,10 +4004,10 @@
         <v>21</v>
       </c>
       <c t="s" r="H81" s="8">
-        <v>153</v>
+        <v>17</v>
       </c>
       <c t="s" r="I81" s="7">
-        <v>154</v>
+        <v>62</v>
       </c>
       <c t="s" r="J81" s="7">
         <v>143</v>
@@ -4021,7 +4021,7 @@
         <v>13</v>
       </c>
       <c r="B82" s="7">
-        <v>1241</v>
+        <v>718</v>
       </c>
       <c t="s" r="C82" s="7">
         <v>14</v>
@@ -4034,16 +4034,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G82" s="8">
-        <v>153</v>
+        <v>17</v>
       </c>
       <c t="s" r="H82" s="8">
-        <v>21</v>
+        <v>94</v>
       </c>
       <c t="s" r="I82" s="7">
-        <v>155</v>
+        <v>53</v>
       </c>
       <c t="s" r="J82" s="7">
-        <v>156</v>
+        <v>146</v>
       </c>
       <c r="K82" s="7"/>
       <c r="L82" s="7"/>
@@ -4054,7 +4054,7 @@
         <v>13</v>
       </c>
       <c r="B83" s="7">
-        <v>325</v>
+        <v>719</v>
       </c>
       <c t="s" r="C83" s="7">
         <v>14</v>
@@ -4067,16 +4067,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G83" s="8">
-        <v>21</v>
+        <v>94</v>
       </c>
       <c t="s" r="H83" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I83" s="7">
-        <v>68</v>
+        <v>153</v>
       </c>
       <c t="s" r="J83" s="7">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="K83" s="7"/>
       <c r="L83" s="7"/>
@@ -4087,7 +4087,7 @@
         <v>13</v>
       </c>
       <c r="B84" s="7">
-        <v>978</v>
+        <v>452</v>
       </c>
       <c t="s" r="C84" s="7">
         <v>14</v>
@@ -4103,29 +4103,47 @@
         <v>17</v>
       </c>
       <c t="s" r="H84" s="8">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c t="s" r="I84" s="7">
-        <v>158</v>
+        <v>98</v>
       </c>
       <c t="s" r="J84" s="7">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="K84" s="7"/>
       <c r="L84" s="7"/>
       <c r="M84" s="7"/>
     </row>
     <row r="85" ht="15" customHeight="1">
-      <c r="A85" s="6"/>
-      <c r="B85" s="7"/>
-      <c r="C85" s="7"/>
+      <c t="s" r="A85" s="6">
+        <v>13</v>
+      </c>
+      <c r="B85" s="7">
+        <v>141</v>
+      </c>
+      <c t="s" r="C85" s="7">
+        <v>14</v>
+      </c>
       <c r="D85" s="7"/>
-      <c r="E85" s="7"/>
-      <c r="F85" s="7"/>
-      <c r="G85" s="8"/>
-      <c r="H85" s="8"/>
-      <c r="I85" s="7"/>
-      <c r="J85" s="7"/>
+      <c t="s" r="E85" s="7">
+        <v>152</v>
+      </c>
+      <c r="F85" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G85" s="8">
+        <v>24</v>
+      </c>
+      <c t="s" r="H85" s="8">
+        <v>21</v>
+      </c>
+      <c t="s" r="I85" s="7">
+        <v>156</v>
+      </c>
+      <c t="s" r="J85" s="7">
+        <v>157</v>
+      </c>
       <c r="K85" s="7"/>
       <c r="L85" s="7"/>
       <c r="M85" s="7"/>
@@ -4135,29 +4153,29 @@
         <v>13</v>
       </c>
       <c r="B86" s="7">
-        <v>501</v>
+        <v>150</v>
       </c>
       <c t="s" r="C86" s="7">
         <v>14</v>
       </c>
       <c r="D86" s="7"/>
       <c t="s" r="E86" s="7">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="F86" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G86" s="8">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c t="s" r="H86" s="8">
-        <v>94</v>
+        <v>24</v>
       </c>
       <c t="s" r="I86" s="7">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c t="s" r="J86" s="7">
-        <v>141</v>
+        <v>159</v>
       </c>
       <c r="K86" s="7"/>
       <c r="L86" s="7"/>
@@ -4165,66 +4183,48 @@
     </row>
     <row r="87" ht="14.25" customHeight="1">
       <c t="s" r="A87" s="6">
-        <v>13</v>
+        <v>48</v>
       </c>
       <c r="B87" s="7">
-        <v>514</v>
+        <v>960</v>
       </c>
       <c t="s" r="C87" s="7">
         <v>14</v>
       </c>
       <c r="D87" s="7"/>
       <c t="s" r="E87" s="7">
+        <v>152</v>
+      </c>
+      <c r="F87" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G87" s="8">
+        <v>24</v>
+      </c>
+      <c t="s" r="H87" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="I87" s="7">
         <v>160</v>
       </c>
-      <c r="F87" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G87" s="8">
-        <v>94</v>
-      </c>
-      <c t="s" r="H87" s="8">
-        <v>24</v>
-      </c>
-      <c t="s" r="I87" s="7">
-        <v>142</v>
-      </c>
       <c t="s" r="J87" s="7">
-        <v>143</v>
+        <v>161</v>
       </c>
       <c r="K87" s="7"/>
       <c r="L87" s="7"/>
       <c r="M87" s="7"/>
     </row>
     <row r="88" ht="14.25" customHeight="1">
-      <c t="s" r="A88" s="6">
-        <v>13</v>
-      </c>
-      <c r="B88" s="7">
-        <v>563</v>
-      </c>
-      <c t="s" r="C88" s="7">
-        <v>14</v>
-      </c>
+      <c r="A88" s="6"/>
+      <c r="B88" s="7"/>
+      <c r="C88" s="7"/>
       <c r="D88" s="7"/>
-      <c t="s" r="E88" s="7">
-        <v>160</v>
-      </c>
-      <c r="F88" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G88" s="8">
-        <v>24</v>
-      </c>
-      <c t="s" r="H88" s="8">
-        <v>162</v>
-      </c>
-      <c t="s" r="I88" s="7">
-        <v>155</v>
-      </c>
-      <c t="s" r="J88" s="7">
-        <v>130</v>
-      </c>
+      <c r="E88" s="7"/>
+      <c r="F88" s="7"/>
+      <c r="G88" s="8"/>
+      <c r="H88" s="8"/>
+      <c r="I88" s="7"/>
+      <c r="J88" s="7"/>
       <c r="K88" s="7"/>
       <c r="L88" s="7"/>
       <c r="M88" s="7"/>
@@ -4234,29 +4234,29 @@
         <v>13</v>
       </c>
       <c r="B89" s="7">
-        <v>564</v>
+        <v>1242</v>
       </c>
       <c t="s" r="C89" s="7">
         <v>14</v>
       </c>
       <c r="D89" s="7"/>
       <c t="s" r="E89" s="7">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="F89" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G89" s="8">
-        <v>162</v>
+        <v>21</v>
       </c>
       <c t="s" r="H89" s="8">
-        <v>24</v>
+        <v>163</v>
       </c>
       <c t="s" r="I89" s="7">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c t="s" r="J89" s="7">
-        <v>164</v>
+        <v>143</v>
       </c>
       <c r="K89" s="7"/>
       <c r="L89" s="7"/>
@@ -4267,29 +4267,29 @@
         <v>13</v>
       </c>
       <c r="B90" s="7">
-        <v>401</v>
+        <v>1241</v>
       </c>
       <c t="s" r="C90" s="7">
         <v>14</v>
       </c>
       <c r="D90" s="7"/>
       <c t="s" r="E90" s="7">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="F90" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G90" s="8">
-        <v>24</v>
+        <v>163</v>
       </c>
       <c t="s" r="H90" s="8">
+        <v>21</v>
+      </c>
+      <c t="s" r="I90" s="7">
         <v>165</v>
       </c>
-      <c t="s" r="I90" s="7">
-        <v>148</v>
-      </c>
       <c t="s" r="J90" s="7">
-        <v>79</v>
+        <v>166</v>
       </c>
       <c r="K90" s="7"/>
       <c r="L90" s="7"/>
@@ -4300,29 +4300,29 @@
         <v>13</v>
       </c>
       <c r="B91" s="7">
-        <v>798</v>
+        <v>325</v>
       </c>
       <c t="s" r="C91" s="7">
         <v>14</v>
       </c>
       <c r="D91" s="7"/>
       <c t="s" r="E91" s="7">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="F91" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G91" s="8">
-        <v>165</v>
+        <v>21</v>
       </c>
       <c t="s" r="H91" s="8">
-        <v>100</v>
+        <v>17</v>
       </c>
       <c t="s" r="I91" s="7">
-        <v>110</v>
+        <v>68</v>
       </c>
       <c t="s" r="J91" s="7">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="K91" s="7"/>
       <c r="L91" s="7"/>
@@ -4333,78 +4333,78 @@
         <v>13</v>
       </c>
       <c r="B92" s="7">
-        <v>799</v>
+        <v>978</v>
       </c>
       <c t="s" r="C92" s="7">
         <v>14</v>
       </c>
       <c r="D92" s="7"/>
       <c t="s" r="E92" s="7">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="F92" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G92" s="8">
-        <v>100</v>
+        <v>17</v>
       </c>
       <c t="s" r="H92" s="8">
-        <v>165</v>
+        <v>16</v>
       </c>
       <c t="s" r="I92" s="7">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c t="s" r="J92" s="7">
-        <v>33</v>
+        <v>169</v>
       </c>
       <c r="K92" s="7"/>
       <c r="L92" s="7"/>
       <c r="M92" s="7"/>
     </row>
     <row r="93" ht="14.25" customHeight="1">
-      <c t="s" r="A93" s="6">
-        <v>13</v>
-      </c>
-      <c r="B93" s="7">
-        <v>402</v>
-      </c>
-      <c t="s" r="C93" s="7">
-        <v>14</v>
-      </c>
+      <c r="A93" s="6"/>
+      <c r="B93" s="7"/>
+      <c r="C93" s="7"/>
       <c r="D93" s="7"/>
-      <c t="s" r="E93" s="7">
-        <v>160</v>
-      </c>
-      <c r="F93" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G93" s="8">
-        <v>165</v>
-      </c>
-      <c t="s" r="H93" s="8">
-        <v>24</v>
-      </c>
-      <c t="s" r="I93" s="7">
-        <v>103</v>
-      </c>
-      <c t="s" r="J93" s="7">
-        <v>104</v>
-      </c>
+      <c r="E93" s="7"/>
+      <c r="F93" s="7"/>
+      <c r="G93" s="8"/>
+      <c r="H93" s="8"/>
+      <c r="I93" s="7"/>
+      <c r="J93" s="7"/>
       <c r="K93" s="7"/>
       <c r="L93" s="7"/>
       <c r="M93" s="7"/>
     </row>
     <row r="94" ht="14.25" customHeight="1">
-      <c r="A94" s="6"/>
-      <c r="B94" s="7"/>
-      <c r="C94" s="7"/>
+      <c t="s" r="A94" s="6">
+        <v>13</v>
+      </c>
+      <c r="B94" s="7">
+        <v>501</v>
+      </c>
+      <c t="s" r="C94" s="7">
+        <v>14</v>
+      </c>
       <c r="D94" s="7"/>
-      <c r="E94" s="7"/>
-      <c r="F94" s="7"/>
-      <c r="G94" s="8"/>
-      <c r="H94" s="8"/>
-      <c r="I94" s="7"/>
-      <c r="J94" s="7"/>
+      <c t="s" r="E94" s="7">
+        <v>170</v>
+      </c>
+      <c r="F94" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G94" s="8">
+        <v>24</v>
+      </c>
+      <c t="s" r="H94" s="8">
+        <v>94</v>
+      </c>
+      <c t="s" r="I94" s="7">
+        <v>171</v>
+      </c>
+      <c t="s" r="J94" s="7">
+        <v>141</v>
+      </c>
       <c r="K94" s="7"/>
       <c r="L94" s="7"/>
       <c r="M94" s="7"/>
@@ -4414,26 +4414,26 @@
         <v>13</v>
       </c>
       <c r="B95" s="7">
-        <v>339</v>
+        <v>514</v>
       </c>
       <c t="s" r="C95" s="7">
         <v>14</v>
       </c>
       <c r="D95" s="7"/>
       <c t="s" r="E95" s="7">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="F95" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G95" s="8">
-        <v>21</v>
+        <v>94</v>
       </c>
       <c t="s" r="H95" s="8">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c t="s" r="I95" s="7">
-        <v>62</v>
+        <v>142</v>
       </c>
       <c t="s" r="J95" s="7">
         <v>143</v>
@@ -4447,29 +4447,29 @@
         <v>13</v>
       </c>
       <c r="B96" s="7">
-        <v>718</v>
+        <v>563</v>
       </c>
       <c t="s" r="C96" s="7">
         <v>14</v>
       </c>
       <c r="D96" s="7"/>
       <c t="s" r="E96" s="7">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="F96" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G96" s="8">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c t="s" r="H96" s="8">
-        <v>94</v>
+        <v>172</v>
       </c>
       <c t="s" r="I96" s="7">
-        <v>53</v>
+        <v>165</v>
       </c>
       <c t="s" r="J96" s="7">
-        <v>146</v>
+        <v>130</v>
       </c>
       <c r="K96" s="7"/>
       <c r="L96" s="7"/>
@@ -4480,29 +4480,29 @@
         <v>13</v>
       </c>
       <c r="B97" s="7">
-        <v>719</v>
+        <v>564</v>
       </c>
       <c t="s" r="C97" s="7">
         <v>14</v>
       </c>
       <c r="D97" s="7"/>
       <c t="s" r="E97" s="7">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="F97" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G97" s="8">
-        <v>94</v>
+        <v>172</v>
       </c>
       <c t="s" r="H97" s="8">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c t="s" r="I97" s="7">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c t="s" r="J97" s="7">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="K97" s="7"/>
       <c r="L97" s="7"/>
@@ -4513,29 +4513,29 @@
         <v>13</v>
       </c>
       <c r="B98" s="7">
-        <v>452</v>
+        <v>401</v>
       </c>
       <c t="s" r="C98" s="7">
         <v>14</v>
       </c>
       <c r="D98" s="7"/>
       <c t="s" r="E98" s="7">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="F98" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G98" s="8">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c t="s" r="H98" s="8">
-        <v>24</v>
+        <v>175</v>
       </c>
       <c t="s" r="I98" s="7">
-        <v>98</v>
+        <v>148</v>
       </c>
       <c t="s" r="J98" s="7">
-        <v>171</v>
+        <v>79</v>
       </c>
       <c r="K98" s="7"/>
       <c r="L98" s="7"/>
@@ -4546,29 +4546,29 @@
         <v>13</v>
       </c>
       <c r="B99" s="7">
-        <v>141</v>
+        <v>798</v>
       </c>
       <c t="s" r="C99" s="7">
         <v>14</v>
       </c>
       <c r="D99" s="7"/>
       <c t="s" r="E99" s="7">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="F99" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G99" s="8">
-        <v>24</v>
+        <v>175</v>
       </c>
       <c t="s" r="H99" s="8">
-        <v>21</v>
+        <v>100</v>
       </c>
       <c t="s" r="I99" s="7">
-        <v>172</v>
+        <v>110</v>
       </c>
       <c t="s" r="J99" s="7">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="K99" s="7"/>
       <c r="L99" s="7"/>
@@ -4579,29 +4579,29 @@
         <v>13</v>
       </c>
       <c r="B100" s="7">
-        <v>150</v>
+        <v>799</v>
       </c>
       <c t="s" r="C100" s="7">
         <v>14</v>
       </c>
       <c r="D100" s="7"/>
       <c t="s" r="E100" s="7">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="F100" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G100" s="8">
-        <v>21</v>
+        <v>100</v>
       </c>
       <c t="s" r="H100" s="8">
-        <v>24</v>
+        <v>175</v>
       </c>
       <c t="s" r="I100" s="7">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c t="s" r="J100" s="7">
-        <v>175</v>
+        <v>33</v>
       </c>
       <c r="K100" s="7"/>
       <c r="L100" s="7"/>
@@ -4609,32 +4609,32 @@
     </row>
     <row r="101" ht="14.25" customHeight="1">
       <c t="s" r="A101" s="6">
-        <v>48</v>
+        <v>13</v>
       </c>
       <c r="B101" s="7">
-        <v>960</v>
+        <v>402</v>
       </c>
       <c t="s" r="C101" s="7">
         <v>14</v>
       </c>
       <c r="D101" s="7"/>
       <c t="s" r="E101" s="7">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="F101" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G101" s="8">
-        <v>24</v>
+        <v>175</v>
       </c>
       <c t="s" r="H101" s="8">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c t="s" r="I101" s="7">
-        <v>176</v>
+        <v>103</v>
       </c>
       <c t="s" r="J101" s="7">
-        <v>177</v>
+        <v>104</v>
       </c>
       <c r="K101" s="7"/>
       <c r="L101" s="7"/>
@@ -4679,7 +4679,7 @@
         <v>21</v>
       </c>
       <c t="s" r="I103" s="7">
-        <v>169</v>
+        <v>153</v>
       </c>
       <c t="s" r="J103" s="7">
         <v>179</v>
@@ -5036,7 +5036,7 @@
         <v>24</v>
       </c>
       <c t="s" r="H115" s="8">
-        <v>165</v>
+        <v>175</v>
       </c>
       <c t="s" r="I115" s="7">
         <v>98</v>
@@ -5066,7 +5066,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G116" s="8">
-        <v>165</v>
+        <v>175</v>
       </c>
       <c t="s" r="H116" s="8">
         <v>24</v>
@@ -5075,7 +5075,7 @@
         <v>197</v>
       </c>
       <c t="s" r="J116" s="7">
-        <v>166</v>
+        <v>176</v>
       </c>
       <c r="K116" s="7"/>
       <c r="L116" s="7"/>
@@ -5153,7 +5153,7 @@
         <v>64</v>
       </c>
       <c t="s" r="I119" s="7">
-        <v>177</v>
+        <v>161</v>
       </c>
       <c t="s" r="J119" s="7">
         <v>200</v>
@@ -5234,10 +5234,10 @@
         <v>24</v>
       </c>
       <c t="s" r="I122" s="7">
-        <v>155</v>
+        <v>165</v>
       </c>
       <c t="s" r="J122" s="7">
-        <v>164</v>
+        <v>174</v>
       </c>
       <c r="K122" s="7"/>
       <c r="L122" s="7"/>
@@ -5333,7 +5333,7 @@
         <v>52</v>
       </c>
       <c t="s" r="I125" s="7">
-        <v>176</v>
+        <v>160</v>
       </c>
       <c t="s" r="J125" s="7">
         <v>73</v>
@@ -5417,7 +5417,7 @@
         <v>42</v>
       </c>
       <c t="s" r="J128" s="7">
-        <v>174</v>
+        <v>158</v>
       </c>
       <c r="K128" s="7"/>
       <c r="L128" s="7"/>
@@ -5741,7 +5741,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I139" s="7">
-        <v>164</v>
+        <v>174</v>
       </c>
       <c t="s" r="J139" s="7">
         <v>32</v>
@@ -5822,7 +5822,7 @@
         <v>24</v>
       </c>
       <c t="s" r="I142" s="7">
-        <v>156</v>
+        <v>166</v>
       </c>
       <c t="s" r="J142" s="7">
         <v>68</v>
@@ -6215,7 +6215,7 @@
         <v>24</v>
       </c>
       <c t="s" r="I155" s="7">
-        <v>155</v>
+        <v>165</v>
       </c>
       <c t="s" r="J155" s="7">
         <v>236</v>
@@ -6380,7 +6380,7 @@
         <v>94</v>
       </c>
       <c t="s" r="I160" s="7">
-        <v>167</v>
+        <v>177</v>
       </c>
       <c t="s" r="J160" s="7">
         <v>124</v>
@@ -6534,7 +6534,7 @@
         <v>245</v>
       </c>
       <c t="s" r="J165" s="7">
-        <v>167</v>
+        <v>177</v>
       </c>
       <c r="K165" s="7"/>
       <c r="L165" s="7"/>
@@ -6600,7 +6600,7 @@
         <v>219</v>
       </c>
       <c t="s" r="J167" s="7">
-        <v>177</v>
+        <v>161</v>
       </c>
       <c r="K167" s="7"/>
       <c r="L167" s="7"/>
@@ -7068,7 +7068,7 @@
         <v>21</v>
       </c>
       <c t="s" r="H183" s="8">
-        <v>162</v>
+        <v>172</v>
       </c>
       <c t="s" r="I183" s="7">
         <v>260</v>
@@ -7098,7 +7098,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G184" s="8">
-        <v>162</v>
+        <v>172</v>
       </c>
       <c t="s" r="H184" s="8">
         <v>21</v>
@@ -7134,7 +7134,7 @@
         <v>21</v>
       </c>
       <c t="s" r="H185" s="8">
-        <v>162</v>
+        <v>172</v>
       </c>
       <c t="s" r="I185" s="7">
         <v>262</v>
@@ -7164,7 +7164,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G186" s="8">
-        <v>162</v>
+        <v>172</v>
       </c>
       <c t="s" r="H186" s="8">
         <v>21</v>
@@ -7200,7 +7200,7 @@
         <v>21</v>
       </c>
       <c t="s" r="H187" s="8">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c t="s" r="I187" s="7">
         <v>197</v>
@@ -7230,7 +7230,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G188" s="8">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c t="s" r="H188" s="8">
         <v>21</v>
@@ -7533,7 +7533,7 @@
         <v>232</v>
       </c>
       <c t="s" r="J198" s="7">
-        <v>167</v>
+        <v>177</v>
       </c>
       <c r="K198" s="7"/>
       <c r="L198" s="7"/>
@@ -7560,7 +7560,7 @@
         <v>24</v>
       </c>
       <c t="s" r="H199" s="8">
-        <v>165</v>
+        <v>175</v>
       </c>
       <c t="s" r="I199" s="7">
         <v>271</v>
@@ -7590,7 +7590,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G200" s="8">
-        <v>165</v>
+        <v>175</v>
       </c>
       <c t="s" r="H200" s="8">
         <v>24</v>
@@ -7812,7 +7812,7 @@
         <v>277</v>
       </c>
       <c t="s" r="J207" s="7">
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="K207" s="7"/>
       <c r="L207" s="7"/>
@@ -7923,7 +7923,7 @@
         <v>24</v>
       </c>
       <c t="s" r="I211" s="7">
-        <v>156</v>
+        <v>166</v>
       </c>
       <c t="s" r="J211" s="7">
         <v>108</v>
@@ -8073,7 +8073,7 @@
         <v>65</v>
       </c>
       <c t="s" r="J216" s="7">
-        <v>169</v>
+        <v>153</v>
       </c>
       <c r="K216" s="7"/>
       <c r="L216" s="7"/>
@@ -8379,13 +8379,13 @@
         <v>21</v>
       </c>
       <c t="s" r="H226" s="8">
-        <v>162</v>
+        <v>172</v>
       </c>
       <c t="s" r="I226" s="7">
         <v>197</v>
       </c>
       <c t="s" r="J226" s="7">
-        <v>158</v>
+        <v>168</v>
       </c>
       <c r="K226" s="7"/>
       <c r="L226" s="7"/>
@@ -8409,7 +8409,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G227" s="8">
-        <v>162</v>
+        <v>172</v>
       </c>
       <c t="s" r="H227" s="8">
         <v>21</v>
@@ -8907,10 +8907,10 @@
         <v>293</v>
       </c>
       <c t="s" r="I243" s="7">
-        <v>175</v>
+        <v>159</v>
       </c>
       <c t="s" r="J243" s="7">
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="K243" s="7"/>
       <c r="L243" s="7"/>
@@ -9369,7 +9369,7 @@
         <v>181</v>
       </c>
       <c t="s" r="J258" s="7">
-        <v>175</v>
+        <v>159</v>
       </c>
       <c r="K258" s="7"/>
       <c r="L258" s="7"/>
@@ -9447,7 +9447,7 @@
         <v>24</v>
       </c>
       <c t="s" r="I261" s="7">
-        <v>163</v>
+        <v>173</v>
       </c>
       <c t="s" r="J261" s="7">
         <v>205</v>
@@ -9792,7 +9792,7 @@
         <v>142</v>
       </c>
       <c t="s" r="J273" s="7">
-        <v>155</v>
+        <v>165</v>
       </c>
       <c r="K273" s="7"/>
       <c r="L273" s="7"/>
@@ -9825,7 +9825,7 @@
         <v>210</v>
       </c>
       <c t="s" r="J274" s="7">
-        <v>169</v>
+        <v>153</v>
       </c>
       <c r="K274" s="7"/>
       <c r="L274" s="7"/>
@@ -9852,7 +9852,7 @@
         <v>21</v>
       </c>
       <c t="s" r="H275" s="8">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c t="s" r="I275" s="7">
         <v>321</v>
@@ -9882,7 +9882,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G276" s="8">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c t="s" r="H276" s="8">
         <v>21</v>
@@ -9891,7 +9891,7 @@
         <v>308</v>
       </c>
       <c t="s" r="J276" s="7">
-        <v>166</v>
+        <v>176</v>
       </c>
       <c r="K276" s="7"/>
       <c r="L276" s="7"/>
@@ -9921,7 +9921,7 @@
         <v>24</v>
       </c>
       <c t="s" r="I277" s="7">
-        <v>167</v>
+        <v>177</v>
       </c>
       <c t="s" r="J277" s="7">
         <v>71</v>
@@ -10299,7 +10299,7 @@
         <v>142</v>
       </c>
       <c t="s" r="J290" s="7">
-        <v>169</v>
+        <v>153</v>
       </c>
       <c r="K290" s="7"/>
       <c r="L290" s="7"/>
@@ -10440,7 +10440,7 @@
         <v>24</v>
       </c>
       <c t="s" r="H295" s="8">
-        <v>165</v>
+        <v>175</v>
       </c>
       <c t="s" r="I295" s="7">
         <v>300</v>
@@ -10470,7 +10470,7 @@
         <v>320</v>
       </c>
       <c t="s" r="G296" s="8">
-        <v>165</v>
+        <v>175</v>
       </c>
       <c t="s" r="H296" s="8">
         <v>24</v>
@@ -10545,7 +10545,7 @@
         <v>44</v>
       </c>
       <c t="s" r="J298" s="7">
-        <v>173</v>
+        <v>157</v>
       </c>
       <c r="K298" s="7"/>
       <c r="L298" s="7"/>
@@ -11052,14 +11052,14 @@
         <v>279</v>
       </c>
       <c t="s" r="J315" s="7">
-        <v>154</v>
+        <v>164</v>
       </c>
       <c t="s" r="K315" s="7">
         <v>279</v>
       </c>
       <c r="L315" s="7"/>
       <c t="s" r="M315" s="7">
-        <v>154</v>
+        <v>164</v>
       </c>
     </row>
     <row r="316" ht="14.25" customHeight="1">
@@ -11119,7 +11119,7 @@
         <v>21</v>
       </c>
       <c t="s" r="I317" s="7">
-        <v>155</v>
+        <v>165</v>
       </c>
       <c t="s" r="J317" s="7">
         <v>213</v>
@@ -11464,7 +11464,7 @@
         <v>24</v>
       </c>
       <c t="s" r="I328" s="7">
-        <v>173</v>
+        <v>157</v>
       </c>
       <c t="s" r="J328" s="7">
         <v>149</v>
@@ -11824,7 +11824,7 @@
         <v>100</v>
       </c>
       <c t="s" r="I340" s="7">
-        <v>174</v>
+        <v>158</v>
       </c>
       <c t="s" r="J340" s="7">
         <v>125</v>
@@ -11935,7 +11935,7 @@
         <v>40</v>
       </c>
       <c t="s" r="H344" s="8">
-        <v>165</v>
+        <v>175</v>
       </c>
       <c t="s" r="I344" s="7">
         <v>308</v>
@@ -11965,7 +11965,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G345" s="8">
-        <v>165</v>
+        <v>175</v>
       </c>
       <c t="s" r="H345" s="8">
         <v>40</v>
@@ -12115,7 +12115,7 @@
         <v>21</v>
       </c>
       <c t="s" r="H350" s="8">
-        <v>162</v>
+        <v>172</v>
       </c>
       <c t="s" r="I350" s="7">
         <v>143</v>
@@ -12145,7 +12145,7 @@
         <v>320</v>
       </c>
       <c t="s" r="G351" s="8">
-        <v>162</v>
+        <v>172</v>
       </c>
       <c t="s" r="H351" s="8">
         <v>21</v>
@@ -12220,7 +12220,7 @@
         <v>133</v>
       </c>
       <c t="s" r="J353" s="7">
-        <v>171</v>
+        <v>155</v>
       </c>
       <c r="K353" s="7"/>
       <c r="L353" s="7"/>
@@ -12253,7 +12253,7 @@
         <v>255</v>
       </c>
       <c t="s" r="J354" s="7">
-        <v>158</v>
+        <v>168</v>
       </c>
       <c r="K354" s="7"/>
       <c r="L354" s="7"/>
@@ -12313,7 +12313,7 @@
         <v>21</v>
       </c>
       <c t="s" r="H356" s="8">
-        <v>162</v>
+        <v>172</v>
       </c>
       <c t="s" r="I356" s="7">
         <v>46</v>
@@ -12343,7 +12343,7 @@
         <v>320</v>
       </c>
       <c t="s" r="G357" s="8">
-        <v>162</v>
+        <v>172</v>
       </c>
       <c t="s" r="H357" s="8">
         <v>21</v>
@@ -12460,7 +12460,7 @@
         <v>21</v>
       </c>
       <c t="s" r="H361" s="8">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c t="s" r="I361" s="7">
         <v>147</v>
@@ -12490,7 +12490,7 @@
         <v>320</v>
       </c>
       <c t="s" r="G362" s="8">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c t="s" r="H362" s="8">
         <v>21</v>
@@ -12676,7 +12676,7 @@
         <v>21</v>
       </c>
       <c t="s" r="I368" s="7">
-        <v>156</v>
+        <v>166</v>
       </c>
       <c t="s" r="J368" s="7">
         <v>108</v>
@@ -12745,7 +12745,7 @@
         <v>110</v>
       </c>
       <c t="s" r="J370" s="7">
-        <v>172</v>
+        <v>156</v>
       </c>
       <c r="K370" s="7"/>
       <c r="L370" s="7"/>
@@ -12991,7 +12991,7 @@
         <v>81</v>
       </c>
       <c t="s" r="J378" s="7">
-        <v>158</v>
+        <v>168</v>
       </c>
       <c r="K378" s="7"/>
       <c r="L378" s="7"/>
@@ -13069,7 +13069,7 @@
         <v>349</v>
       </c>
       <c t="s" r="I381" s="7">
-        <v>155</v>
+        <v>165</v>
       </c>
       <c t="s" r="J381" s="7">
         <v>236</v>
@@ -13132,7 +13132,7 @@
         <v>21</v>
       </c>
       <c t="s" r="H383" s="8">
-        <v>165</v>
+        <v>175</v>
       </c>
       <c t="s" r="I383" s="7">
         <v>56</v>
@@ -13162,7 +13162,7 @@
         <v>320</v>
       </c>
       <c t="s" r="G384" s="8">
-        <v>165</v>
+        <v>175</v>
       </c>
       <c t="s" r="H384" s="8">
         <v>21</v>
@@ -13345,7 +13345,7 @@
         <v>21</v>
       </c>
       <c t="s" r="H390" s="8">
-        <v>162</v>
+        <v>172</v>
       </c>
       <c t="s" r="I390" s="7">
         <v>69</v>
@@ -13375,7 +13375,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G391" s="8">
-        <v>162</v>
+        <v>172</v>
       </c>
       <c t="s" r="H391" s="8">
         <v>21</v>
@@ -13450,7 +13450,7 @@
         <v>83</v>
       </c>
       <c t="s" r="J393" s="7">
-        <v>177</v>
+        <v>161</v>
       </c>
       <c r="K393" s="7"/>
       <c r="L393" s="7"/>
@@ -13738,7 +13738,7 @@
         <v>24</v>
       </c>
       <c t="s" r="H403" s="8">
-        <v>162</v>
+        <v>172</v>
       </c>
       <c t="s" r="I403" s="7">
         <v>324</v>
@@ -13768,7 +13768,7 @@
         <v>320</v>
       </c>
       <c t="s" r="G404" s="8">
-        <v>162</v>
+        <v>172</v>
       </c>
       <c t="s" r="H404" s="8">
         <v>24</v>
@@ -13840,7 +13840,7 @@
         <v>24</v>
       </c>
       <c t="s" r="I406" s="7">
-        <v>158</v>
+        <v>168</v>
       </c>
       <c t="s" r="J406" s="7">
         <v>32</v>
@@ -14167,7 +14167,7 @@
         <v>21</v>
       </c>
       <c t="s" r="I417" s="7">
-        <v>164</v>
+        <v>174</v>
       </c>
       <c t="s" r="J417" s="7">
         <v>269</v>
@@ -14314,7 +14314,7 @@
         <v>94</v>
       </c>
       <c t="s" r="I422" s="7">
-        <v>177</v>
+        <v>161</v>
       </c>
       <c t="s" r="J422" s="7">
         <v>212</v>
@@ -14380,7 +14380,7 @@
         <v>94</v>
       </c>
       <c t="s" r="I424" s="7">
-        <v>156</v>
+        <v>166</v>
       </c>
       <c t="s" r="J424" s="7">
         <v>348</v>
@@ -14836,7 +14836,7 @@
         <v>24</v>
       </c>
       <c t="s" r="H439" s="8">
-        <v>162</v>
+        <v>172</v>
       </c>
       <c t="s" r="I439" s="7">
         <v>42</v>
@@ -14866,7 +14866,7 @@
         <v>320</v>
       </c>
       <c t="s" r="G440" s="8">
-        <v>162</v>
+        <v>172</v>
       </c>
       <c t="s" r="H440" s="8">
         <v>24</v>
@@ -15202,7 +15202,7 @@
         <v>81</v>
       </c>
       <c t="s" r="J451" s="7">
-        <v>158</v>
+        <v>168</v>
       </c>
       <c r="K451" s="7"/>
       <c r="L451" s="7"/>
@@ -15589,10 +15589,10 @@
         <v>396</v>
       </c>
       <c t="s" r="I465" s="7">
+        <v>165</v>
+      </c>
+      <c t="s" r="J465" s="7">
         <v>155</v>
-      </c>
-      <c t="s" r="J465" s="7">
-        <v>171</v>
       </c>
       <c r="K465" s="7"/>
       <c r="L465" s="7"/>
@@ -15622,7 +15622,7 @@
         <v>94</v>
       </c>
       <c t="s" r="I466" s="7">
-        <v>172</v>
+        <v>156</v>
       </c>
       <c t="s" r="J466" s="7">
         <v>208</v>
@@ -15673,7 +15673,7 @@
         <v>39</v>
       </c>
       <c t="s" r="J468" s="7">
-        <v>171</v>
+        <v>155</v>
       </c>
       <c r="K468" s="7"/>
       <c r="L468" s="7"/>

--- a/Data/FlightPlan/FPL_26AUG26.xlsx
+++ b/Data/FlightPlan/FPL_26AUG26.xlsx
@@ -812,117 +812,117 @@
     <t>VN-A634</t>
   </si>
   <si>
+    <t>09:05</t>
+  </si>
+  <si>
+    <t>10:25</t>
+  </si>
+  <si>
+    <t>UIH</t>
+  </si>
+  <si>
+    <t>15:25</t>
+  </si>
+  <si>
+    <t>16:00</t>
+  </si>
+  <si>
+    <t>20:10</t>
+  </si>
+  <si>
+    <t>22:20</t>
+  </si>
+  <si>
+    <t>23:00</t>
+  </si>
+  <si>
+    <t>VN-A635</t>
+  </si>
+  <si>
+    <t>14:20</t>
+  </si>
+  <si>
+    <t>TBB</t>
+  </si>
+  <si>
+    <t>19:15</t>
+  </si>
+  <si>
+    <t>CAN</t>
+  </si>
+  <si>
+    <t>02:10</t>
+  </si>
+  <si>
+    <t>03:05</t>
+  </si>
+  <si>
+    <t>VN-A636</t>
+  </si>
+  <si>
+    <t>05:00</t>
+  </si>
+  <si>
+    <t>14:05</t>
+  </si>
+  <si>
+    <t>16:15</t>
+  </si>
+  <si>
+    <t>VN-A637</t>
+  </si>
+  <si>
+    <t>VN-A639</t>
+  </si>
+  <si>
+    <t>11:15</t>
+  </si>
+  <si>
+    <t>12:45</t>
+  </si>
+  <si>
+    <t>19:40</t>
+  </si>
+  <si>
+    <t>20:15</t>
+  </si>
+  <si>
+    <t>22:45</t>
+  </si>
+  <si>
+    <t>00:45</t>
+  </si>
+  <si>
+    <t>VN-A640</t>
+  </si>
+  <si>
+    <t>18:30</t>
+  </si>
+  <si>
+    <t>21:45</t>
+  </si>
+  <si>
+    <t>01:30</t>
+  </si>
+  <si>
+    <t>02:30</t>
+  </si>
+  <si>
+    <t>04:10</t>
+  </si>
+  <si>
+    <t>VN-A641</t>
+  </si>
+  <si>
     <t>08:15</t>
   </si>
   <si>
-    <t>12:45</t>
-  </si>
-  <si>
     <t>14:30</t>
   </si>
   <si>
     <t>PXU</t>
   </si>
   <si>
-    <t>19:15</t>
-  </si>
-  <si>
-    <t>VN-A635</t>
-  </si>
-  <si>
-    <t>14:20</t>
-  </si>
-  <si>
-    <t>TBB</t>
-  </si>
-  <si>
-    <t>20:10</t>
-  </si>
-  <si>
-    <t>22:20</t>
-  </si>
-  <si>
-    <t>23:00</t>
-  </si>
-  <si>
-    <t>VN-A636</t>
-  </si>
-  <si>
-    <t>05:00</t>
-  </si>
-  <si>
-    <t>14:05</t>
-  </si>
-  <si>
-    <t>16:15</t>
-  </si>
-  <si>
-    <t>VN-A637</t>
-  </si>
-  <si>
-    <t>15:25</t>
-  </si>
-  <si>
-    <t>16:00</t>
-  </si>
-  <si>
-    <t>VN-A639</t>
-  </si>
-  <si>
-    <t>11:15</t>
-  </si>
-  <si>
-    <t>19:40</t>
-  </si>
-  <si>
-    <t>20:15</t>
-  </si>
-  <si>
-    <t>22:45</t>
-  </si>
-  <si>
-    <t>00:45</t>
-  </si>
-  <si>
-    <t>VN-A640</t>
-  </si>
-  <si>
-    <t>18:30</t>
-  </si>
-  <si>
-    <t>CAN</t>
-  </si>
-  <si>
-    <t>21:45</t>
-  </si>
-  <si>
-    <t>01:30</t>
-  </si>
-  <si>
-    <t>02:30</t>
-  </si>
-  <si>
-    <t>04:10</t>
-  </si>
-  <si>
-    <t>VN-A641</t>
-  </si>
-  <si>
-    <t>09:05</t>
-  </si>
-  <si>
-    <t>10:25</t>
-  </si>
-  <si>
-    <t>UIH</t>
-  </si>
-  <si>
-    <t>02:10</t>
-  </si>
-  <si>
-    <t>03:05</t>
-  </si>
-  <si>
     <t>VN-A642</t>
   </si>
   <si>
@@ -1220,7 +1220,7 @@
     <t>Total Record(s): 390</t>
   </si>
   <si>
-    <t xml:space="preserve">Generated on  Aug 26, 2026 03:35</t>
+    <t xml:space="preserve">Generated on  Aug 26, 2026 03:51</t>
   </si>
   <si>
     <t>Page 1 of 1</t>
@@ -7346,7 +7346,7 @@
         <v>13</v>
       </c>
       <c r="B193" s="7">
-        <v>491</v>
+        <v>505</v>
       </c>
       <c t="s" r="C193" s="7">
         <v>14</v>
@@ -7362,13 +7362,13 @@
         <v>24</v>
       </c>
       <c t="s" r="H193" s="8">
-        <v>29</v>
+        <v>94</v>
       </c>
       <c t="s" r="I193" s="7">
-        <v>220</v>
+        <v>267</v>
       </c>
       <c t="s" r="J193" s="7">
-        <v>252</v>
+        <v>268</v>
       </c>
       <c r="K193" s="7"/>
       <c r="L193" s="7"/>
@@ -7379,7 +7379,7 @@
         <v>13</v>
       </c>
       <c r="B194" s="7">
-        <v>492</v>
+        <v>506</v>
       </c>
       <c t="s" r="C194" s="7">
         <v>14</v>
@@ -7392,16 +7392,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G194" s="8">
-        <v>29</v>
+        <v>94</v>
       </c>
       <c t="s" r="H194" s="8">
         <v>24</v>
       </c>
       <c t="s" r="I194" s="7">
-        <v>267</v>
+        <v>186</v>
       </c>
       <c t="s" r="J194" s="7">
-        <v>107</v>
+        <v>214</v>
       </c>
       <c r="K194" s="7"/>
       <c r="L194" s="7"/>
@@ -7412,7 +7412,7 @@
         <v>13</v>
       </c>
       <c r="B195" s="7">
-        <v>1491</v>
+        <v>433</v>
       </c>
       <c t="s" r="C195" s="7">
         <v>14</v>
@@ -7428,13 +7428,13 @@
         <v>24</v>
       </c>
       <c t="s" r="H195" s="8">
-        <v>29</v>
+        <v>269</v>
       </c>
       <c t="s" r="I195" s="7">
-        <v>262</v>
+        <v>188</v>
       </c>
       <c t="s" r="J195" s="7">
-        <v>214</v>
+        <v>270</v>
       </c>
       <c r="K195" s="7"/>
       <c r="L195" s="7"/>
@@ -7445,7 +7445,7 @@
         <v>13</v>
       </c>
       <c r="B196" s="7">
-        <v>1492</v>
+        <v>434</v>
       </c>
       <c t="s" r="C196" s="7">
         <v>14</v>
@@ -7458,16 +7458,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G196" s="8">
-        <v>29</v>
+        <v>269</v>
       </c>
       <c t="s" r="H196" s="8">
         <v>24</v>
       </c>
       <c t="s" r="I196" s="7">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c t="s" r="J196" s="7">
-        <v>269</v>
+        <v>233</v>
       </c>
       <c r="K196" s="7"/>
       <c r="L196" s="7"/>
@@ -7478,7 +7478,7 @@
         <v>13</v>
       </c>
       <c r="B197" s="7">
-        <v>423</v>
+        <v>159</v>
       </c>
       <c t="s" r="C197" s="7">
         <v>14</v>
@@ -7494,13 +7494,13 @@
         <v>24</v>
       </c>
       <c t="s" r="H197" s="8">
-        <v>270</v>
+        <v>21</v>
       </c>
       <c t="s" r="I197" s="7">
-        <v>79</v>
+        <v>272</v>
       </c>
       <c t="s" r="J197" s="7">
-        <v>99</v>
+        <v>273</v>
       </c>
       <c r="K197" s="7"/>
       <c r="L197" s="7"/>
@@ -7511,7 +7511,7 @@
         <v>13</v>
       </c>
       <c r="B198" s="7">
-        <v>424</v>
+        <v>168</v>
       </c>
       <c t="s" r="C198" s="7">
         <v>14</v>
@@ -7524,50 +7524,32 @@
         <v>321</v>
       </c>
       <c t="s" r="G198" s="8">
-        <v>270</v>
+        <v>21</v>
       </c>
       <c t="s" r="H198" s="8">
         <v>24</v>
       </c>
       <c t="s" r="I198" s="7">
-        <v>232</v>
+        <v>274</v>
       </c>
       <c t="s" r="J198" s="7">
-        <v>177</v>
+        <v>169</v>
       </c>
       <c r="K198" s="7"/>
       <c r="L198" s="7"/>
       <c r="M198" s="7"/>
     </row>
     <row r="199" ht="14.25" customHeight="1">
-      <c t="s" r="A199" s="6">
-        <v>13</v>
-      </c>
-      <c r="B199" s="7">
-        <v>409</v>
-      </c>
-      <c t="s" r="C199" s="7">
-        <v>14</v>
-      </c>
+      <c r="A199" s="6"/>
+      <c r="B199" s="7"/>
+      <c r="C199" s="7"/>
       <c r="D199" s="7"/>
-      <c t="s" r="E199" s="7">
-        <v>266</v>
-      </c>
-      <c r="F199" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G199" s="8">
-        <v>24</v>
-      </c>
-      <c t="s" r="H199" s="8">
-        <v>175</v>
-      </c>
-      <c t="s" r="I199" s="7">
-        <v>271</v>
-      </c>
-      <c t="s" r="J199" s="7">
-        <v>198</v>
-      </c>
+      <c r="E199" s="7"/>
+      <c r="F199" s="7"/>
+      <c r="G199" s="8"/>
+      <c r="H199" s="8"/>
+      <c r="I199" s="7"/>
+      <c r="J199" s="7"/>
       <c r="K199" s="7"/>
       <c r="L199" s="7"/>
       <c r="M199" s="7"/>
@@ -7577,45 +7559,63 @@
         <v>13</v>
       </c>
       <c r="B200" s="7">
-        <v>410</v>
+        <v>1773</v>
       </c>
       <c t="s" r="C200" s="7">
         <v>14</v>
       </c>
       <c r="D200" s="7"/>
       <c t="s" r="E200" s="7">
-        <v>266</v>
+        <v>275</v>
       </c>
       <c r="F200" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G200" s="8">
-        <v>175</v>
+        <v>24</v>
       </c>
       <c t="s" r="H200" s="8">
-        <v>24</v>
+        <v>76</v>
       </c>
       <c t="s" r="I200" s="7">
-        <v>207</v>
+        <v>107</v>
       </c>
       <c t="s" r="J200" s="7">
-        <v>150</v>
+        <v>249</v>
       </c>
       <c r="K200" s="7"/>
       <c r="L200" s="7"/>
       <c r="M200" s="7"/>
     </row>
     <row r="201" ht="14.25" customHeight="1">
-      <c r="A201" s="6"/>
-      <c r="B201" s="7"/>
-      <c r="C201" s="7"/>
+      <c t="s" r="A201" s="6">
+        <v>13</v>
+      </c>
+      <c r="B201" s="7">
+        <v>1774</v>
+      </c>
+      <c t="s" r="C201" s="7">
+        <v>14</v>
+      </c>
       <c r="D201" s="7"/>
-      <c r="E201" s="7"/>
-      <c r="F201" s="7"/>
-      <c r="G201" s="8"/>
-      <c r="H201" s="8"/>
-      <c r="I201" s="7"/>
-      <c r="J201" s="7"/>
+      <c t="s" r="E201" s="7">
+        <v>275</v>
+      </c>
+      <c r="F201" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G201" s="8">
+        <v>76</v>
+      </c>
+      <c t="s" r="H201" s="8">
+        <v>24</v>
+      </c>
+      <c t="s" r="I201" s="7">
+        <v>115</v>
+      </c>
+      <c t="s" r="J201" s="7">
+        <v>276</v>
+      </c>
       <c r="K201" s="7"/>
       <c r="L201" s="7"/>
       <c r="M201" s="7"/>
@@ -7625,14 +7625,14 @@
         <v>13</v>
       </c>
       <c r="B202" s="7">
-        <v>1773</v>
+        <v>419</v>
       </c>
       <c t="s" r="C202" s="7">
         <v>14</v>
       </c>
       <c r="D202" s="7"/>
       <c t="s" r="E202" s="7">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="F202" s="7">
         <v>321</v>
@@ -7641,13 +7641,13 @@
         <v>24</v>
       </c>
       <c t="s" r="H202" s="8">
-        <v>76</v>
+        <v>277</v>
       </c>
       <c t="s" r="I202" s="7">
-        <v>107</v>
+        <v>190</v>
       </c>
       <c t="s" r="J202" s="7">
-        <v>249</v>
+        <v>237</v>
       </c>
       <c r="K202" s="7"/>
       <c r="L202" s="7"/>
@@ -7658,29 +7658,29 @@
         <v>13</v>
       </c>
       <c r="B203" s="7">
-        <v>1774</v>
+        <v>420</v>
       </c>
       <c t="s" r="C203" s="7">
         <v>14</v>
       </c>
       <c r="D203" s="7"/>
       <c t="s" r="E203" s="7">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="F203" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G203" s="8">
-        <v>76</v>
+        <v>277</v>
       </c>
       <c t="s" r="H203" s="8">
         <v>24</v>
       </c>
       <c t="s" r="I203" s="7">
-        <v>115</v>
+        <v>134</v>
       </c>
       <c t="s" r="J203" s="7">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="K203" s="7"/>
       <c r="L203" s="7"/>
@@ -7691,14 +7691,14 @@
         <v>13</v>
       </c>
       <c r="B204" s="7">
-        <v>419</v>
+        <v>7526</v>
       </c>
       <c t="s" r="C204" s="7">
         <v>14</v>
       </c>
       <c r="D204" s="7"/>
       <c t="s" r="E204" s="7">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="F204" s="7">
         <v>321</v>
@@ -7707,13 +7707,13 @@
         <v>24</v>
       </c>
       <c t="s" r="H204" s="8">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c t="s" r="I204" s="7">
-        <v>190</v>
+        <v>159</v>
       </c>
       <c t="s" r="J204" s="7">
-        <v>237</v>
+        <v>169</v>
       </c>
       <c r="K204" s="7"/>
       <c r="L204" s="7"/>
@@ -7721,66 +7721,48 @@
     </row>
     <row r="205" ht="15" customHeight="1">
       <c t="s" r="A205" s="6">
-        <v>13</v>
+        <v>48</v>
       </c>
       <c r="B205" s="7">
-        <v>420</v>
+        <v>7527</v>
       </c>
       <c t="s" r="C205" s="7">
         <v>14</v>
       </c>
       <c r="D205" s="7"/>
       <c t="s" r="E205" s="7">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="F205" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G205" s="8">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c t="s" r="H205" s="8">
         <v>24</v>
       </c>
       <c t="s" r="I205" s="7">
-        <v>134</v>
+        <v>280</v>
       </c>
       <c t="s" r="J205" s="7">
-        <v>271</v>
+        <v>281</v>
       </c>
       <c r="K205" s="7"/>
       <c r="L205" s="7"/>
       <c r="M205" s="7"/>
     </row>
     <row r="206" ht="14.25" customHeight="1">
-      <c t="s" r="A206" s="6">
-        <v>13</v>
-      </c>
-      <c r="B206" s="7">
-        <v>159</v>
-      </c>
-      <c t="s" r="C206" s="7">
-        <v>14</v>
-      </c>
+      <c r="A206" s="6"/>
+      <c r="B206" s="7"/>
+      <c r="C206" s="7"/>
       <c r="D206" s="7"/>
-      <c t="s" r="E206" s="7">
-        <v>272</v>
-      </c>
-      <c r="F206" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G206" s="8">
-        <v>24</v>
-      </c>
-      <c t="s" r="H206" s="8">
-        <v>21</v>
-      </c>
-      <c t="s" r="I206" s="7">
-        <v>275</v>
-      </c>
-      <c t="s" r="J206" s="7">
-        <v>276</v>
-      </c>
+      <c r="E206" s="7"/>
+      <c r="F206" s="7"/>
+      <c r="G206" s="8"/>
+      <c r="H206" s="8"/>
+      <c r="I206" s="7"/>
+      <c r="J206" s="7"/>
       <c r="K206" s="7"/>
       <c r="L206" s="7"/>
       <c r="M206" s="7"/>
@@ -7790,14 +7772,14 @@
         <v>13</v>
       </c>
       <c r="B207" s="7">
-        <v>168</v>
+        <v>120</v>
       </c>
       <c t="s" r="C207" s="7">
         <v>14</v>
       </c>
       <c r="D207" s="7"/>
       <c t="s" r="E207" s="7">
-        <v>272</v>
+        <v>282</v>
       </c>
       <c r="F207" s="7">
         <v>321</v>
@@ -7809,26 +7791,44 @@
         <v>24</v>
       </c>
       <c t="s" r="I207" s="7">
-        <v>277</v>
+        <v>283</v>
       </c>
       <c t="s" r="J207" s="7">
-        <v>169</v>
+        <v>138</v>
       </c>
       <c r="K207" s="7"/>
       <c r="L207" s="7"/>
       <c r="M207" s="7"/>
     </row>
     <row r="208" ht="14.25" customHeight="1">
-      <c r="A208" s="6"/>
-      <c r="B208" s="7"/>
-      <c r="C208" s="7"/>
+      <c t="s" r="A208" s="6">
+        <v>13</v>
+      </c>
+      <c r="B208" s="7">
+        <v>127</v>
+      </c>
+      <c t="s" r="C208" s="7">
+        <v>14</v>
+      </c>
       <c r="D208" s="7"/>
-      <c r="E208" s="7"/>
-      <c r="F208" s="7"/>
-      <c r="G208" s="8"/>
-      <c r="H208" s="8"/>
-      <c r="I208" s="7"/>
-      <c r="J208" s="7"/>
+      <c t="s" r="E208" s="7">
+        <v>282</v>
+      </c>
+      <c r="F208" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G208" s="8">
+        <v>24</v>
+      </c>
+      <c t="s" r="H208" s="8">
+        <v>21</v>
+      </c>
+      <c t="s" r="I208" s="7">
+        <v>37</v>
+      </c>
+      <c t="s" r="J208" s="7">
+        <v>213</v>
+      </c>
       <c r="K208" s="7"/>
       <c r="L208" s="7"/>
       <c r="M208" s="7"/>
@@ -7838,14 +7838,14 @@
         <v>13</v>
       </c>
       <c r="B209" s="7">
-        <v>120</v>
+        <v>134</v>
       </c>
       <c t="s" r="C209" s="7">
         <v>14</v>
       </c>
       <c r="D209" s="7"/>
       <c t="s" r="E209" s="7">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="F209" s="7">
         <v>321</v>
@@ -7857,10 +7857,10 @@
         <v>24</v>
       </c>
       <c t="s" r="I209" s="7">
-        <v>279</v>
+        <v>166</v>
       </c>
       <c t="s" r="J209" s="7">
-        <v>138</v>
+        <v>108</v>
       </c>
       <c r="K209" s="7"/>
       <c r="L209" s="7"/>
@@ -7871,14 +7871,14 @@
         <v>13</v>
       </c>
       <c r="B210" s="7">
-        <v>127</v>
+        <v>143</v>
       </c>
       <c t="s" r="C210" s="7">
         <v>14</v>
       </c>
       <c r="D210" s="7"/>
       <c t="s" r="E210" s="7">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="F210" s="7">
         <v>321</v>
@@ -7890,10 +7890,10 @@
         <v>21</v>
       </c>
       <c t="s" r="I210" s="7">
-        <v>37</v>
+        <v>284</v>
       </c>
       <c t="s" r="J210" s="7">
-        <v>213</v>
+        <v>285</v>
       </c>
       <c r="K210" s="7"/>
       <c r="L210" s="7"/>
@@ -7904,14 +7904,14 @@
         <v>13</v>
       </c>
       <c r="B211" s="7">
-        <v>134</v>
+        <v>146</v>
       </c>
       <c t="s" r="C211" s="7">
         <v>14</v>
       </c>
       <c r="D211" s="7"/>
       <c t="s" r="E211" s="7">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="F211" s="7">
         <v>321</v>
@@ -7923,44 +7923,26 @@
         <v>24</v>
       </c>
       <c t="s" r="I211" s="7">
-        <v>166</v>
+        <v>28</v>
       </c>
       <c t="s" r="J211" s="7">
-        <v>108</v>
+        <v>31</v>
       </c>
       <c r="K211" s="7"/>
       <c r="L211" s="7"/>
       <c r="M211" s="7"/>
     </row>
     <row r="212" ht="14.25" customHeight="1">
-      <c t="s" r="A212" s="6">
-        <v>13</v>
-      </c>
-      <c r="B212" s="7">
-        <v>143</v>
-      </c>
-      <c t="s" r="C212" s="7">
-        <v>14</v>
-      </c>
+      <c r="A212" s="6"/>
+      <c r="B212" s="7"/>
+      <c r="C212" s="7"/>
       <c r="D212" s="7"/>
-      <c t="s" r="E212" s="7">
-        <v>278</v>
-      </c>
-      <c r="F212" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G212" s="8">
-        <v>24</v>
-      </c>
-      <c t="s" r="H212" s="8">
-        <v>21</v>
-      </c>
-      <c t="s" r="I212" s="7">
-        <v>280</v>
-      </c>
-      <c t="s" r="J212" s="7">
-        <v>281</v>
-      </c>
+      <c r="E212" s="7"/>
+      <c r="F212" s="7"/>
+      <c r="G212" s="8"/>
+      <c r="H212" s="8"/>
+      <c r="I212" s="7"/>
+      <c r="J212" s="7"/>
       <c r="K212" s="7"/>
       <c r="L212" s="7"/>
       <c r="M212" s="7"/>
@@ -7970,45 +7952,63 @@
         <v>13</v>
       </c>
       <c r="B213" s="7">
-        <v>146</v>
+        <v>461</v>
       </c>
       <c t="s" r="C213" s="7">
         <v>14</v>
       </c>
       <c r="D213" s="7"/>
       <c t="s" r="E213" s="7">
-        <v>278</v>
+        <v>286</v>
       </c>
       <c r="F213" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G213" s="8">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c t="s" r="H213" s="8">
-        <v>24</v>
+        <v>144</v>
       </c>
       <c t="s" r="I213" s="7">
-        <v>28</v>
+        <v>77</v>
       </c>
       <c t="s" r="J213" s="7">
-        <v>31</v>
+        <v>241</v>
       </c>
       <c r="K213" s="7"/>
       <c r="L213" s="7"/>
       <c r="M213" s="7"/>
     </row>
     <row r="214" ht="14.25" customHeight="1">
-      <c r="A214" s="6"/>
-      <c r="B214" s="7"/>
-      <c r="C214" s="7"/>
+      <c t="s" r="A214" s="6">
+        <v>13</v>
+      </c>
+      <c r="B214" s="7">
+        <v>462</v>
+      </c>
+      <c t="s" r="C214" s="7">
+        <v>14</v>
+      </c>
       <c r="D214" s="7"/>
-      <c r="E214" s="7"/>
-      <c r="F214" s="7"/>
-      <c r="G214" s="8"/>
-      <c r="H214" s="8"/>
-      <c r="I214" s="7"/>
-      <c r="J214" s="7"/>
+      <c t="s" r="E214" s="7">
+        <v>286</v>
+      </c>
+      <c r="F214" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G214" s="8">
+        <v>144</v>
+      </c>
+      <c t="s" r="H214" s="8">
+        <v>24</v>
+      </c>
+      <c t="s" r="I214" s="7">
+        <v>65</v>
+      </c>
+      <c t="s" r="J214" s="7">
+        <v>153</v>
+      </c>
       <c r="K214" s="7"/>
       <c r="L214" s="7"/>
       <c r="M214" s="7"/>
@@ -8018,14 +8018,14 @@
         <v>13</v>
       </c>
       <c r="B215" s="7">
-        <v>461</v>
+        <v>515</v>
       </c>
       <c t="s" r="C215" s="7">
         <v>14</v>
       </c>
       <c r="D215" s="7"/>
       <c t="s" r="E215" s="7">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="F215" s="7">
         <v>321</v>
@@ -8034,13 +8034,13 @@
         <v>24</v>
       </c>
       <c t="s" r="H215" s="8">
-        <v>144</v>
+        <v>94</v>
       </c>
       <c t="s" r="I215" s="7">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c t="s" r="J215" s="7">
-        <v>241</v>
+        <v>108</v>
       </c>
       <c r="K215" s="7"/>
       <c r="L215" s="7"/>
@@ -8051,29 +8051,29 @@
         <v>13</v>
       </c>
       <c r="B216" s="7">
-        <v>462</v>
+        <v>508</v>
       </c>
       <c t="s" r="C216" s="7">
         <v>14</v>
       </c>
       <c r="D216" s="7"/>
       <c t="s" r="E216" s="7">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="F216" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G216" s="8">
-        <v>144</v>
+        <v>94</v>
       </c>
       <c t="s" r="H216" s="8">
         <v>24</v>
       </c>
       <c t="s" r="I216" s="7">
-        <v>65</v>
+        <v>284</v>
       </c>
       <c t="s" r="J216" s="7">
-        <v>153</v>
+        <v>270</v>
       </c>
       <c r="K216" s="7"/>
       <c r="L216" s="7"/>
@@ -8084,14 +8084,14 @@
         <v>13</v>
       </c>
       <c r="B217" s="7">
-        <v>515</v>
+        <v>773</v>
       </c>
       <c t="s" r="C217" s="7">
         <v>14</v>
       </c>
       <c r="D217" s="7"/>
       <c t="s" r="E217" s="7">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="F217" s="7">
         <v>321</v>
@@ -8100,13 +8100,13 @@
         <v>24</v>
       </c>
       <c t="s" r="H217" s="8">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c t="s" r="I217" s="7">
-        <v>87</v>
+        <v>271</v>
       </c>
       <c t="s" r="J217" s="7">
-        <v>108</v>
+        <v>57</v>
       </c>
       <c r="K217" s="7"/>
       <c r="L217" s="7"/>
@@ -8117,63 +8117,45 @@
         <v>13</v>
       </c>
       <c r="B218" s="7">
-        <v>508</v>
+        <v>776</v>
       </c>
       <c t="s" r="C218" s="7">
         <v>14</v>
       </c>
       <c r="D218" s="7"/>
       <c t="s" r="E218" s="7">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="F218" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G218" s="8">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c t="s" r="H218" s="8">
         <v>24</v>
       </c>
       <c t="s" r="I218" s="7">
-        <v>280</v>
+        <v>263</v>
       </c>
       <c t="s" r="J218" s="7">
-        <v>283</v>
+        <v>272</v>
       </c>
       <c r="K218" s="7"/>
       <c r="L218" s="7"/>
       <c r="M218" s="7"/>
     </row>
     <row r="219" ht="14.25" customHeight="1">
-      <c t="s" r="A219" s="6">
-        <v>13</v>
-      </c>
-      <c r="B219" s="7">
-        <v>773</v>
-      </c>
-      <c t="s" r="C219" s="7">
-        <v>14</v>
-      </c>
+      <c r="A219" s="6"/>
+      <c r="B219" s="7"/>
+      <c r="C219" s="7"/>
       <c r="D219" s="7"/>
-      <c t="s" r="E219" s="7">
-        <v>282</v>
-      </c>
-      <c r="F219" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G219" s="8">
-        <v>24</v>
-      </c>
-      <c t="s" r="H219" s="8">
-        <v>76</v>
-      </c>
-      <c t="s" r="I219" s="7">
-        <v>284</v>
-      </c>
-      <c t="s" r="J219" s="7">
-        <v>57</v>
-      </c>
+      <c r="E219" s="7"/>
+      <c r="F219" s="7"/>
+      <c r="G219" s="8"/>
+      <c r="H219" s="8"/>
+      <c r="I219" s="7"/>
+      <c r="J219" s="7"/>
       <c r="K219" s="7"/>
       <c r="L219" s="7"/>
       <c r="M219" s="7"/>
@@ -8183,45 +8165,63 @@
         <v>13</v>
       </c>
       <c r="B220" s="7">
-        <v>776</v>
+        <v>270</v>
       </c>
       <c t="s" r="C220" s="7">
         <v>14</v>
       </c>
       <c r="D220" s="7"/>
       <c t="s" r="E220" s="7">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="F220" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G220" s="8">
-        <v>76</v>
+        <v>21</v>
       </c>
       <c t="s" r="H220" s="8">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c t="s" r="I220" s="7">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c t="s" r="J220" s="7">
-        <v>275</v>
+        <v>142</v>
       </c>
       <c r="K220" s="7"/>
       <c r="L220" s="7"/>
       <c r="M220" s="7"/>
     </row>
     <row r="221" ht="14.25" customHeight="1">
-      <c r="A221" s="6"/>
-      <c r="B221" s="7"/>
-      <c r="C221" s="7"/>
+      <c t="s" r="A221" s="6">
+        <v>13</v>
+      </c>
+      <c r="B221" s="7">
+        <v>271</v>
+      </c>
+      <c t="s" r="C221" s="7">
+        <v>14</v>
+      </c>
       <c r="D221" s="7"/>
-      <c r="E221" s="7"/>
-      <c r="F221" s="7"/>
-      <c r="G221" s="8"/>
-      <c r="H221" s="8"/>
-      <c r="I221" s="7"/>
-      <c r="J221" s="7"/>
+      <c t="s" r="E221" s="7">
+        <v>287</v>
+      </c>
+      <c r="F221" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G221" s="8">
+        <v>40</v>
+      </c>
+      <c t="s" r="H221" s="8">
+        <v>21</v>
+      </c>
+      <c t="s" r="I221" s="7">
+        <v>73</v>
+      </c>
+      <c t="s" r="J221" s="7">
+        <v>107</v>
+      </c>
       <c r="K221" s="7"/>
       <c r="L221" s="7"/>
       <c r="M221" s="7"/>
@@ -8231,14 +8231,14 @@
         <v>13</v>
       </c>
       <c r="B222" s="7">
-        <v>270</v>
+        <v>803</v>
       </c>
       <c t="s" r="C222" s="7">
         <v>14</v>
       </c>
       <c r="D222" s="7"/>
       <c t="s" r="E222" s="7">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="F222" s="7">
         <v>321</v>
@@ -8247,13 +8247,13 @@
         <v>21</v>
       </c>
       <c t="s" r="H222" s="8">
-        <v>40</v>
+        <v>244</v>
       </c>
       <c t="s" r="I222" s="7">
-        <v>260</v>
+        <v>288</v>
       </c>
       <c t="s" r="J222" s="7">
-        <v>142</v>
+        <v>289</v>
       </c>
       <c r="K222" s="7"/>
       <c r="L222" s="7"/>
@@ -8264,29 +8264,29 @@
         <v>13</v>
       </c>
       <c r="B223" s="7">
-        <v>271</v>
+        <v>804</v>
       </c>
       <c t="s" r="C223" s="7">
         <v>14</v>
       </c>
       <c r="D223" s="7"/>
       <c t="s" r="E223" s="7">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="F223" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G223" s="8">
-        <v>40</v>
+        <v>244</v>
       </c>
       <c t="s" r="H223" s="8">
         <v>21</v>
       </c>
       <c t="s" r="I223" s="7">
-        <v>73</v>
+        <v>188</v>
       </c>
       <c t="s" r="J223" s="7">
-        <v>107</v>
+        <v>89</v>
       </c>
       <c r="K223" s="7"/>
       <c r="L223" s="7"/>
@@ -8297,14 +8297,14 @@
         <v>13</v>
       </c>
       <c r="B224" s="7">
-        <v>803</v>
+        <v>310</v>
       </c>
       <c t="s" r="C224" s="7">
         <v>14</v>
       </c>
       <c r="D224" s="7"/>
       <c t="s" r="E224" s="7">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="F224" s="7">
         <v>321</v>
@@ -8313,13 +8313,13 @@
         <v>21</v>
       </c>
       <c t="s" r="H224" s="8">
-        <v>244</v>
+        <v>172</v>
       </c>
       <c t="s" r="I224" s="7">
-        <v>286</v>
+        <v>197</v>
       </c>
       <c t="s" r="J224" s="7">
-        <v>268</v>
+        <v>168</v>
       </c>
       <c r="K224" s="7"/>
       <c r="L224" s="7"/>
@@ -8330,29 +8330,29 @@
         <v>13</v>
       </c>
       <c r="B225" s="7">
-        <v>804</v>
+        <v>309</v>
       </c>
       <c t="s" r="C225" s="7">
         <v>14</v>
       </c>
       <c r="D225" s="7"/>
       <c t="s" r="E225" s="7">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="F225" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G225" s="8">
-        <v>244</v>
+        <v>172</v>
       </c>
       <c t="s" r="H225" s="8">
         <v>21</v>
       </c>
       <c t="s" r="I225" s="7">
-        <v>188</v>
+        <v>123</v>
       </c>
       <c t="s" r="J225" s="7">
-        <v>89</v>
+        <v>290</v>
       </c>
       <c r="K225" s="7"/>
       <c r="L225" s="7"/>
@@ -8363,14 +8363,14 @@
         <v>13</v>
       </c>
       <c r="B226" s="7">
-        <v>310</v>
+        <v>1282</v>
       </c>
       <c t="s" r="C226" s="7">
         <v>14</v>
       </c>
       <c r="D226" s="7"/>
       <c t="s" r="E226" s="7">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="F226" s="7">
         <v>321</v>
@@ -8379,13 +8379,13 @@
         <v>21</v>
       </c>
       <c t="s" r="H226" s="8">
-        <v>172</v>
+        <v>40</v>
       </c>
       <c t="s" r="I226" s="7">
-        <v>197</v>
+        <v>291</v>
       </c>
       <c t="s" r="J226" s="7">
-        <v>168</v>
+        <v>90</v>
       </c>
       <c r="K226" s="7"/>
       <c r="L226" s="7"/>
@@ -8396,63 +8396,45 @@
         <v>13</v>
       </c>
       <c r="B227" s="7">
-        <v>309</v>
+        <v>1283</v>
       </c>
       <c t="s" r="C227" s="7">
         <v>14</v>
       </c>
       <c r="D227" s="7"/>
       <c t="s" r="E227" s="7">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="F227" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G227" s="8">
-        <v>172</v>
+        <v>40</v>
       </c>
       <c t="s" r="H227" s="8">
         <v>21</v>
       </c>
       <c t="s" r="I227" s="7">
-        <v>123</v>
+        <v>292</v>
       </c>
       <c t="s" r="J227" s="7">
-        <v>287</v>
+        <v>293</v>
       </c>
       <c r="K227" s="7"/>
       <c r="L227" s="7"/>
       <c r="M227" s="7"/>
     </row>
     <row r="228" ht="14.25" customHeight="1">
-      <c t="s" r="A228" s="6">
-        <v>13</v>
-      </c>
-      <c r="B228" s="7">
-        <v>1282</v>
-      </c>
-      <c t="s" r="C228" s="7">
-        <v>14</v>
-      </c>
+      <c r="A228" s="6"/>
+      <c r="B228" s="7"/>
+      <c r="C228" s="7"/>
       <c r="D228" s="7"/>
-      <c t="s" r="E228" s="7">
-        <v>285</v>
-      </c>
-      <c r="F228" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G228" s="8">
-        <v>21</v>
-      </c>
-      <c t="s" r="H228" s="8">
-        <v>40</v>
-      </c>
-      <c t="s" r="I228" s="7">
-        <v>288</v>
-      </c>
-      <c t="s" r="J228" s="7">
-        <v>90</v>
-      </c>
+      <c r="E228" s="7"/>
+      <c r="F228" s="7"/>
+      <c r="G228" s="8"/>
+      <c r="H228" s="8"/>
+      <c r="I228" s="7"/>
+      <c r="J228" s="7"/>
       <c r="K228" s="7"/>
       <c r="L228" s="7"/>
       <c r="M228" s="7"/>
@@ -8462,45 +8444,63 @@
         <v>13</v>
       </c>
       <c r="B229" s="7">
-        <v>1283</v>
+        <v>1619</v>
       </c>
       <c t="s" r="C229" s="7">
         <v>14</v>
       </c>
       <c r="D229" s="7"/>
       <c t="s" r="E229" s="7">
-        <v>285</v>
+        <v>294</v>
       </c>
       <c r="F229" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G229" s="8">
-        <v>40</v>
+        <v>76</v>
       </c>
       <c t="s" r="H229" s="8">
         <v>21</v>
       </c>
       <c t="s" r="I229" s="7">
-        <v>289</v>
+        <v>220</v>
       </c>
       <c t="s" r="J229" s="7">
-        <v>290</v>
+        <v>141</v>
       </c>
       <c r="K229" s="7"/>
       <c r="L229" s="7"/>
       <c r="M229" s="7"/>
     </row>
     <row r="230" ht="15" customHeight="1">
-      <c r="A230" s="6"/>
-      <c r="B230" s="7"/>
-      <c r="C230" s="7"/>
+      <c t="s" r="A230" s="6">
+        <v>13</v>
+      </c>
+      <c r="B230" s="7">
+        <v>126</v>
+      </c>
+      <c t="s" r="C230" s="7">
+        <v>14</v>
+      </c>
       <c r="D230" s="7"/>
-      <c r="E230" s="7"/>
-      <c r="F230" s="7"/>
-      <c r="G230" s="8"/>
-      <c r="H230" s="8"/>
-      <c r="I230" s="7"/>
-      <c r="J230" s="7"/>
+      <c t="s" r="E230" s="7">
+        <v>294</v>
+      </c>
+      <c r="F230" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G230" s="8">
+        <v>21</v>
+      </c>
+      <c t="s" r="H230" s="8">
+        <v>24</v>
+      </c>
+      <c t="s" r="I230" s="7">
+        <v>19</v>
+      </c>
+      <c t="s" r="J230" s="7">
+        <v>242</v>
+      </c>
       <c r="K230" s="7"/>
       <c r="L230" s="7"/>
       <c r="M230" s="7"/>
@@ -8510,29 +8510,29 @@
         <v>13</v>
       </c>
       <c r="B231" s="7">
-        <v>1619</v>
+        <v>131</v>
       </c>
       <c t="s" r="C231" s="7">
         <v>14</v>
       </c>
       <c r="D231" s="7"/>
       <c t="s" r="E231" s="7">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="F231" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G231" s="8">
-        <v>76</v>
+        <v>24</v>
       </c>
       <c t="s" r="H231" s="8">
         <v>21</v>
       </c>
       <c t="s" r="I231" s="7">
-        <v>220</v>
+        <v>213</v>
       </c>
       <c t="s" r="J231" s="7">
-        <v>141</v>
+        <v>115</v>
       </c>
       <c r="K231" s="7"/>
       <c r="L231" s="7"/>
@@ -8543,14 +8543,14 @@
         <v>13</v>
       </c>
       <c r="B232" s="7">
-        <v>126</v>
+        <v>210</v>
       </c>
       <c t="s" r="C232" s="7">
         <v>14</v>
       </c>
       <c r="D232" s="7"/>
       <c t="s" r="E232" s="7">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="F232" s="7">
         <v>321</v>
@@ -8559,13 +8559,13 @@
         <v>21</v>
       </c>
       <c t="s" r="H232" s="8">
-        <v>24</v>
+        <v>100</v>
       </c>
       <c t="s" r="I232" s="7">
-        <v>19</v>
+        <v>99</v>
       </c>
       <c t="s" r="J232" s="7">
-        <v>242</v>
+        <v>295</v>
       </c>
       <c r="K232" s="7"/>
       <c r="L232" s="7"/>
@@ -8576,29 +8576,29 @@
         <v>13</v>
       </c>
       <c r="B233" s="7">
-        <v>131</v>
+        <v>211</v>
       </c>
       <c t="s" r="C233" s="7">
         <v>14</v>
       </c>
       <c r="D233" s="7"/>
       <c t="s" r="E233" s="7">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="F233" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G233" s="8">
-        <v>24</v>
+        <v>100</v>
       </c>
       <c t="s" r="H233" s="8">
         <v>21</v>
       </c>
       <c t="s" r="I233" s="7">
-        <v>213</v>
+        <v>70</v>
       </c>
       <c t="s" r="J233" s="7">
-        <v>115</v>
+        <v>256</v>
       </c>
       <c r="K233" s="7"/>
       <c r="L233" s="7"/>
@@ -8609,14 +8609,14 @@
         <v>13</v>
       </c>
       <c r="B234" s="7">
-        <v>210</v>
+        <v>3908</v>
       </c>
       <c t="s" r="C234" s="7">
         <v>14</v>
       </c>
       <c r="D234" s="7"/>
       <c t="s" r="E234" s="7">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="F234" s="7">
         <v>321</v>
@@ -8625,13 +8625,13 @@
         <v>21</v>
       </c>
       <c t="s" r="H234" s="8">
-        <v>100</v>
+        <v>279</v>
       </c>
       <c t="s" r="I234" s="7">
-        <v>99</v>
+        <v>296</v>
       </c>
       <c t="s" r="J234" s="7">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="K234" s="7"/>
       <c r="L234" s="7"/>
@@ -8639,114 +8639,114 @@
     </row>
     <row r="235" ht="15" customHeight="1">
       <c t="s" r="A235" s="6">
-        <v>13</v>
+        <v>48</v>
       </c>
       <c r="B235" s="7">
-        <v>211</v>
+        <v>3909</v>
       </c>
       <c t="s" r="C235" s="7">
         <v>14</v>
       </c>
       <c r="D235" s="7"/>
       <c t="s" r="E235" s="7">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="F235" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G235" s="8">
-        <v>100</v>
+        <v>279</v>
       </c>
       <c t="s" r="H235" s="8">
         <v>21</v>
       </c>
       <c t="s" r="I235" s="7">
-        <v>70</v>
+        <v>298</v>
       </c>
       <c t="s" r="J235" s="7">
-        <v>256</v>
+        <v>299</v>
       </c>
       <c r="K235" s="7"/>
       <c r="L235" s="7"/>
       <c r="M235" s="7"/>
     </row>
     <row r="236" ht="14.25" customHeight="1">
-      <c t="s" r="A236" s="6">
-        <v>13</v>
-      </c>
-      <c r="B236" s="7">
-        <v>3908</v>
-      </c>
-      <c t="s" r="C236" s="7">
-        <v>14</v>
-      </c>
+      <c r="A236" s="6"/>
+      <c r="B236" s="7"/>
+      <c r="C236" s="7"/>
       <c r="D236" s="7"/>
-      <c t="s" r="E236" s="7">
-        <v>291</v>
-      </c>
-      <c r="F236" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G236" s="8">
-        <v>21</v>
-      </c>
-      <c t="s" r="H236" s="8">
-        <v>293</v>
-      </c>
-      <c t="s" r="I236" s="7">
-        <v>294</v>
-      </c>
-      <c t="s" r="J236" s="7">
-        <v>295</v>
-      </c>
+      <c r="E236" s="7"/>
+      <c r="F236" s="7"/>
+      <c r="G236" s="8"/>
+      <c r="H236" s="8"/>
+      <c r="I236" s="7"/>
+      <c r="J236" s="7"/>
       <c r="K236" s="7"/>
       <c r="L236" s="7"/>
       <c r="M236" s="7"/>
     </row>
     <row r="237" ht="14.25" customHeight="1">
       <c t="s" r="A237" s="6">
-        <v>48</v>
+        <v>13</v>
       </c>
       <c r="B237" s="7">
-        <v>3909</v>
+        <v>491</v>
       </c>
       <c t="s" r="C237" s="7">
         <v>14</v>
       </c>
       <c r="D237" s="7"/>
       <c t="s" r="E237" s="7">
-        <v>291</v>
+        <v>300</v>
       </c>
       <c r="F237" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G237" s="8">
-        <v>293</v>
+        <v>24</v>
       </c>
       <c t="s" r="H237" s="8">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c t="s" r="I237" s="7">
-        <v>296</v>
+        <v>220</v>
       </c>
       <c t="s" r="J237" s="7">
-        <v>297</v>
+        <v>252</v>
       </c>
       <c r="K237" s="7"/>
       <c r="L237" s="7"/>
       <c r="M237" s="7"/>
     </row>
     <row r="238" ht="14.25" customHeight="1">
-      <c r="A238" s="6"/>
-      <c r="B238" s="7"/>
-      <c r="C238" s="7"/>
+      <c t="s" r="A238" s="6">
+        <v>13</v>
+      </c>
+      <c r="B238" s="7">
+        <v>492</v>
+      </c>
+      <c t="s" r="C238" s="7">
+        <v>14</v>
+      </c>
       <c r="D238" s="7"/>
-      <c r="E238" s="7"/>
-      <c r="F238" s="7"/>
-      <c r="G238" s="8"/>
-      <c r="H238" s="8"/>
-      <c r="I238" s="7"/>
-      <c r="J238" s="7"/>
+      <c t="s" r="E238" s="7">
+        <v>300</v>
+      </c>
+      <c r="F238" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G238" s="8">
+        <v>29</v>
+      </c>
+      <c t="s" r="H238" s="8">
+        <v>24</v>
+      </c>
+      <c t="s" r="I238" s="7">
+        <v>301</v>
+      </c>
+      <c t="s" r="J238" s="7">
+        <v>107</v>
+      </c>
       <c r="K238" s="7"/>
       <c r="L238" s="7"/>
       <c r="M238" s="7"/>
@@ -8756,14 +8756,14 @@
         <v>13</v>
       </c>
       <c r="B239" s="7">
-        <v>505</v>
+        <v>1491</v>
       </c>
       <c t="s" r="C239" s="7">
         <v>14</v>
       </c>
       <c r="D239" s="7"/>
       <c t="s" r="E239" s="7">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="F239" s="7">
         <v>321</v>
@@ -8772,13 +8772,13 @@
         <v>24</v>
       </c>
       <c t="s" r="H239" s="8">
-        <v>94</v>
+        <v>29</v>
       </c>
       <c t="s" r="I239" s="7">
-        <v>299</v>
+        <v>262</v>
       </c>
       <c t="s" r="J239" s="7">
-        <v>300</v>
+        <v>214</v>
       </c>
       <c r="K239" s="7"/>
       <c r="L239" s="7"/>
@@ -8789,29 +8789,29 @@
         <v>13</v>
       </c>
       <c r="B240" s="7">
-        <v>506</v>
+        <v>1492</v>
       </c>
       <c t="s" r="C240" s="7">
         <v>14</v>
       </c>
       <c r="D240" s="7"/>
       <c t="s" r="E240" s="7">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="F240" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G240" s="8">
-        <v>94</v>
+        <v>29</v>
       </c>
       <c t="s" r="H240" s="8">
         <v>24</v>
       </c>
       <c t="s" r="I240" s="7">
-        <v>186</v>
+        <v>289</v>
       </c>
       <c t="s" r="J240" s="7">
-        <v>214</v>
+        <v>302</v>
       </c>
       <c r="K240" s="7"/>
       <c r="L240" s="7"/>
@@ -8822,14 +8822,14 @@
         <v>13</v>
       </c>
       <c r="B241" s="7">
-        <v>433</v>
+        <v>423</v>
       </c>
       <c t="s" r="C241" s="7">
         <v>14</v>
       </c>
       <c r="D241" s="7"/>
       <c t="s" r="E241" s="7">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="F241" s="7">
         <v>321</v>
@@ -8838,13 +8838,13 @@
         <v>24</v>
       </c>
       <c t="s" r="H241" s="8">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c t="s" r="I241" s="7">
-        <v>188</v>
+        <v>79</v>
       </c>
       <c t="s" r="J241" s="7">
-        <v>283</v>
+        <v>99</v>
       </c>
       <c r="K241" s="7"/>
       <c r="L241" s="7"/>
@@ -8855,29 +8855,29 @@
         <v>13</v>
       </c>
       <c r="B242" s="7">
-        <v>434</v>
+        <v>424</v>
       </c>
       <c t="s" r="C242" s="7">
         <v>14</v>
       </c>
       <c r="D242" s="7"/>
       <c t="s" r="E242" s="7">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="F242" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G242" s="8">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c t="s" r="H242" s="8">
         <v>24</v>
       </c>
       <c t="s" r="I242" s="7">
-        <v>284</v>
+        <v>232</v>
       </c>
       <c t="s" r="J242" s="7">
-        <v>233</v>
+        <v>177</v>
       </c>
       <c r="K242" s="7"/>
       <c r="L242" s="7"/>
@@ -8888,14 +8888,14 @@
         <v>13</v>
       </c>
       <c r="B243" s="7">
-        <v>7526</v>
+        <v>409</v>
       </c>
       <c t="s" r="C243" s="7">
         <v>14</v>
       </c>
       <c r="D243" s="7"/>
       <c t="s" r="E243" s="7">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="F243" s="7">
         <v>321</v>
@@ -8904,13 +8904,13 @@
         <v>24</v>
       </c>
       <c t="s" r="H243" s="8">
-        <v>293</v>
+        <v>175</v>
       </c>
       <c t="s" r="I243" s="7">
-        <v>159</v>
+        <v>278</v>
       </c>
       <c t="s" r="J243" s="7">
-        <v>169</v>
+        <v>198</v>
       </c>
       <c r="K243" s="7"/>
       <c r="L243" s="7"/>
@@ -8918,32 +8918,32 @@
     </row>
     <row r="244" ht="14.25" customHeight="1">
       <c t="s" r="A244" s="6">
-        <v>48</v>
+        <v>13</v>
       </c>
       <c r="B244" s="7">
-        <v>7527</v>
+        <v>410</v>
       </c>
       <c t="s" r="C244" s="7">
         <v>14</v>
       </c>
       <c r="D244" s="7"/>
       <c t="s" r="E244" s="7">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="F244" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G244" s="8">
-        <v>293</v>
+        <v>175</v>
       </c>
       <c t="s" r="H244" s="8">
         <v>24</v>
       </c>
       <c t="s" r="I244" s="7">
-        <v>302</v>
+        <v>207</v>
       </c>
       <c t="s" r="J244" s="7">
-        <v>303</v>
+        <v>150</v>
       </c>
       <c r="K244" s="7"/>
       <c r="L244" s="7"/>
@@ -9237,7 +9237,7 @@
         <v>106</v>
       </c>
       <c t="s" r="J254" s="7">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="K254" s="7"/>
       <c r="L254" s="7"/>
@@ -9399,7 +9399,7 @@
         <v>21</v>
       </c>
       <c t="s" r="I259" s="7">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c t="s" r="J259" s="7">
         <v>228</v>
@@ -9741,7 +9741,7 @@
         <v>94</v>
       </c>
       <c t="s" r="I271" s="7">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c t="s" r="J271" s="7">
         <v>88</v>
@@ -10413,7 +10413,7 @@
         <v>183</v>
       </c>
       <c t="s" r="J294" s="7">
-        <v>299</v>
+        <v>267</v>
       </c>
       <c r="K294" s="7"/>
       <c r="L294" s="7"/>
@@ -10443,7 +10443,7 @@
         <v>175</v>
       </c>
       <c t="s" r="I295" s="7">
-        <v>300</v>
+        <v>268</v>
       </c>
       <c t="s" r="J295" s="7">
         <v>214</v>
@@ -10476,10 +10476,10 @@
         <v>24</v>
       </c>
       <c t="s" r="I296" s="7">
-        <v>268</v>
+        <v>289</v>
       </c>
       <c t="s" r="J296" s="7">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="K296" s="7"/>
       <c r="L296" s="7"/>
@@ -10755,7 +10755,7 @@
         <v>40</v>
       </c>
       <c t="s" r="I305" s="7">
-        <v>284</v>
+        <v>271</v>
       </c>
       <c t="s" r="J305" s="7">
         <v>335</v>
@@ -10872,7 +10872,7 @@
         <v>239</v>
       </c>
       <c t="s" r="J309" s="7">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="K309" s="7"/>
       <c r="L309" s="7"/>
@@ -10935,7 +10935,7 @@
         <v>24</v>
       </c>
       <c t="s" r="I311" s="7">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c t="s" r="J311" s="7">
         <v>42</v>
@@ -11049,13 +11049,13 @@
         <v>100</v>
       </c>
       <c t="s" r="I315" s="7">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c t="s" r="J315" s="7">
         <v>164</v>
       </c>
       <c t="s" r="K315" s="7">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="L315" s="7"/>
       <c t="s" r="M315" s="7">
@@ -11218,7 +11218,7 @@
         <v>94</v>
       </c>
       <c t="s" r="I320" s="7">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c t="s" r="J320" s="7">
         <v>191</v>
@@ -11296,7 +11296,7 @@
         <v>24</v>
       </c>
       <c t="s" r="H323" s="8">
-        <v>270</v>
+        <v>303</v>
       </c>
       <c t="s" r="I323" s="7">
         <v>138</v>
@@ -11326,7 +11326,7 @@
         <v>320</v>
       </c>
       <c t="s" r="G324" s="8">
-        <v>270</v>
+        <v>303</v>
       </c>
       <c t="s" r="H324" s="8">
         <v>24</v>
@@ -11398,7 +11398,7 @@
         <v>24</v>
       </c>
       <c t="s" r="I326" s="7">
-        <v>269</v>
+        <v>302</v>
       </c>
       <c t="s" r="J326" s="7">
         <v>255</v>
@@ -11434,7 +11434,7 @@
         <v>134</v>
       </c>
       <c t="s" r="J327" s="7">
-        <v>271</v>
+        <v>278</v>
       </c>
       <c r="K327" s="7"/>
       <c r="L327" s="7"/>
@@ -11728,7 +11728,7 @@
         <v>205</v>
       </c>
       <c t="s" r="J337" s="7">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="K337" s="7"/>
       <c r="L337" s="7"/>
@@ -11974,7 +11974,7 @@
         <v>44</v>
       </c>
       <c t="s" r="J345" s="7">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="K345" s="7"/>
       <c r="L345" s="7"/>
@@ -12049,7 +12049,7 @@
         <v>21</v>
       </c>
       <c t="s" r="H348" s="8">
-        <v>301</v>
+        <v>269</v>
       </c>
       <c t="s" r="I348" s="7">
         <v>140</v>
@@ -12079,7 +12079,7 @@
         <v>320</v>
       </c>
       <c t="s" r="G349" s="8">
-        <v>301</v>
+        <v>269</v>
       </c>
       <c t="s" r="H349" s="8">
         <v>21</v>
@@ -12247,7 +12247,7 @@
         <v>21</v>
       </c>
       <c t="s" r="H354" s="8">
-        <v>301</v>
+        <v>269</v>
       </c>
       <c t="s" r="I354" s="7">
         <v>255</v>
@@ -12277,7 +12277,7 @@
         <v>320</v>
       </c>
       <c t="s" r="G355" s="8">
-        <v>301</v>
+        <v>269</v>
       </c>
       <c t="s" r="H355" s="8">
         <v>21</v>
@@ -12394,7 +12394,7 @@
         <v>21</v>
       </c>
       <c t="s" r="H359" s="8">
-        <v>301</v>
+        <v>269</v>
       </c>
       <c t="s" r="I359" s="7">
         <v>229</v>
@@ -12424,7 +12424,7 @@
         <v>320</v>
       </c>
       <c t="s" r="G360" s="8">
-        <v>301</v>
+        <v>269</v>
       </c>
       <c t="s" r="H360" s="8">
         <v>21</v>
@@ -12499,7 +12499,7 @@
         <v>357</v>
       </c>
       <c t="s" r="J362" s="7">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="K362" s="7"/>
       <c r="L362" s="7"/>
@@ -12526,7 +12526,7 @@
         <v>21</v>
       </c>
       <c t="s" r="H363" s="8">
-        <v>270</v>
+        <v>303</v>
       </c>
       <c t="s" r="I363" s="7">
         <v>335</v>
@@ -12556,16 +12556,16 @@
         <v>320</v>
       </c>
       <c t="s" r="G364" s="8">
-        <v>270</v>
+        <v>303</v>
       </c>
       <c t="s" r="H364" s="8">
         <v>21</v>
       </c>
       <c t="s" r="I364" s="7">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c t="s" r="J364" s="7">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="K364" s="7"/>
       <c r="L364" s="7"/>
@@ -12712,7 +12712,7 @@
         <v>334</v>
       </c>
       <c t="s" r="J369" s="7">
-        <v>284</v>
+        <v>271</v>
       </c>
       <c r="K369" s="7"/>
       <c r="L369" s="7"/>
@@ -12778,7 +12778,7 @@
         <v>312</v>
       </c>
       <c t="s" r="J371" s="7">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="K371" s="7"/>
       <c r="L371" s="7"/>
@@ -12808,10 +12808,10 @@
         <v>21</v>
       </c>
       <c t="s" r="I372" s="7">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c t="s" r="J372" s="7">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="K372" s="7"/>
       <c r="L372" s="7"/>
@@ -12859,7 +12859,7 @@
         <v>363</v>
       </c>
       <c t="s" r="J374" s="7">
-        <v>267</v>
+        <v>301</v>
       </c>
       <c r="K374" s="7"/>
       <c r="L374" s="7"/>
@@ -13168,7 +13168,7 @@
         <v>21</v>
       </c>
       <c t="s" r="I384" s="7">
-        <v>284</v>
+        <v>271</v>
       </c>
       <c t="s" r="J384" s="7">
         <v>237</v>
@@ -13237,7 +13237,7 @@
         <v>265</v>
       </c>
       <c t="s" r="J386" s="7">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="K386" s="7"/>
       <c r="L386" s="7"/>
@@ -13315,7 +13315,7 @@
         <v>21</v>
       </c>
       <c t="s" r="I389" s="7">
-        <v>283</v>
+        <v>270</v>
       </c>
       <c t="s" r="J389" s="7">
         <v>110</v>
@@ -13561,7 +13561,7 @@
         <v>144</v>
       </c>
       <c t="s" r="I397" s="7">
-        <v>269</v>
+        <v>302</v>
       </c>
       <c t="s" r="J397" s="7">
         <v>99</v>
@@ -13744,7 +13744,7 @@
         <v>324</v>
       </c>
       <c t="s" r="J403" s="7">
-        <v>268</v>
+        <v>289</v>
       </c>
       <c r="K403" s="7"/>
       <c r="L403" s="7"/>
@@ -13777,7 +13777,7 @@
         <v>148</v>
       </c>
       <c t="s" r="J404" s="7">
-        <v>269</v>
+        <v>302</v>
       </c>
       <c r="K404" s="7"/>
       <c r="L404" s="7"/>
@@ -13804,7 +13804,7 @@
         <v>24</v>
       </c>
       <c t="s" r="H405" s="8">
-        <v>301</v>
+        <v>269</v>
       </c>
       <c t="s" r="I405" s="7">
         <v>81</v>
@@ -13834,7 +13834,7 @@
         <v>320</v>
       </c>
       <c t="s" r="G406" s="8">
-        <v>301</v>
+        <v>269</v>
       </c>
       <c t="s" r="H406" s="8">
         <v>24</v>
@@ -13888,7 +13888,7 @@
         <v>85</v>
       </c>
       <c t="s" r="I408" s="7">
-        <v>300</v>
+        <v>268</v>
       </c>
       <c t="s" r="J408" s="7">
         <v>108</v>
@@ -13921,7 +13921,7 @@
         <v>21</v>
       </c>
       <c t="s" r="I409" s="7">
-        <v>269</v>
+        <v>302</v>
       </c>
       <c t="s" r="J409" s="7">
         <v>215</v>
@@ -13987,7 +13987,7 @@
         <v>21</v>
       </c>
       <c t="s" r="I411" s="7">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c t="s" r="J411" s="7">
         <v>149</v>
@@ -14023,7 +14023,7 @@
         <v>375</v>
       </c>
       <c t="s" r="J412" s="7">
-        <v>302</v>
+        <v>280</v>
       </c>
       <c r="K412" s="7"/>
       <c r="L412" s="7"/>
@@ -14137,7 +14137,7 @@
         <v>53</v>
       </c>
       <c t="s" r="J416" s="7">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="K416" s="7"/>
       <c r="L416" s="7"/>
@@ -14170,7 +14170,7 @@
         <v>174</v>
       </c>
       <c t="s" r="J417" s="7">
-        <v>269</v>
+        <v>302</v>
       </c>
       <c r="K417" s="7"/>
       <c r="L417" s="7"/>
@@ -14200,7 +14200,7 @@
         <v>24</v>
       </c>
       <c t="s" r="I418" s="7">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c t="s" r="J418" s="7">
         <v>44</v>
@@ -14524,7 +14524,7 @@
         <v>21</v>
       </c>
       <c t="s" r="H429" s="8">
-        <v>270</v>
+        <v>303</v>
       </c>
       <c t="s" r="I429" s="7">
         <v>128</v>
@@ -14554,7 +14554,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G430" s="8">
-        <v>270</v>
+        <v>303</v>
       </c>
       <c t="s" r="H430" s="8">
         <v>21</v>
@@ -14629,7 +14629,7 @@
         <v>115</v>
       </c>
       <c t="s" r="J432" s="7">
-        <v>269</v>
+        <v>302</v>
       </c>
       <c r="K432" s="7"/>
       <c r="L432" s="7"/>
@@ -14704,7 +14704,7 @@
         <v>24</v>
       </c>
       <c t="s" r="H435" s="8">
-        <v>301</v>
+        <v>269</v>
       </c>
       <c t="s" r="I435" s="7">
         <v>363</v>
@@ -14734,7 +14734,7 @@
         <v>320</v>
       </c>
       <c t="s" r="G436" s="8">
-        <v>301</v>
+        <v>269</v>
       </c>
       <c t="s" r="H436" s="8">
         <v>24</v>
@@ -14905,7 +14905,7 @@
         <v>94</v>
       </c>
       <c t="s" r="I441" s="7">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c t="s" r="J441" s="7">
         <v>103</v>
@@ -14989,7 +14989,7 @@
         <v>253</v>
       </c>
       <c t="s" r="J444" s="7">
-        <v>269</v>
+        <v>302</v>
       </c>
       <c r="K444" s="7"/>
       <c r="L444" s="7"/>
@@ -15787,7 +15787,7 @@
         <v>401</v>
       </c>
       <c t="s" r="J472" s="7">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="K472" s="7"/>
       <c r="L472" s="7"/>

--- a/Data/FlightPlan/FPL_26AUG26.xlsx
+++ b/Data/FlightPlan/FPL_26AUG26.xlsx
@@ -317,12 +317,21 @@
     <t>12:05</t>
   </si>
   <si>
+    <t>12:25</t>
+  </si>
+  <si>
     <t>12:40</t>
   </si>
   <si>
     <t>14:00</t>
   </si>
   <si>
+    <t>14:50</t>
+  </si>
+  <si>
+    <t>16:10</t>
+  </si>
+  <si>
     <t>16:40</t>
   </si>
   <si>
@@ -428,9 +437,6 @@
     <t>10:35</t>
   </si>
   <si>
-    <t>12:25</t>
-  </si>
-  <si>
     <t>12:13</t>
   </si>
   <si>
@@ -488,6 +494,9 @@
     <t>13:15</t>
   </si>
   <si>
+    <t>13:01</t>
+  </si>
+  <si>
     <t>21:30</t>
   </si>
   <si>
@@ -578,7 +587,7 @@
     <t>12:20</t>
   </si>
   <si>
-    <t>11:59</t>
+    <t>12:28</t>
   </si>
   <si>
     <t>DLI</t>
@@ -626,6 +635,9 @@
     <t>13:50</t>
   </si>
   <si>
+    <t>13:27</t>
+  </si>
+  <si>
     <t>HKG</t>
   </si>
   <si>
@@ -773,9 +785,6 @@
     <t>09:32</t>
   </si>
   <si>
-    <t>14:50</t>
-  </si>
-  <si>
     <t>17:10</t>
   </si>
   <si>
@@ -914,6 +923,9 @@
     <t>10:29</t>
   </si>
   <si>
+    <t>12:37</t>
+  </si>
+  <si>
     <t>UIH</t>
   </si>
   <si>
@@ -1058,7 +1070,7 @@
     <t>10:21</t>
   </si>
   <si>
-    <t>16:10</t>
+    <t>12:29</t>
   </si>
   <si>
     <t>17:20</t>
@@ -1106,9 +1118,6 @@
     <t>VN-A649</t>
   </si>
   <si>
-    <t>12:29</t>
-  </si>
-  <si>
     <t>VN-A650</t>
   </si>
   <si>
@@ -1121,6 +1130,9 @@
     <t>VN-A651</t>
   </si>
   <si>
+    <t>13:02</t>
+  </si>
+  <si>
     <t>VN-A653</t>
   </si>
   <si>
@@ -1298,9 +1310,15 @@
     <t>VN-A672</t>
   </si>
   <si>
+    <t>12:31</t>
+  </si>
+  <si>
     <t>VN-A673</t>
   </si>
   <si>
+    <t>14:51</t>
+  </si>
+  <si>
     <t>00:50</t>
   </si>
   <si>
@@ -1328,6 +1346,9 @@
     <t>10:01</t>
   </si>
   <si>
+    <t>12:51</t>
+  </si>
+  <si>
     <t>VN-A683</t>
   </si>
   <si>
@@ -1421,9 +1442,6 @@
     <t>OVB</t>
   </si>
   <si>
-    <t>14:51</t>
-  </si>
-  <si>
     <t>SYD</t>
   </si>
   <si>
@@ -1463,7 +1481,7 @@
     <t>Total Record(s): 390</t>
   </si>
   <si>
-    <t xml:space="preserve">Generated on  Aug 26, 2026 11:07</t>
+    <t xml:space="preserve">Generated on  Aug 26, 2026 11:34</t>
   </si>
   <si>
     <t>Page 1 of 1</t>
@@ -3074,7 +3092,7 @@
       <c r="K41" s="7"/>
       <c r="L41" s="7"/>
       <c t="s" r="M41" s="7">
-        <v>26</v>
+        <v>102</v>
       </c>
     </row>
     <row r="42" ht="14.25" customHeight="1">
@@ -3101,10 +3119,10 @@
         <v>25</v>
       </c>
       <c t="s" r="I42" s="7">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c t="s" r="J42" s="7">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="K42" s="7"/>
       <c r="L42" s="7"/>
@@ -3139,9 +3157,13 @@
       <c t="s" r="J43" s="7">
         <v>45</v>
       </c>
-      <c r="K43" s="7"/>
+      <c t="s" r="K43" s="7">
+        <v>105</v>
+      </c>
       <c r="L43" s="7"/>
-      <c r="M43" s="7"/>
+      <c t="s" r="M43" s="7">
+        <v>106</v>
+      </c>
     </row>
     <row r="44" ht="14.25" customHeight="1">
       <c t="s" r="A44" s="6">
@@ -3167,7 +3189,7 @@
         <v>21</v>
       </c>
       <c t="s" r="I44" s="7">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c t="s" r="J44" s="7">
         <v>71</v>
@@ -3197,13 +3219,13 @@
         <v>21</v>
       </c>
       <c t="s" r="H45" s="8">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c t="s" r="I45" s="7">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c t="s" r="J45" s="7">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="K45" s="7"/>
       <c r="L45" s="7"/>
@@ -3227,16 +3249,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G46" s="8">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c t="s" r="H46" s="8">
         <v>21</v>
       </c>
       <c t="s" r="I46" s="7">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c t="s" r="J46" s="7">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="K46" s="7"/>
       <c r="L46" s="7"/>
@@ -3269,13 +3291,13 @@
       </c>
       <c r="D48" s="7"/>
       <c t="s" r="E48" s="7">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="F48" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G48" s="8">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c t="s" r="H48" s="8">
         <v>21</v>
@@ -3284,14 +3306,14 @@
         <v>67</v>
       </c>
       <c t="s" r="J48" s="7">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c t="s" r="K48" s="7">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="L48" s="7"/>
       <c t="s" r="M48" s="7">
-        <v>114</v>
+        <v>117</v>
       </c>
     </row>
     <row r="49" ht="14.25" customHeight="1">
@@ -3306,7 +3328,7 @@
       </c>
       <c r="D49" s="7"/>
       <c t="s" r="E49" s="7">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="F49" s="7">
         <v>321</v>
@@ -3315,10 +3337,10 @@
         <v>21</v>
       </c>
       <c t="s" r="H49" s="8">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c t="s" r="I49" s="7">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c t="s" r="J49" s="7">
         <v>50</v>
@@ -3339,22 +3361,22 @@
       </c>
       <c r="D50" s="7"/>
       <c t="s" r="E50" s="7">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="F50" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G50" s="8">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c t="s" r="H50" s="8">
         <v>21</v>
       </c>
       <c t="s" r="I50" s="7">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c t="s" r="J50" s="7">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="K50" s="7"/>
       <c r="L50" s="7"/>
@@ -3387,7 +3409,7 @@
       </c>
       <c r="D52" s="7"/>
       <c t="s" r="E52" s="7">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="F52" s="7">
         <v>321</v>
@@ -3396,13 +3418,13 @@
         <v>21</v>
       </c>
       <c t="s" r="H52" s="8">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c t="s" r="I52" s="7">
         <v>23</v>
       </c>
       <c t="s" r="J52" s="7">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="K52" s="7"/>
       <c r="L52" s="7"/>
@@ -3422,22 +3444,22 @@
       </c>
       <c r="D53" s="7"/>
       <c t="s" r="E53" s="7">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="F53" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G53" s="8">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c t="s" r="H53" s="8">
         <v>21</v>
       </c>
       <c t="s" r="I53" s="7">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c t="s" r="J53" s="7">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="K53" s="7"/>
       <c r="L53" s="7"/>
@@ -3455,7 +3477,7 @@
       </c>
       <c r="D54" s="7"/>
       <c t="s" r="E54" s="7">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="F54" s="7">
         <v>321</v>
@@ -3464,13 +3486,13 @@
         <v>21</v>
       </c>
       <c t="s" r="H54" s="8">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c t="s" r="I54" s="7">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c t="s" r="J54" s="7">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="K54" s="7"/>
       <c r="L54" s="7"/>
@@ -3488,22 +3510,22 @@
       </c>
       <c r="D55" s="7"/>
       <c t="s" r="E55" s="7">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="F55" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G55" s="8">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c t="s" r="H55" s="8">
         <v>21</v>
       </c>
       <c t="s" r="I55" s="7">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c t="s" r="J55" s="7">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="K55" s="7"/>
       <c r="L55" s="7"/>
@@ -3536,7 +3558,7 @@
       </c>
       <c r="D57" s="7"/>
       <c t="s" r="E57" s="7">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="F57" s="7">
         <v>321</v>
@@ -3548,7 +3570,7 @@
         <v>69</v>
       </c>
       <c t="s" r="I57" s="7">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c t="s" r="J57" s="7">
         <v>71</v>
@@ -3569,7 +3591,7 @@
       </c>
       <c r="D58" s="7"/>
       <c t="s" r="E58" s="7">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="F58" s="7">
         <v>321</v>
@@ -3584,7 +3606,7 @@
         <v>72</v>
       </c>
       <c t="s" r="J58" s="7">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="K58" s="7"/>
       <c r="L58" s="7"/>
@@ -3617,7 +3639,7 @@
       </c>
       <c r="D60" s="7"/>
       <c t="s" r="E60" s="7">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="F60" s="7">
         <v>321</v>
@@ -3626,18 +3648,18 @@
         <v>25</v>
       </c>
       <c t="s" r="H60" s="8">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c t="s" r="I60" s="7">
         <v>40</v>
       </c>
       <c t="s" r="J60" s="7">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="K60" s="7"/>
       <c r="L60" s="7"/>
       <c t="s" r="M60" s="7">
-        <v>130</v>
+        <v>133</v>
       </c>
     </row>
     <row r="61" ht="14.25" customHeight="1">
@@ -3652,22 +3674,22 @@
       </c>
       <c r="D61" s="7"/>
       <c t="s" r="E61" s="7">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="F61" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G61" s="8">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c t="s" r="H61" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I61" s="7">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c t="s" r="J61" s="7">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="K61" s="7"/>
       <c r="L61" s="7"/>
@@ -3685,7 +3707,7 @@
       </c>
       <c r="D62" s="7"/>
       <c t="s" r="E62" s="7">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="F62" s="7">
         <v>321</v>
@@ -3700,7 +3722,7 @@
         <v>94</v>
       </c>
       <c t="s" r="J62" s="7">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="K62" s="7"/>
       <c r="L62" s="7"/>
@@ -3718,7 +3740,7 @@
       </c>
       <c r="D63" s="7"/>
       <c t="s" r="E63" s="7">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="F63" s="7">
         <v>321</v>
@@ -3727,13 +3749,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H63" s="8">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c t="s" r="I63" s="7">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c t="s" r="J63" s="7">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="K63" s="7"/>
       <c r="L63" s="7"/>
@@ -3766,7 +3788,7 @@
       </c>
       <c r="D65" s="7"/>
       <c t="s" r="E65" s="7">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="F65" s="7">
         <v>321</v>
@@ -3786,7 +3808,7 @@
       <c r="K65" s="7"/>
       <c r="L65" s="7"/>
       <c t="s" r="M65" s="7">
-        <v>137</v>
+        <v>140</v>
       </c>
     </row>
     <row r="66" ht="14.25" customHeight="1">
@@ -3801,7 +3823,7 @@
       </c>
       <c r="D66" s="7"/>
       <c t="s" r="E66" s="7">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="F66" s="7">
         <v>321</v>
@@ -3813,15 +3835,15 @@
         <v>43</v>
       </c>
       <c t="s" r="I66" s="7">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c t="s" r="J66" s="7">
-        <v>139</v>
+        <v>102</v>
       </c>
       <c r="K66" s="7"/>
       <c r="L66" s="7"/>
       <c t="s" r="M66" s="7">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="67" ht="14.25" customHeight="1">
@@ -3836,7 +3858,7 @@
       </c>
       <c r="D67" s="7"/>
       <c t="s" r="E67" s="7">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="F67" s="7">
         <v>321</v>
@@ -3848,10 +3870,10 @@
         <v>77</v>
       </c>
       <c t="s" r="I67" s="7">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c t="s" r="J67" s="7">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="K67" s="7"/>
       <c r="L67" s="7"/>
@@ -3869,7 +3891,7 @@
       </c>
       <c r="D68" s="7"/>
       <c t="s" r="E68" s="7">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="F68" s="7">
         <v>321</v>
@@ -3884,7 +3906,7 @@
         <v>83</v>
       </c>
       <c t="s" r="J68" s="7">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="K68" s="7"/>
       <c r="L68" s="7"/>
@@ -3902,7 +3924,7 @@
       </c>
       <c r="D69" s="7"/>
       <c t="s" r="E69" s="7">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="F69" s="7">
         <v>321</v>
@@ -3911,13 +3933,13 @@
         <v>25</v>
       </c>
       <c t="s" r="H69" s="8">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c t="s" r="I69" s="7">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c t="s" r="J69" s="7">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="K69" s="7"/>
       <c r="L69" s="7"/>
@@ -3950,7 +3972,7 @@
       </c>
       <c r="D71" s="7"/>
       <c t="s" r="E71" s="7">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="F71" s="7">
         <v>321</v>
@@ -3962,15 +3984,15 @@
         <v>21</v>
       </c>
       <c t="s" r="I71" s="7">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c t="s" r="J71" s="7">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="K71" s="7"/>
       <c r="L71" s="7"/>
       <c t="s" r="M71" s="7">
-        <v>149</v>
+        <v>151</v>
       </c>
     </row>
     <row r="72" ht="14.25" customHeight="1">
@@ -3985,7 +4007,7 @@
       </c>
       <c r="D72" s="7"/>
       <c t="s" r="E72" s="7">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="F72" s="7">
         <v>321</v>
@@ -3997,15 +4019,15 @@
         <v>99</v>
       </c>
       <c t="s" r="I72" s="7">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c t="s" r="J72" s="7">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="K72" s="7"/>
       <c r="L72" s="7"/>
       <c t="s" r="M72" s="7">
-        <v>152</v>
+        <v>154</v>
       </c>
     </row>
     <row r="73" ht="14.25" customHeight="1">
@@ -4020,7 +4042,7 @@
       </c>
       <c r="D73" s="7"/>
       <c t="s" r="E73" s="7">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="F73" s="7">
         <v>321</v>
@@ -4029,18 +4051,18 @@
         <v>99</v>
       </c>
       <c t="s" r="H73" s="8">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c t="s" r="I73" s="7">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c t="s" r="J73" s="7">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="K73" s="7"/>
       <c r="L73" s="7"/>
       <c t="s" r="M73" s="7">
-        <v>156</v>
+        <v>158</v>
       </c>
     </row>
     <row r="74" ht="14.25" customHeight="1">
@@ -4055,26 +4077,28 @@
       </c>
       <c r="D74" s="7"/>
       <c t="s" r="E74" s="7">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="F74" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G74" s="8">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c t="s" r="H74" s="8">
         <v>99</v>
       </c>
       <c t="s" r="I74" s="7">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c t="s" r="J74" s="7">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="K74" s="7"/>
       <c r="L74" s="7"/>
-      <c r="M74" s="7"/>
+      <c t="s" r="M74" s="7">
+        <v>161</v>
+      </c>
     </row>
     <row r="75" ht="15" customHeight="1">
       <c t="s" r="A75" s="6">
@@ -4088,7 +4112,7 @@
       </c>
       <c r="D75" s="7"/>
       <c t="s" r="E75" s="7">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="F75" s="7">
         <v>321</v>
@@ -4121,7 +4145,7 @@
       </c>
       <c r="D76" s="7"/>
       <c t="s" r="E76" s="7">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="F76" s="7">
         <v>321</v>
@@ -4133,10 +4157,10 @@
         <v>99</v>
       </c>
       <c t="s" r="I76" s="7">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c t="s" r="J76" s="7">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="K76" s="7"/>
       <c r="L76" s="7"/>
@@ -4154,7 +4178,7 @@
       </c>
       <c r="D77" s="7"/>
       <c t="s" r="E77" s="7">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="F77" s="7">
         <v>321</v>
@@ -4166,10 +4190,10 @@
         <v>25</v>
       </c>
       <c t="s" r="I77" s="7">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c t="s" r="J77" s="7">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="K77" s="7"/>
       <c r="L77" s="7"/>
@@ -4187,7 +4211,7 @@
       </c>
       <c r="D78" s="7"/>
       <c t="s" r="E78" s="7">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="F78" s="7">
         <v>321</v>
@@ -4199,10 +4223,10 @@
         <v>21</v>
       </c>
       <c t="s" r="I78" s="7">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c t="s" r="J78" s="7">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="K78" s="7"/>
       <c r="L78" s="7"/>
@@ -4235,7 +4259,7 @@
       </c>
       <c r="D80" s="7"/>
       <c t="s" r="E80" s="7">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="F80" s="7">
         <v>321</v>
@@ -4247,15 +4271,15 @@
         <v>17</v>
       </c>
       <c t="s" r="I80" s="7">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c t="s" r="J80" s="7">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="K80" s="7"/>
       <c r="L80" s="7"/>
       <c t="s" r="M80" s="7">
-        <v>163</v>
+        <v>166</v>
       </c>
     </row>
     <row r="81" ht="14.25" customHeight="1">
@@ -4270,7 +4294,7 @@
       </c>
       <c r="D81" s="7"/>
       <c t="s" r="E81" s="7">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="F81" s="7">
         <v>321</v>
@@ -4285,12 +4309,12 @@
         <v>56</v>
       </c>
       <c t="s" r="J81" s="7">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="K81" s="7"/>
       <c r="L81" s="7"/>
       <c t="s" r="M81" s="7">
-        <v>164</v>
+        <v>167</v>
       </c>
     </row>
     <row r="82" ht="14.25" customHeight="1">
@@ -4305,7 +4329,7 @@
       </c>
       <c r="D82" s="7"/>
       <c t="s" r="E82" s="7">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="F82" s="7">
         <v>321</v>
@@ -4317,10 +4341,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I82" s="7">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c t="s" r="J82" s="7">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="K82" s="7"/>
       <c r="L82" s="7"/>
@@ -4338,7 +4362,7 @@
       </c>
       <c r="D83" s="7"/>
       <c t="s" r="E83" s="7">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="F83" s="7">
         <v>321</v>
@@ -4350,10 +4374,10 @@
         <v>25</v>
       </c>
       <c t="s" r="I83" s="7">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c t="s" r="J83" s="7">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="K83" s="7"/>
       <c r="L83" s="7"/>
@@ -4371,7 +4395,7 @@
       </c>
       <c r="D84" s="7"/>
       <c t="s" r="E84" s="7">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="F84" s="7">
         <v>321</v>
@@ -4383,10 +4407,10 @@
         <v>21</v>
       </c>
       <c t="s" r="I84" s="7">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c t="s" r="J84" s="7">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="K84" s="7"/>
       <c r="L84" s="7"/>
@@ -4404,7 +4428,7 @@
       </c>
       <c r="D85" s="7"/>
       <c t="s" r="E85" s="7">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="F85" s="7">
         <v>321</v>
@@ -4416,10 +4440,10 @@
         <v>25</v>
       </c>
       <c t="s" r="I85" s="7">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c t="s" r="J85" s="7">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="K85" s="7"/>
       <c r="L85" s="7"/>
@@ -4437,7 +4461,7 @@
       </c>
       <c r="D86" s="7"/>
       <c t="s" r="E86" s="7">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="F86" s="7">
         <v>321</v>
@@ -4452,7 +4476,7 @@
         <v>63</v>
       </c>
       <c t="s" r="J86" s="7">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="K86" s="7"/>
       <c r="L86" s="7"/>
@@ -4485,7 +4509,7 @@
       </c>
       <c r="D88" s="7"/>
       <c t="s" r="E88" s="7">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="F88" s="7">
         <v>321</v>
@@ -4494,18 +4518,18 @@
         <v>21</v>
       </c>
       <c t="s" r="H88" s="8">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c t="s" r="I88" s="7">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c t="s" r="J88" s="7">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="K88" s="7"/>
       <c r="L88" s="7"/>
       <c t="s" r="M88" s="7">
-        <v>176</v>
+        <v>179</v>
       </c>
     </row>
     <row r="89" ht="14.25" customHeight="1">
@@ -4520,27 +4544,27 @@
       </c>
       <c r="D89" s="7"/>
       <c t="s" r="E89" s="7">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="F89" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G89" s="8">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c t="s" r="H89" s="8">
         <v>21</v>
       </c>
       <c t="s" r="I89" s="7">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c t="s" r="J89" s="7">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="K89" s="7"/>
       <c r="L89" s="7"/>
       <c t="s" r="M89" s="7">
-        <v>178</v>
+        <v>181</v>
       </c>
     </row>
     <row r="90" ht="15" customHeight="1">
@@ -4555,7 +4579,7 @@
       </c>
       <c r="D90" s="7"/>
       <c t="s" r="E90" s="7">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="F90" s="7">
         <v>321</v>
@@ -4570,7 +4594,7 @@
         <v>70</v>
       </c>
       <c t="s" r="J90" s="7">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="K90" s="7"/>
       <c r="L90" s="7"/>
@@ -4588,7 +4612,7 @@
       </c>
       <c r="D91" s="7"/>
       <c t="s" r="E91" s="7">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="F91" s="7">
         <v>321</v>
@@ -4600,10 +4624,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I91" s="7">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c t="s" r="J91" s="7">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="K91" s="7"/>
       <c r="L91" s="7"/>
@@ -4636,7 +4660,7 @@
       </c>
       <c r="D93" s="7"/>
       <c t="s" r="E93" s="7">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="F93" s="7">
         <v>321</v>
@@ -4648,10 +4672,10 @@
         <v>99</v>
       </c>
       <c t="s" r="I93" s="7">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c t="s" r="J93" s="7">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="K93" s="7"/>
       <c r="L93" s="7"/>
@@ -4671,7 +4695,7 @@
       </c>
       <c r="D94" s="7"/>
       <c t="s" r="E94" s="7">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="F94" s="7">
         <v>321</v>
@@ -4683,15 +4707,15 @@
         <v>25</v>
       </c>
       <c t="s" r="I94" s="7">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c t="s" r="J94" s="7">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="K94" s="7"/>
       <c r="L94" s="7"/>
       <c t="s" r="M94" s="7">
-        <v>184</v>
+        <v>187</v>
       </c>
     </row>
     <row r="95" ht="15" customHeight="1">
@@ -4706,7 +4730,7 @@
       </c>
       <c r="D95" s="7"/>
       <c t="s" r="E95" s="7">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="F95" s="7">
         <v>321</v>
@@ -4715,18 +4739,18 @@
         <v>25</v>
       </c>
       <c t="s" r="H95" s="8">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c t="s" r="I95" s="7">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c t="s" r="J95" s="7">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="K95" s="7"/>
       <c r="L95" s="7"/>
       <c t="s" r="M95" s="7">
-        <v>186</v>
+        <v>189</v>
       </c>
     </row>
     <row r="96" ht="14.25" customHeight="1">
@@ -4741,27 +4765,27 @@
       </c>
       <c r="D96" s="7"/>
       <c t="s" r="E96" s="7">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="F96" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G96" s="8">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c t="s" r="H96" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I96" s="7">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c t="s" r="J96" s="7">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="K96" s="7"/>
       <c r="L96" s="7"/>
       <c t="s" r="M96" s="7">
-        <v>189</v>
+        <v>192</v>
       </c>
     </row>
     <row r="97" ht="14.25" customHeight="1">
@@ -4776,7 +4800,7 @@
       </c>
       <c r="D97" s="7"/>
       <c t="s" r="E97" s="7">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="F97" s="7">
         <v>321</v>
@@ -4785,10 +4809,10 @@
         <v>25</v>
       </c>
       <c t="s" r="H97" s="8">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c t="s" r="I97" s="7">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c t="s" r="J97" s="7">
         <v>81</v>
@@ -4809,22 +4833,22 @@
       </c>
       <c r="D98" s="7"/>
       <c t="s" r="E98" s="7">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="F98" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G98" s="8">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c t="s" r="H98" s="8">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c t="s" r="I98" s="7">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c t="s" r="J98" s="7">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="K98" s="7"/>
       <c r="L98" s="7"/>
@@ -4842,19 +4866,19 @@
       </c>
       <c r="D99" s="7"/>
       <c t="s" r="E99" s="7">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="F99" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G99" s="8">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c t="s" r="H99" s="8">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c t="s" r="I99" s="7">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c t="s" r="J99" s="7">
         <v>34</v>
@@ -4875,22 +4899,22 @@
       </c>
       <c r="D100" s="7"/>
       <c t="s" r="E100" s="7">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="F100" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G100" s="8">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c t="s" r="H100" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I100" s="7">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c t="s" r="J100" s="7">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="K100" s="7"/>
       <c r="L100" s="7"/>
@@ -4923,7 +4947,7 @@
       </c>
       <c r="D102" s="7"/>
       <c t="s" r="E102" s="7">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="F102" s="7">
         <v>321</v>
@@ -4935,15 +4959,15 @@
         <v>21</v>
       </c>
       <c t="s" r="I102" s="7">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c t="s" r="J102" s="7">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="K102" s="7"/>
       <c r="L102" s="7"/>
       <c t="s" r="M102" s="7">
-        <v>195</v>
+        <v>198</v>
       </c>
     </row>
     <row r="103" ht="14.25" customHeight="1">
@@ -4958,7 +4982,7 @@
       </c>
       <c r="D103" s="7"/>
       <c t="s" r="E103" s="7">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="F103" s="7">
         <v>321</v>
@@ -4967,7 +4991,7 @@
         <v>21</v>
       </c>
       <c t="s" r="H103" s="8">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c t="s" r="I103" s="7">
         <v>46</v>
@@ -4991,22 +5015,22 @@
       </c>
       <c r="D104" s="7"/>
       <c t="s" r="E104" s="7">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="F104" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G104" s="8">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c t="s" r="H104" s="8">
         <v>21</v>
       </c>
       <c t="s" r="I104" s="7">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c t="s" r="J104" s="7">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="K104" s="7"/>
       <c r="L104" s="7"/>
@@ -5024,7 +5048,7 @@
       </c>
       <c r="D105" s="7"/>
       <c t="s" r="E105" s="7">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="F105" s="7">
         <v>321</v>
@@ -5033,13 +5057,13 @@
         <v>21</v>
       </c>
       <c t="s" r="H105" s="8">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c t="s" r="I105" s="7">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c t="s" r="J105" s="7">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="K105" s="7"/>
       <c r="L105" s="7"/>
@@ -5072,7 +5096,7 @@
       </c>
       <c r="D107" s="7"/>
       <c t="s" r="E107" s="7">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="F107" s="7">
         <v>321</v>
@@ -5081,18 +5105,18 @@
         <v>21</v>
       </c>
       <c t="s" r="H107" s="8">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c t="s" r="I107" s="7">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c t="s" r="J107" s="7">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="K107" s="7"/>
       <c r="L107" s="7"/>
       <c t="s" r="M107" s="7">
-        <v>138</v>
+        <v>141</v>
       </c>
     </row>
     <row r="108" ht="14.25" customHeight="1">
@@ -5107,26 +5131,28 @@
       </c>
       <c r="D108" s="7"/>
       <c t="s" r="E108" s="7">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="F108" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G108" s="8">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c t="s" r="H108" s="8">
         <v>21</v>
       </c>
       <c t="s" r="I108" s="7">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c t="s" r="J108" s="7">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="K108" s="7"/>
       <c r="L108" s="7"/>
-      <c r="M108" s="7"/>
+      <c t="s" r="M108" s="7">
+        <v>208</v>
+      </c>
     </row>
     <row r="109" ht="14.25" customHeight="1">
       <c t="s" r="A109" s="6">
@@ -5140,7 +5166,7 @@
       </c>
       <c r="D109" s="7"/>
       <c t="s" r="E109" s="7">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="F109" s="7">
         <v>321</v>
@@ -5149,10 +5175,10 @@
         <v>21</v>
       </c>
       <c t="s" r="H109" s="8">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c t="s" r="I109" s="7">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c t="s" r="J109" s="7">
         <v>61</v>
@@ -5173,22 +5199,22 @@
       </c>
       <c r="D110" s="7"/>
       <c t="s" r="E110" s="7">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="F110" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G110" s="8">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c t="s" r="H110" s="8">
         <v>21</v>
       </c>
       <c t="s" r="I110" s="7">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c t="s" r="J110" s="7">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="K110" s="7"/>
       <c r="L110" s="7"/>
@@ -5221,7 +5247,7 @@
       </c>
       <c r="D112" s="7"/>
       <c t="s" r="E112" s="7">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="F112" s="7">
         <v>321</v>
@@ -5233,15 +5259,15 @@
         <v>17</v>
       </c>
       <c t="s" r="I112" s="7">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c t="s" r="J112" s="7">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="K112" s="7"/>
       <c r="L112" s="7"/>
       <c t="s" r="M112" s="7">
-        <v>210</v>
+        <v>214</v>
       </c>
     </row>
     <row r="113" ht="14.25" customHeight="1">
@@ -5256,7 +5282,7 @@
       </c>
       <c r="D113" s="7"/>
       <c t="s" r="E113" s="7">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="F113" s="7">
         <v>321</v>
@@ -5268,10 +5294,10 @@
         <v>25</v>
       </c>
       <c t="s" r="I113" s="7">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c t="s" r="J113" s="7">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="K113" s="7"/>
       <c r="L113" s="7"/>
@@ -5289,7 +5315,7 @@
       </c>
       <c r="D114" s="7"/>
       <c t="s" r="E114" s="7">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="F114" s="7">
         <v>321</v>
@@ -5298,13 +5324,13 @@
         <v>25</v>
       </c>
       <c t="s" r="H114" s="8">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c t="s" r="I114" s="7">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c t="s" r="J114" s="7">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="K114" s="7"/>
       <c r="L114" s="7"/>
@@ -5322,22 +5348,22 @@
       </c>
       <c r="D115" s="7"/>
       <c t="s" r="E115" s="7">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="F115" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G115" s="8">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c t="s" r="H115" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I115" s="7">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c t="s" r="J115" s="7">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="K115" s="7"/>
       <c r="L115" s="7"/>
@@ -5355,7 +5381,7 @@
       </c>
       <c r="D116" s="7"/>
       <c t="s" r="E116" s="7">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="F116" s="7">
         <v>321</v>
@@ -5370,7 +5396,7 @@
         <v>32</v>
       </c>
       <c t="s" r="J116" s="7">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="K116" s="7"/>
       <c r="L116" s="7"/>
@@ -5403,7 +5429,7 @@
       </c>
       <c r="D118" s="7"/>
       <c t="s" r="E118" s="7">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="F118" s="7">
         <v>321</v>
@@ -5415,15 +5441,15 @@
         <v>66</v>
       </c>
       <c t="s" r="I118" s="7">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c t="s" r="J118" s="7">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="K118" s="7"/>
       <c r="L118" s="7"/>
       <c t="s" r="M118" s="7">
-        <v>217</v>
+        <v>221</v>
       </c>
     </row>
     <row r="119" ht="14.25" customHeight="1">
@@ -5438,7 +5464,7 @@
       </c>
       <c r="D119" s="7"/>
       <c t="s" r="E119" s="7">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="F119" s="7">
         <v>321</v>
@@ -5450,7 +5476,7 @@
         <v>25</v>
       </c>
       <c t="s" r="I119" s="7">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c t="s" r="J119" s="7">
         <v>94</v>
@@ -5486,27 +5512,27 @@
       </c>
       <c r="D121" s="7"/>
       <c t="s" r="E121" s="7">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="F121" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G121" s="8">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c t="s" r="H121" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I121" s="7">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c t="s" r="J121" s="7">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="K121" s="7"/>
       <c r="L121" s="7"/>
       <c t="s" r="M121" s="7">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="122" ht="14.25" customHeight="1">
@@ -5521,7 +5547,7 @@
       </c>
       <c r="D122" s="7"/>
       <c t="s" r="E122" s="7">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="F122" s="7">
         <v>321</v>
@@ -5530,13 +5556,13 @@
         <v>25</v>
       </c>
       <c t="s" r="H122" s="8">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c t="s" r="I122" s="7">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c t="s" r="J122" s="7">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="K122" s="7"/>
       <c r="L122" s="7"/>
@@ -5554,13 +5580,13 @@
       </c>
       <c r="D123" s="7"/>
       <c t="s" r="E123" s="7">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="F123" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G123" s="8">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c t="s" r="H123" s="8">
         <v>25</v>
@@ -5569,7 +5595,7 @@
         <v>71</v>
       </c>
       <c t="s" r="J123" s="7">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="K123" s="7"/>
       <c r="L123" s="7"/>
@@ -5587,7 +5613,7 @@
       </c>
       <c r="D124" s="7"/>
       <c t="s" r="E124" s="7">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="F124" s="7">
         <v>321</v>
@@ -5602,7 +5628,7 @@
         <v>34</v>
       </c>
       <c t="s" r="J124" s="7">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="K124" s="7"/>
       <c r="L124" s="7"/>
@@ -5620,7 +5646,7 @@
       </c>
       <c r="D125" s="7"/>
       <c t="s" r="E125" s="7">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="F125" s="7">
         <v>321</v>
@@ -5632,10 +5658,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I125" s="7">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c t="s" r="J125" s="7">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="K125" s="7"/>
       <c r="L125" s="7"/>
@@ -5668,27 +5694,27 @@
       </c>
       <c r="D127" s="7"/>
       <c t="s" r="E127" s="7">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="F127" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G127" s="8">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c t="s" r="H127" s="8">
         <v>77</v>
       </c>
       <c t="s" r="I127" s="7">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c t="s" r="J127" s="7">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="K127" s="7"/>
       <c r="L127" s="7"/>
       <c t="s" r="M127" s="7">
-        <v>226</v>
+        <v>230</v>
       </c>
     </row>
     <row r="128" ht="14.25" customHeight="1">
@@ -5703,7 +5729,7 @@
       </c>
       <c r="D128" s="7"/>
       <c t="s" r="E128" s="7">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="F128" s="7">
         <v>321</v>
@@ -5712,13 +5738,13 @@
         <v>77</v>
       </c>
       <c t="s" r="H128" s="8">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c t="s" r="I128" s="7">
         <v>45</v>
       </c>
       <c t="s" r="J128" s="7">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="K128" s="7"/>
       <c r="L128" s="7"/>
@@ -5736,22 +5762,22 @@
       </c>
       <c r="D129" s="7"/>
       <c t="s" r="E129" s="7">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="F129" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G129" s="8">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c t="s" r="H129" s="8">
         <v>77</v>
       </c>
       <c t="s" r="I129" s="7">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c t="s" r="J129" s="7">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="K129" s="7"/>
       <c r="L129" s="7"/>
@@ -5769,7 +5795,7 @@
       </c>
       <c r="D130" s="7"/>
       <c t="s" r="E130" s="7">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="F130" s="7">
         <v>321</v>
@@ -5778,13 +5804,13 @@
         <v>77</v>
       </c>
       <c t="s" r="H130" s="8">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c t="s" r="I130" s="7">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c t="s" r="J130" s="7">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="K130" s="7"/>
       <c r="L130" s="7"/>
@@ -5817,7 +5843,7 @@
       </c>
       <c r="D132" s="7"/>
       <c t="s" r="E132" s="7">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="F132" s="7">
         <v>321</v>
@@ -5829,15 +5855,15 @@
         <v>99</v>
       </c>
       <c t="s" r="I132" s="7">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c t="s" r="J132" s="7">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="K132" s="7"/>
       <c r="L132" s="7"/>
       <c t="s" r="M132" s="7">
-        <v>235</v>
+        <v>239</v>
       </c>
     </row>
     <row r="133" ht="14.25" customHeight="1">
@@ -5852,7 +5878,7 @@
       </c>
       <c r="D133" s="7"/>
       <c t="s" r="E133" s="7">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="F133" s="7">
         <v>321</v>
@@ -5864,10 +5890,10 @@
         <v>21</v>
       </c>
       <c t="s" r="I133" s="7">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c t="s" r="J133" s="7">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="K133" s="7"/>
       <c r="L133" s="7"/>
@@ -5885,7 +5911,7 @@
       </c>
       <c r="D134" s="7"/>
       <c t="s" r="E134" s="7">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="F134" s="7">
         <v>321</v>
@@ -5900,7 +5926,7 @@
         <v>68</v>
       </c>
       <c t="s" r="J134" s="7">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="K134" s="7"/>
       <c r="L134" s="7"/>
@@ -5918,7 +5944,7 @@
       </c>
       <c r="D135" s="7"/>
       <c t="s" r="E135" s="7">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="F135" s="7">
         <v>321</v>
@@ -5930,7 +5956,7 @@
         <v>21</v>
       </c>
       <c t="s" r="I135" s="7">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c t="s" r="J135" s="7">
         <v>31</v>
@@ -5951,7 +5977,7 @@
       </c>
       <c r="D136" s="7"/>
       <c t="s" r="E136" s="7">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="F136" s="7">
         <v>321</v>
@@ -5960,10 +5986,10 @@
         <v>21</v>
       </c>
       <c t="s" r="H136" s="8">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c t="s" r="I136" s="7">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c t="s" r="J136" s="7">
         <v>84</v>
@@ -5984,22 +6010,22 @@
       </c>
       <c r="D137" s="7"/>
       <c t="s" r="E137" s="7">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="F137" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G137" s="8">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c t="s" r="H137" s="8">
         <v>21</v>
       </c>
       <c t="s" r="I137" s="7">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c t="s" r="J137" s="7">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="K137" s="7"/>
       <c r="L137" s="7"/>
@@ -6032,7 +6058,7 @@
       </c>
       <c r="D139" s="7"/>
       <c t="s" r="E139" s="7">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="F139" s="7">
         <v>321</v>
@@ -6044,7 +6070,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I139" s="7">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c t="s" r="J139" s="7">
         <v>33</v>
@@ -6065,7 +6091,7 @@
       </c>
       <c r="D140" s="7"/>
       <c t="s" r="E140" s="7">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="F140" s="7">
         <v>321</v>
@@ -6077,7 +6103,7 @@
         <v>21</v>
       </c>
       <c t="s" r="I140" s="7">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c t="s" r="J140" s="7">
         <v>74</v>
@@ -6113,19 +6139,19 @@
       </c>
       <c r="D142" s="7"/>
       <c t="s" r="E142" s="7">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="F142" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G142" s="8">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c t="s" r="H142" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I142" s="7">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c t="s" r="J142" s="7">
         <v>70</v>
@@ -6146,7 +6172,7 @@
       </c>
       <c r="D143" s="7"/>
       <c t="s" r="E143" s="7">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="F143" s="7">
         <v>321</v>
@@ -6158,10 +6184,10 @@
         <v>77</v>
       </c>
       <c t="s" r="I143" s="7">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c t="s" r="J143" s="7">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="K143" s="7"/>
       <c r="L143" s="7"/>
@@ -6179,7 +6205,7 @@
       </c>
       <c r="D144" s="7"/>
       <c t="s" r="E144" s="7">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="F144" s="7">
         <v>321</v>
@@ -6191,10 +6217,10 @@
         <v>25</v>
       </c>
       <c t="s" r="I144" s="7">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c t="s" r="J144" s="7">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="K144" s="7"/>
       <c r="L144" s="7"/>
@@ -6212,7 +6238,7 @@
       </c>
       <c r="D145" s="7"/>
       <c t="s" r="E145" s="7">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="F145" s="7">
         <v>321</v>
@@ -6221,13 +6247,13 @@
         <v>25</v>
       </c>
       <c t="s" r="H145" s="8">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c t="s" r="I145" s="7">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c t="s" r="J145" s="7">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="K145" s="7"/>
       <c r="L145" s="7"/>
@@ -6260,7 +6286,7 @@
       </c>
       <c r="D147" s="7"/>
       <c t="s" r="E147" s="7">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="F147" s="7">
         <v>321</v>
@@ -6272,15 +6298,15 @@
         <v>99</v>
       </c>
       <c t="s" r="I147" s="7">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c t="s" r="J147" s="7">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="K147" s="7"/>
       <c r="L147" s="7"/>
       <c t="s" r="M147" s="7">
-        <v>253</v>
+        <v>257</v>
       </c>
     </row>
     <row r="148" ht="14.25" customHeight="1">
@@ -6295,7 +6321,7 @@
       </c>
       <c r="D148" s="7"/>
       <c t="s" r="E148" s="7">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="F148" s="7">
         <v>321</v>
@@ -6304,13 +6330,13 @@
         <v>99</v>
       </c>
       <c t="s" r="H148" s="8">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c t="s" r="I148" s="7">
         <v>80</v>
       </c>
       <c t="s" r="J148" s="7">
-        <v>254</v>
+        <v>105</v>
       </c>
       <c r="K148" s="7"/>
       <c r="L148" s="7"/>
@@ -6328,22 +6354,22 @@
       </c>
       <c r="D149" s="7"/>
       <c t="s" r="E149" s="7">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="F149" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G149" s="8">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c t="s" r="H149" s="8">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c t="s" r="I149" s="7">
         <v>92</v>
       </c>
       <c t="s" r="J149" s="7">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="K149" s="7"/>
       <c r="L149" s="7"/>
@@ -6361,22 +6387,22 @@
       </c>
       <c r="D150" s="7"/>
       <c t="s" r="E150" s="7">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="F150" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G150" s="8">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c t="s" r="H150" s="8">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c t="s" r="I150" s="7">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c t="s" r="J150" s="7">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="K150" s="7"/>
       <c r="L150" s="7"/>
@@ -6394,13 +6420,13 @@
       </c>
       <c r="D151" s="7"/>
       <c t="s" r="E151" s="7">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="F151" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G151" s="8">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c t="s" r="H151" s="8">
         <v>99</v>
@@ -6409,7 +6435,7 @@
         <v>49</v>
       </c>
       <c t="s" r="J151" s="7">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="K151" s="7"/>
       <c r="L151" s="7"/>
@@ -6427,7 +6453,7 @@
       </c>
       <c r="D152" s="7"/>
       <c t="s" r="E152" s="7">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="F152" s="7">
         <v>321</v>
@@ -6439,10 +6465,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I152" s="7">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c t="s" r="J152" s="7">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="K152" s="7"/>
       <c r="L152" s="7"/>
@@ -6475,7 +6501,7 @@
       </c>
       <c r="D154" s="7"/>
       <c t="s" r="E154" s="7">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="F154" s="7">
         <v>321</v>
@@ -6487,15 +6513,15 @@
         <v>99</v>
       </c>
       <c t="s" r="I154" s="7">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c t="s" r="J154" s="7">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="K154" s="7"/>
       <c r="L154" s="7"/>
       <c t="s" r="M154" s="7">
-        <v>259</v>
+        <v>262</v>
       </c>
     </row>
     <row r="155" ht="15" customHeight="1">
@@ -6510,7 +6536,7 @@
       </c>
       <c r="D155" s="7"/>
       <c t="s" r="E155" s="7">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="F155" s="7">
         <v>321</v>
@@ -6522,15 +6548,15 @@
         <v>25</v>
       </c>
       <c t="s" r="I155" s="7">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c t="s" r="J155" s="7">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="K155" s="7"/>
       <c r="L155" s="7"/>
       <c t="s" r="M155" s="7">
-        <v>261</v>
+        <v>264</v>
       </c>
     </row>
     <row r="156" ht="14.25" customHeight="1">
@@ -6545,7 +6571,7 @@
       </c>
       <c r="D156" s="7"/>
       <c t="s" r="E156" s="7">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="F156" s="7">
         <v>321</v>
@@ -6557,13 +6583,13 @@
         <v>99</v>
       </c>
       <c t="s" r="I156" s="7">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c t="s" r="J156" s="7">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c t="s" r="K156" s="7">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="L156" s="7"/>
       <c t="s" r="M156" s="7">
@@ -6582,7 +6608,7 @@
       </c>
       <c r="D157" s="7"/>
       <c t="s" r="E157" s="7">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="F157" s="7">
         <v>321</v>
@@ -6594,17 +6620,17 @@
         <v>25</v>
       </c>
       <c t="s" r="I157" s="7">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c t="s" r="J157" s="7">
         <v>59</v>
       </c>
       <c t="s" r="K157" s="7">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="L157" s="7"/>
       <c t="s" r="M157" s="7">
-        <v>262</v>
+        <v>265</v>
       </c>
     </row>
     <row r="158" ht="14.25" customHeight="1">
@@ -6619,7 +6645,7 @@
       </c>
       <c r="D158" s="7"/>
       <c t="s" r="E158" s="7">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="F158" s="7">
         <v>321</v>
@@ -6637,11 +6663,11 @@
         <v>46</v>
       </c>
       <c t="s" r="K158" s="7">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="L158" s="7"/>
       <c t="s" r="M158" s="7">
-        <v>263</v>
+        <v>266</v>
       </c>
     </row>
     <row r="159" ht="14.25" customHeight="1">
@@ -6656,7 +6682,7 @@
       </c>
       <c r="D159" s="7"/>
       <c t="s" r="E159" s="7">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="F159" s="7">
         <v>321</v>
@@ -6671,7 +6697,7 @@
         <v>84</v>
       </c>
       <c t="s" r="J159" s="7">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="K159" s="7"/>
       <c r="L159" s="7"/>
@@ -6689,7 +6715,7 @@
       </c>
       <c r="D160" s="7"/>
       <c t="s" r="E160" s="7">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="F160" s="7">
         <v>321</v>
@@ -6698,13 +6724,13 @@
         <v>25</v>
       </c>
       <c t="s" r="H160" s="8">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c t="s" r="I160" s="7">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c t="s" r="J160" s="7">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="K160" s="7"/>
       <c r="L160" s="7"/>
@@ -6737,7 +6763,7 @@
       </c>
       <c r="D162" s="7"/>
       <c t="s" r="E162" s="7">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="F162" s="7">
         <v>321</v>
@@ -6749,17 +6775,17 @@
         <v>21</v>
       </c>
       <c t="s" r="I162" s="7">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c t="s" r="J162" s="7">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c t="s" r="K162" s="7">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="L162" s="7"/>
       <c t="s" r="M162" s="7">
-        <v>268</v>
+        <v>271</v>
       </c>
     </row>
     <row r="163" ht="14.25" customHeight="1">
@@ -6774,7 +6800,7 @@
       </c>
       <c r="D163" s="7"/>
       <c t="s" r="E163" s="7">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="F163" s="7">
         <v>321</v>
@@ -6783,13 +6809,13 @@
         <v>21</v>
       </c>
       <c t="s" r="H163" s="8">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c t="s" r="I163" s="7">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c t="s" r="J163" s="7">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="K163" s="7"/>
       <c r="L163" s="7"/>
@@ -6807,22 +6833,22 @@
       </c>
       <c r="D164" s="7"/>
       <c t="s" r="E164" s="7">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="F164" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G164" s="8">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c t="s" r="H164" s="8">
         <v>21</v>
       </c>
       <c t="s" r="I164" s="7">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c t="s" r="J164" s="7">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="K164" s="7"/>
       <c r="L164" s="7"/>
@@ -6840,7 +6866,7 @@
       </c>
       <c r="D165" s="7"/>
       <c t="s" r="E165" s="7">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="F165" s="7">
         <v>321</v>
@@ -6852,10 +6878,10 @@
         <v>66</v>
       </c>
       <c t="s" r="I165" s="7">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c t="s" r="J165" s="7">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="K165" s="7"/>
       <c r="L165" s="7"/>
@@ -6888,7 +6914,7 @@
       </c>
       <c r="D167" s="7"/>
       <c t="s" r="E167" s="7">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="F167" s="7">
         <v>321</v>
@@ -6900,15 +6926,15 @@
         <v>30</v>
       </c>
       <c t="s" r="I167" s="7">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c t="s" r="J167" s="7">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="K167" s="7"/>
       <c r="L167" s="7"/>
       <c t="s" r="M167" s="7">
-        <v>273</v>
+        <v>276</v>
       </c>
     </row>
     <row r="168" ht="14.25" customHeight="1">
@@ -6923,7 +6949,7 @@
       </c>
       <c r="D168" s="7"/>
       <c t="s" r="E168" s="7">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="F168" s="7">
         <v>321</v>
@@ -6932,7 +6958,7 @@
         <v>30</v>
       </c>
       <c t="s" r="H168" s="8">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c t="s" r="I168" s="7">
         <v>88</v>
@@ -6943,7 +6969,7 @@
       <c r="K168" s="7"/>
       <c r="L168" s="7"/>
       <c t="s" r="M168" s="7">
-        <v>274</v>
+        <v>277</v>
       </c>
     </row>
     <row r="169" ht="14.25" customHeight="1">
@@ -6958,27 +6984,27 @@
       </c>
       <c r="D169" s="7"/>
       <c t="s" r="E169" s="7">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="F169" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G169" s="8">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c t="s" r="H169" s="8">
         <v>21</v>
       </c>
       <c t="s" r="I169" s="7">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c t="s" r="J169" s="7">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="K169" s="7"/>
       <c r="L169" s="7"/>
       <c t="s" r="M169" s="7">
-        <v>277</v>
+        <v>280</v>
       </c>
     </row>
     <row r="170" ht="15" customHeight="1">
@@ -6993,7 +7019,7 @@
       </c>
       <c r="D170" s="7"/>
       <c t="s" r="E170" s="7">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="F170" s="7">
         <v>321</v>
@@ -7005,10 +7031,10 @@
         <v>99</v>
       </c>
       <c t="s" r="I170" s="7">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c t="s" r="J170" s="7">
-        <v>254</v>
+        <v>105</v>
       </c>
       <c r="K170" s="7"/>
       <c r="L170" s="7"/>
@@ -7026,7 +7052,7 @@
       </c>
       <c r="D171" s="7"/>
       <c t="s" r="E171" s="7">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="F171" s="7">
         <v>321</v>
@@ -7041,7 +7067,7 @@
         <v>92</v>
       </c>
       <c t="s" r="J171" s="7">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="K171" s="7"/>
       <c r="L171" s="7"/>
@@ -7059,7 +7085,7 @@
       </c>
       <c r="D172" s="7"/>
       <c t="s" r="E172" s="7">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="F172" s="7">
         <v>321</v>
@@ -7071,10 +7097,10 @@
         <v>25</v>
       </c>
       <c t="s" r="I172" s="7">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c t="s" r="J172" s="7">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="K172" s="7"/>
       <c r="L172" s="7"/>
@@ -7092,7 +7118,7 @@
       </c>
       <c r="D173" s="7"/>
       <c t="s" r="E173" s="7">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="F173" s="7">
         <v>321</v>
@@ -7107,7 +7133,7 @@
         <v>73</v>
       </c>
       <c t="s" r="J173" s="7">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="K173" s="7"/>
       <c r="L173" s="7"/>
@@ -7140,27 +7166,27 @@
       </c>
       <c r="D175" s="7"/>
       <c t="s" r="E175" s="7">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="F175" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G175" s="8">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c t="s" r="H175" s="8">
         <v>99</v>
       </c>
       <c t="s" r="I175" s="7">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c t="s" r="J175" s="7">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="K175" s="7"/>
       <c r="L175" s="7"/>
       <c t="s" r="M175" s="7">
-        <v>282</v>
+        <v>285</v>
       </c>
     </row>
     <row r="176" ht="14.25" customHeight="1">
@@ -7175,7 +7201,7 @@
       </c>
       <c r="D176" s="7"/>
       <c t="s" r="E176" s="7">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="F176" s="7">
         <v>321</v>
@@ -7184,13 +7210,13 @@
         <v>99</v>
       </c>
       <c t="s" r="H176" s="8">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c t="s" r="I176" s="7">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c t="s" r="J176" s="7">
-        <v>254</v>
+        <v>105</v>
       </c>
       <c r="K176" s="7"/>
       <c r="L176" s="7"/>
@@ -7208,22 +7234,22 @@
       </c>
       <c r="D177" s="7"/>
       <c t="s" r="E177" s="7">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="F177" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G177" s="8">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c t="s" r="H177" s="8">
         <v>99</v>
       </c>
       <c t="s" r="I177" s="7">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c t="s" r="J177" s="7">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="K177" s="7"/>
       <c r="L177" s="7"/>
@@ -7241,7 +7267,7 @@
       </c>
       <c r="D178" s="7"/>
       <c t="s" r="E178" s="7">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="F178" s="7">
         <v>321</v>
@@ -7250,13 +7276,13 @@
         <v>99</v>
       </c>
       <c t="s" r="H178" s="8">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c t="s" r="I178" s="7">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c t="s" r="J178" s="7">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="K178" s="7"/>
       <c r="L178" s="7"/>
@@ -7274,22 +7300,22 @@
       </c>
       <c r="D179" s="7"/>
       <c t="s" r="E179" s="7">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="F179" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G179" s="8">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c t="s" r="H179" s="8">
         <v>99</v>
       </c>
       <c t="s" r="I179" s="7">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c t="s" r="J179" s="7">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="K179" s="7"/>
       <c r="L179" s="7"/>
@@ -7322,7 +7348,7 @@
       </c>
       <c r="D181" s="7"/>
       <c t="s" r="E181" s="7">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="F181" s="7">
         <v>321</v>
@@ -7331,18 +7357,18 @@
         <v>21</v>
       </c>
       <c t="s" r="H181" s="8">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c t="s" r="I181" s="7">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c t="s" r="J181" s="7">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="K181" s="7"/>
       <c r="L181" s="7"/>
       <c t="s" r="M181" s="7">
-        <v>135</v>
+        <v>138</v>
       </c>
     </row>
     <row r="182" ht="14.25" customHeight="1">
@@ -7357,27 +7383,27 @@
       </c>
       <c r="D182" s="7"/>
       <c t="s" r="E182" s="7">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="F182" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G182" s="8">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c t="s" r="H182" s="8">
         <v>21</v>
       </c>
       <c t="s" r="I182" s="7">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c t="s" r="J182" s="7">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="K182" s="7"/>
       <c r="L182" s="7"/>
       <c t="s" r="M182" s="7">
-        <v>291</v>
+        <v>294</v>
       </c>
     </row>
     <row r="183" ht="14.25" customHeight="1">
@@ -7392,7 +7418,7 @@
       </c>
       <c r="D183" s="7"/>
       <c t="s" r="E183" s="7">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="F183" s="7">
         <v>321</v>
@@ -7401,18 +7427,18 @@
         <v>21</v>
       </c>
       <c t="s" r="H183" s="8">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c t="s" r="I183" s="7">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c t="s" r="J183" s="7">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="K183" s="7"/>
       <c r="L183" s="7"/>
       <c t="s" r="M183" s="7">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="184" ht="14.25" customHeight="1">
@@ -7427,22 +7453,22 @@
       </c>
       <c r="D184" s="7"/>
       <c t="s" r="E184" s="7">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="F184" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G184" s="8">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c t="s" r="H184" s="8">
         <v>21</v>
       </c>
       <c t="s" r="I184" s="7">
-        <v>139</v>
+        <v>102</v>
       </c>
       <c t="s" r="J184" s="7">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="K184" s="7"/>
       <c r="L184" s="7"/>
@@ -7460,7 +7486,7 @@
       </c>
       <c r="D185" s="7"/>
       <c t="s" r="E185" s="7">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="F185" s="7">
         <v>321</v>
@@ -7469,13 +7495,13 @@
         <v>21</v>
       </c>
       <c t="s" r="H185" s="8">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c t="s" r="I185" s="7">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c t="s" r="J185" s="7">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="K185" s="7"/>
       <c r="L185" s="7"/>
@@ -7493,13 +7519,13 @@
       </c>
       <c r="D186" s="7"/>
       <c t="s" r="E186" s="7">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="F186" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G186" s="8">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c t="s" r="H186" s="8">
         <v>21</v>
@@ -7508,7 +7534,7 @@
         <v>61</v>
       </c>
       <c t="s" r="J186" s="7">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="K186" s="7"/>
       <c r="L186" s="7"/>
@@ -7541,7 +7567,7 @@
       </c>
       <c r="D188" s="7"/>
       <c t="s" r="E188" s="7">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="F188" s="7">
         <v>321</v>
@@ -7553,13 +7579,13 @@
         <v>25</v>
       </c>
       <c t="s" r="I188" s="7">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c t="s" r="J188" s="7">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c t="s" r="K188" s="7">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="L188" s="7"/>
       <c t="s" r="M188" s="7">
@@ -7578,7 +7604,7 @@
       </c>
       <c r="D189" s="7"/>
       <c t="s" r="E189" s="7">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="F189" s="7">
         <v>321</v>
@@ -7590,13 +7616,13 @@
         <v>99</v>
       </c>
       <c t="s" r="I189" s="7">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c t="s" r="J189" s="7">
         <v>94</v>
       </c>
       <c t="s" r="K189" s="7">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="L189" s="7"/>
       <c t="s" r="M189" s="7">
@@ -7615,7 +7641,7 @@
       </c>
       <c r="D190" s="7"/>
       <c t="s" r="E190" s="7">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="F190" s="7">
         <v>321</v>
@@ -7627,17 +7653,17 @@
         <v>25</v>
       </c>
       <c t="s" r="I190" s="7">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c t="s" r="J190" s="7">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c t="s" r="K190" s="7">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="L190" s="7"/>
       <c t="s" r="M190" s="7">
-        <v>109</v>
+        <v>112</v>
       </c>
     </row>
     <row r="191" ht="14.25" customHeight="1">
@@ -7652,7 +7678,7 @@
       </c>
       <c r="D191" s="7"/>
       <c t="s" r="E191" s="7">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="F191" s="7">
         <v>321</v>
@@ -7661,10 +7687,10 @@
         <v>25</v>
       </c>
       <c t="s" r="H191" s="8">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c t="s" r="I191" s="7">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c t="s" r="J191" s="7">
         <v>97</v>
@@ -7700,7 +7726,7 @@
       </c>
       <c r="D193" s="7"/>
       <c t="s" r="E193" s="7">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="F193" s="7">
         <v>321</v>
@@ -7712,15 +7738,15 @@
         <v>99</v>
       </c>
       <c t="s" r="I193" s="7">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c t="s" r="J193" s="7">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="K193" s="7"/>
       <c r="L193" s="7"/>
       <c t="s" r="M193" s="7">
-        <v>300</v>
+        <v>303</v>
       </c>
     </row>
     <row r="194" ht="14.25" customHeight="1">
@@ -7735,7 +7761,7 @@
       </c>
       <c r="D194" s="7"/>
       <c t="s" r="E194" s="7">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="F194" s="7">
         <v>321</v>
@@ -7747,14 +7773,16 @@
         <v>25</v>
       </c>
       <c t="s" r="I194" s="7">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c t="s" r="J194" s="7">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="K194" s="7"/>
       <c r="L194" s="7"/>
-      <c r="M194" s="7"/>
+      <c t="s" r="M194" s="7">
+        <v>304</v>
+      </c>
     </row>
     <row r="195" ht="15" customHeight="1">
       <c t="s" r="A195" s="6">
@@ -7768,7 +7796,7 @@
       </c>
       <c r="D195" s="7"/>
       <c t="s" r="E195" s="7">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="F195" s="7">
         <v>321</v>
@@ -7777,13 +7805,13 @@
         <v>25</v>
       </c>
       <c t="s" r="H195" s="8">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c t="s" r="I195" s="7">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c t="s" r="J195" s="7">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="K195" s="7"/>
       <c r="L195" s="7"/>
@@ -7801,22 +7829,22 @@
       </c>
       <c r="D196" s="7"/>
       <c t="s" r="E196" s="7">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="F196" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G196" s="8">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c t="s" r="H196" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I196" s="7">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c t="s" r="J196" s="7">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="K196" s="7"/>
       <c r="L196" s="7"/>
@@ -7834,7 +7862,7 @@
       </c>
       <c r="D197" s="7"/>
       <c t="s" r="E197" s="7">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="F197" s="7">
         <v>321</v>
@@ -7846,10 +7874,10 @@
         <v>21</v>
       </c>
       <c t="s" r="I197" s="7">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c t="s" r="J197" s="7">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="K197" s="7"/>
       <c r="L197" s="7"/>
@@ -7867,7 +7895,7 @@
       </c>
       <c r="D198" s="7"/>
       <c t="s" r="E198" s="7">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="F198" s="7">
         <v>321</v>
@@ -7879,10 +7907,10 @@
         <v>25</v>
       </c>
       <c t="s" r="I198" s="7">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c t="s" r="J198" s="7">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="K198" s="7"/>
       <c r="L198" s="7"/>
@@ -7915,7 +7943,7 @@
       </c>
       <c r="D200" s="7"/>
       <c t="s" r="E200" s="7">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="F200" s="7">
         <v>321</v>
@@ -7927,15 +7955,15 @@
         <v>77</v>
       </c>
       <c t="s" r="I200" s="7">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c t="s" r="J200" s="7">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="K200" s="7"/>
       <c r="L200" s="7"/>
       <c t="s" r="M200" s="7">
-        <v>308</v>
+        <v>312</v>
       </c>
     </row>
     <row r="201" ht="14.25" customHeight="1">
@@ -7950,7 +7978,7 @@
       </c>
       <c r="D201" s="7"/>
       <c t="s" r="E201" s="7">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="F201" s="7">
         <v>321</v>
@@ -7962,10 +7990,10 @@
         <v>25</v>
       </c>
       <c t="s" r="I201" s="7">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c t="s" r="J201" s="7">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="K201" s="7"/>
       <c r="L201" s="7"/>
@@ -7983,7 +8011,7 @@
       </c>
       <c r="D202" s="7"/>
       <c t="s" r="E202" s="7">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="F202" s="7">
         <v>321</v>
@@ -7992,13 +8020,13 @@
         <v>25</v>
       </c>
       <c t="s" r="H202" s="8">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c t="s" r="I202" s="7">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c t="s" r="J202" s="7">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="K202" s="7"/>
       <c r="L202" s="7"/>
@@ -8016,22 +8044,22 @@
       </c>
       <c r="D203" s="7"/>
       <c t="s" r="E203" s="7">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="F203" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G203" s="8">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c t="s" r="H203" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I203" s="7">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c t="s" r="J203" s="7">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="K203" s="7"/>
       <c r="L203" s="7"/>
@@ -8049,7 +8077,7 @@
       </c>
       <c r="D204" s="7"/>
       <c t="s" r="E204" s="7">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="F204" s="7">
         <v>321</v>
@@ -8058,13 +8086,13 @@
         <v>25</v>
       </c>
       <c t="s" r="H204" s="8">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c t="s" r="I204" s="7">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c t="s" r="J204" s="7">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="K204" s="7"/>
       <c r="L204" s="7"/>
@@ -8082,22 +8110,22 @@
       </c>
       <c r="D205" s="7"/>
       <c t="s" r="E205" s="7">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="F205" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G205" s="8">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c t="s" r="H205" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I205" s="7">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c t="s" r="J205" s="7">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="K205" s="7"/>
       <c r="L205" s="7"/>
@@ -8130,7 +8158,7 @@
       </c>
       <c r="D207" s="7"/>
       <c t="s" r="E207" s="7">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="F207" s="7">
         <v>321</v>
@@ -8142,7 +8170,7 @@
         <v>25</v>
       </c>
       <c t="s" r="I207" s="7">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c t="s" r="J207" s="7">
         <v>97</v>
@@ -8150,7 +8178,7 @@
       <c r="K207" s="7"/>
       <c r="L207" s="7"/>
       <c t="s" r="M207" s="7">
-        <v>317</v>
+        <v>321</v>
       </c>
     </row>
     <row r="208" ht="14.25" customHeight="1">
@@ -8165,7 +8193,7 @@
       </c>
       <c r="D208" s="7"/>
       <c t="s" r="E208" s="7">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="F208" s="7">
         <v>321</v>
@@ -8180,12 +8208,12 @@
         <v>38</v>
       </c>
       <c t="s" r="J208" s="7">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="K208" s="7"/>
       <c r="L208" s="7"/>
       <c t="s" r="M208" s="7">
-        <v>318</v>
+        <v>322</v>
       </c>
     </row>
     <row r="209" ht="14.25" customHeight="1">
@@ -8200,7 +8228,7 @@
       </c>
       <c r="D209" s="7"/>
       <c t="s" r="E209" s="7">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="F209" s="7">
         <v>321</v>
@@ -8212,10 +8240,10 @@
         <v>25</v>
       </c>
       <c t="s" r="I209" s="7">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c t="s" r="J209" s="7">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="K209" s="7"/>
       <c r="L209" s="7"/>
@@ -8233,7 +8261,7 @@
       </c>
       <c r="D210" s="7"/>
       <c t="s" r="E210" s="7">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="F210" s="7">
         <v>321</v>
@@ -8245,10 +8273,10 @@
         <v>21</v>
       </c>
       <c t="s" r="I210" s="7">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c t="s" r="J210" s="7">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="K210" s="7"/>
       <c r="L210" s="7"/>
@@ -8266,7 +8294,7 @@
       </c>
       <c r="D211" s="7"/>
       <c t="s" r="E211" s="7">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="F211" s="7">
         <v>321</v>
@@ -8314,7 +8342,7 @@
       </c>
       <c r="D213" s="7"/>
       <c t="s" r="E213" s="7">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="F213" s="7">
         <v>321</v>
@@ -8323,18 +8351,18 @@
         <v>25</v>
       </c>
       <c t="s" r="H213" s="8">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c t="s" r="I213" s="7">
         <v>78</v>
       </c>
       <c t="s" r="J213" s="7">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="K213" s="7"/>
       <c r="L213" s="7"/>
       <c t="s" r="M213" s="7">
-        <v>322</v>
+        <v>326</v>
       </c>
     </row>
     <row r="214" ht="14.25" customHeight="1">
@@ -8349,13 +8377,13 @@
       </c>
       <c r="D214" s="7"/>
       <c t="s" r="E214" s="7">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="F214" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G214" s="8">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c t="s" r="H214" s="8">
         <v>25</v>
@@ -8364,12 +8392,12 @@
         <v>67</v>
       </c>
       <c t="s" r="J214" s="7">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="K214" s="7"/>
       <c r="L214" s="7"/>
       <c t="s" r="M214" s="7">
-        <v>323</v>
+        <v>327</v>
       </c>
     </row>
     <row r="215" ht="15" customHeight="1">
@@ -8384,7 +8412,7 @@
       </c>
       <c r="D215" s="7"/>
       <c t="s" r="E215" s="7">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="F215" s="7">
         <v>321</v>
@@ -8399,7 +8427,7 @@
         <v>89</v>
       </c>
       <c t="s" r="J215" s="7">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="K215" s="7"/>
       <c r="L215" s="7"/>
@@ -8417,7 +8445,7 @@
       </c>
       <c r="D216" s="7"/>
       <c t="s" r="E216" s="7">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="F216" s="7">
         <v>321</v>
@@ -8429,10 +8457,10 @@
         <v>25</v>
       </c>
       <c t="s" r="I216" s="7">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c t="s" r="J216" s="7">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="K216" s="7"/>
       <c r="L216" s="7"/>
@@ -8450,7 +8478,7 @@
       </c>
       <c r="D217" s="7"/>
       <c t="s" r="E217" s="7">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="F217" s="7">
         <v>321</v>
@@ -8462,7 +8490,7 @@
         <v>77</v>
       </c>
       <c t="s" r="I217" s="7">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c t="s" r="J217" s="7">
         <v>60</v>
@@ -8483,7 +8511,7 @@
       </c>
       <c r="D218" s="7"/>
       <c t="s" r="E218" s="7">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="F218" s="7">
         <v>321</v>
@@ -8495,10 +8523,10 @@
         <v>25</v>
       </c>
       <c t="s" r="I218" s="7">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c t="s" r="J218" s="7">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="K218" s="7"/>
       <c r="L218" s="7"/>
@@ -8531,7 +8559,7 @@
       </c>
       <c r="D220" s="7"/>
       <c t="s" r="E220" s="7">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="F220" s="7">
         <v>321</v>
@@ -8543,15 +8571,15 @@
         <v>43</v>
       </c>
       <c t="s" r="I220" s="7">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c t="s" r="J220" s="7">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="K220" s="7"/>
       <c r="L220" s="7"/>
       <c t="s" r="M220" s="7">
-        <v>325</v>
+        <v>329</v>
       </c>
     </row>
     <row r="221" ht="14.25" customHeight="1">
@@ -8566,7 +8594,7 @@
       </c>
       <c r="D221" s="7"/>
       <c t="s" r="E221" s="7">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="F221" s="7">
         <v>321</v>
@@ -8581,7 +8609,7 @@
         <v>64</v>
       </c>
       <c t="s" r="J221" s="7">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="K221" s="7"/>
       <c r="L221" s="7"/>
@@ -8601,7 +8629,7 @@
       </c>
       <c r="D222" s="7"/>
       <c t="s" r="E222" s="7">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="F222" s="7">
         <v>321</v>
@@ -8610,13 +8638,13 @@
         <v>21</v>
       </c>
       <c t="s" r="H222" s="8">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c t="s" r="I222" s="7">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c t="s" r="J222" s="7">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="K222" s="7"/>
       <c r="L222" s="7"/>
@@ -8634,19 +8662,19 @@
       </c>
       <c r="D223" s="7"/>
       <c t="s" r="E223" s="7">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="F223" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G223" s="8">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c t="s" r="H223" s="8">
         <v>21</v>
       </c>
       <c t="s" r="I223" s="7">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c t="s" r="J223" s="7">
         <v>92</v>
@@ -8667,7 +8695,7 @@
       </c>
       <c r="D224" s="7"/>
       <c t="s" r="E224" s="7">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="F224" s="7">
         <v>321</v>
@@ -8676,13 +8704,13 @@
         <v>21</v>
       </c>
       <c t="s" r="H224" s="8">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c t="s" r="I224" s="7">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c t="s" r="J224" s="7">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="K224" s="7"/>
       <c r="L224" s="7"/>
@@ -8700,22 +8728,22 @@
       </c>
       <c r="D225" s="7"/>
       <c t="s" r="E225" s="7">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="F225" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G225" s="8">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c t="s" r="H225" s="8">
         <v>21</v>
       </c>
       <c t="s" r="I225" s="7">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c t="s" r="J225" s="7">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="K225" s="7"/>
       <c r="L225" s="7"/>
@@ -8733,7 +8761,7 @@
       </c>
       <c r="D226" s="7"/>
       <c t="s" r="E226" s="7">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="F226" s="7">
         <v>321</v>
@@ -8745,10 +8773,10 @@
         <v>43</v>
       </c>
       <c t="s" r="I226" s="7">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c t="s" r="J226" s="7">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="K226" s="7"/>
       <c r="L226" s="7"/>
@@ -8766,7 +8794,7 @@
       </c>
       <c r="D227" s="7"/>
       <c t="s" r="E227" s="7">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="F227" s="7">
         <v>321</v>
@@ -8778,10 +8806,10 @@
         <v>21</v>
       </c>
       <c t="s" r="I227" s="7">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c t="s" r="J227" s="7">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="K227" s="7"/>
       <c r="L227" s="7"/>
@@ -8814,7 +8842,7 @@
       </c>
       <c r="D229" s="7"/>
       <c t="s" r="E229" s="7">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="F229" s="7">
         <v>321</v>
@@ -8826,15 +8854,15 @@
         <v>21</v>
       </c>
       <c t="s" r="I229" s="7">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c t="s" r="J229" s="7">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="K229" s="7"/>
       <c r="L229" s="7"/>
       <c t="s" r="M229" s="7">
-        <v>332</v>
+        <v>336</v>
       </c>
     </row>
     <row r="230" ht="15" customHeight="1">
@@ -8849,7 +8877,7 @@
       </c>
       <c r="D230" s="7"/>
       <c t="s" r="E230" s="7">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="F230" s="7">
         <v>321</v>
@@ -8864,12 +8892,12 @@
         <v>19</v>
       </c>
       <c t="s" r="J230" s="7">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="K230" s="7"/>
       <c r="L230" s="7"/>
       <c t="s" r="M230" s="7">
-        <v>333</v>
+        <v>337</v>
       </c>
     </row>
     <row r="231" ht="14.25" customHeight="1">
@@ -8884,7 +8912,7 @@
       </c>
       <c r="D231" s="7"/>
       <c t="s" r="E231" s="7">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="F231" s="7">
         <v>321</v>
@@ -8896,15 +8924,15 @@
         <v>21</v>
       </c>
       <c t="s" r="I231" s="7">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c t="s" r="J231" s="7">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="K231" s="7"/>
       <c r="L231" s="7"/>
       <c t="s" r="M231" s="7">
-        <v>130</v>
+        <v>80</v>
       </c>
     </row>
     <row r="232" ht="14.25" customHeight="1">
@@ -8919,7 +8947,7 @@
       </c>
       <c r="D232" s="7"/>
       <c t="s" r="E232" s="7">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="F232" s="7">
         <v>321</v>
@@ -8928,13 +8956,13 @@
         <v>21</v>
       </c>
       <c t="s" r="H232" s="8">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c t="s" r="I232" s="7">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c t="s" r="J232" s="7">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="K232" s="7"/>
       <c r="L232" s="7"/>
@@ -8952,13 +8980,13 @@
       </c>
       <c r="D233" s="7"/>
       <c t="s" r="E233" s="7">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="F233" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G233" s="8">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c t="s" r="H233" s="8">
         <v>21</v>
@@ -8967,7 +8995,7 @@
         <v>72</v>
       </c>
       <c t="s" r="J233" s="7">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="K233" s="7"/>
       <c r="L233" s="7"/>
@@ -8985,7 +9013,7 @@
       </c>
       <c r="D234" s="7"/>
       <c t="s" r="E234" s="7">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="F234" s="7">
         <v>321</v>
@@ -8994,13 +9022,13 @@
         <v>21</v>
       </c>
       <c t="s" r="H234" s="8">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c t="s" r="I234" s="7">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c t="s" r="J234" s="7">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="K234" s="7"/>
       <c r="L234" s="7"/>
@@ -9018,22 +9046,22 @@
       </c>
       <c r="D235" s="7"/>
       <c t="s" r="E235" s="7">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="F235" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G235" s="8">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c t="s" r="H235" s="8">
         <v>21</v>
       </c>
       <c t="s" r="I235" s="7">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c t="s" r="J235" s="7">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="K235" s="7"/>
       <c r="L235" s="7"/>
@@ -9066,7 +9094,7 @@
       </c>
       <c r="D237" s="7"/>
       <c t="s" r="E237" s="7">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="F237" s="7">
         <v>321</v>
@@ -9078,10 +9106,10 @@
         <v>30</v>
       </c>
       <c t="s" r="I237" s="7">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c t="s" r="J237" s="7">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="K237" s="7"/>
       <c r="L237" s="7"/>
@@ -9101,7 +9129,7 @@
       </c>
       <c r="D238" s="7"/>
       <c t="s" r="E238" s="7">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="F238" s="7">
         <v>321</v>
@@ -9113,15 +9141,15 @@
         <v>25</v>
       </c>
       <c t="s" r="I238" s="7">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c t="s" r="J238" s="7">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="K238" s="7"/>
       <c r="L238" s="7"/>
       <c t="s" r="M238" s="7">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="239" ht="14.25" customHeight="1">
@@ -9136,7 +9164,7 @@
       </c>
       <c r="D239" s="7"/>
       <c t="s" r="E239" s="7">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="F239" s="7">
         <v>321</v>
@@ -9148,15 +9176,15 @@
         <v>30</v>
       </c>
       <c t="s" r="I239" s="7">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c t="s" r="J239" s="7">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="K239" s="7"/>
       <c r="L239" s="7"/>
       <c t="s" r="M239" s="7">
-        <v>188</v>
+        <v>191</v>
       </c>
     </row>
     <row r="240" ht="15" customHeight="1">
@@ -9171,7 +9199,7 @@
       </c>
       <c r="D240" s="7"/>
       <c t="s" r="E240" s="7">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="F240" s="7">
         <v>321</v>
@@ -9183,10 +9211,10 @@
         <v>25</v>
       </c>
       <c t="s" r="I240" s="7">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c t="s" r="J240" s="7">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="K240" s="7"/>
       <c r="L240" s="7"/>
@@ -9204,7 +9232,7 @@
       </c>
       <c r="D241" s="7"/>
       <c t="s" r="E241" s="7">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="F241" s="7">
         <v>321</v>
@@ -9213,13 +9241,13 @@
         <v>25</v>
       </c>
       <c t="s" r="H241" s="8">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c t="s" r="I241" s="7">
         <v>81</v>
       </c>
       <c t="s" r="J241" s="7">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="K241" s="7"/>
       <c r="L241" s="7"/>
@@ -9237,22 +9265,22 @@
       </c>
       <c r="D242" s="7"/>
       <c t="s" r="E242" s="7">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="F242" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G242" s="8">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c t="s" r="H242" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I242" s="7">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c t="s" r="J242" s="7">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="K242" s="7"/>
       <c r="L242" s="7"/>
@@ -9270,7 +9298,7 @@
       </c>
       <c r="D243" s="7"/>
       <c t="s" r="E243" s="7">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="F243" s="7">
         <v>321</v>
@@ -9279,13 +9307,13 @@
         <v>25</v>
       </c>
       <c t="s" r="H243" s="8">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c t="s" r="I243" s="7">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c t="s" r="J243" s="7">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="K243" s="7"/>
       <c r="L243" s="7"/>
@@ -9303,22 +9331,22 @@
       </c>
       <c r="D244" s="7"/>
       <c t="s" r="E244" s="7">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="F244" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G244" s="8">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c t="s" r="H244" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I244" s="7">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c t="s" r="J244" s="7">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="K244" s="7"/>
       <c r="L244" s="7"/>
@@ -9351,7 +9379,7 @@
       </c>
       <c r="D246" s="7"/>
       <c t="s" r="E246" s="7">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="F246" s="7">
         <v>321</v>
@@ -9363,15 +9391,15 @@
         <v>21</v>
       </c>
       <c t="s" r="I246" s="7">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c t="s" r="J246" s="7">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="K246" s="7"/>
       <c r="L246" s="7"/>
       <c t="s" r="M246" s="7">
-        <v>345</v>
+        <v>349</v>
       </c>
     </row>
     <row r="247" ht="14.25" customHeight="1">
@@ -9386,7 +9414,7 @@
       </c>
       <c r="D247" s="7"/>
       <c t="s" r="E247" s="7">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="F247" s="7">
         <v>321</v>
@@ -9401,12 +9429,12 @@
         <v>40</v>
       </c>
       <c t="s" r="J247" s="7">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="K247" s="7"/>
       <c r="L247" s="7"/>
       <c t="s" r="M247" s="7">
-        <v>178</v>
+        <v>181</v>
       </c>
     </row>
     <row r="248" ht="14.25" customHeight="1">
@@ -9421,7 +9449,7 @@
       </c>
       <c r="D248" s="7"/>
       <c t="s" r="E248" s="7">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="F248" s="7">
         <v>321</v>
@@ -9436,7 +9464,7 @@
         <v>91</v>
       </c>
       <c t="s" r="J248" s="7">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="K248" s="7"/>
       <c r="L248" s="7"/>
@@ -9454,7 +9482,7 @@
       </c>
       <c r="D249" s="7"/>
       <c t="s" r="E249" s="7">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="F249" s="7">
         <v>321</v>
@@ -9466,10 +9494,10 @@
         <v>25</v>
       </c>
       <c t="s" r="I249" s="7">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c t="s" r="J249" s="7">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="K249" s="7"/>
       <c r="L249" s="7"/>
@@ -9502,7 +9530,7 @@
       </c>
       <c r="D251" s="7"/>
       <c t="s" r="E251" s="7">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="F251" s="7">
         <v>321</v>
@@ -9522,7 +9550,7 @@
       <c r="K251" s="7"/>
       <c r="L251" s="7"/>
       <c t="s" r="M251" s="7">
-        <v>340</v>
+        <v>344</v>
       </c>
     </row>
     <row r="252" ht="14.25" customHeight="1">
@@ -9537,7 +9565,7 @@
       </c>
       <c r="D252" s="7"/>
       <c t="s" r="E252" s="7">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="F252" s="7">
         <v>321</v>
@@ -9549,15 +9577,15 @@
         <v>17</v>
       </c>
       <c t="s" r="I252" s="7">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c t="s" r="J252" s="7">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="K252" s="7"/>
       <c r="L252" s="7"/>
       <c t="s" r="M252" s="7">
-        <v>348</v>
+        <v>352</v>
       </c>
     </row>
     <row r="253" ht="14.25" customHeight="1">
@@ -9572,7 +9600,7 @@
       </c>
       <c r="D253" s="7"/>
       <c t="s" r="E253" s="7">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="F253" s="7">
         <v>321</v>
@@ -9584,14 +9612,16 @@
         <v>21</v>
       </c>
       <c t="s" r="I253" s="7">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c t="s" r="J253" s="7">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="K253" s="7"/>
       <c r="L253" s="7"/>
-      <c r="M253" s="7"/>
+      <c t="s" r="M253" s="7">
+        <v>353</v>
+      </c>
     </row>
     <row r="254" ht="14.25" customHeight="1">
       <c t="s" r="A254" s="6">
@@ -9605,7 +9635,7 @@
       </c>
       <c r="D254" s="7"/>
       <c t="s" r="E254" s="7">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="F254" s="7">
         <v>321</v>
@@ -9617,10 +9647,10 @@
         <v>99</v>
       </c>
       <c t="s" r="I254" s="7">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c t="s" r="J254" s="7">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="K254" s="7"/>
       <c r="L254" s="7"/>
@@ -9638,7 +9668,7 @@
       </c>
       <c r="D255" s="7"/>
       <c t="s" r="E255" s="7">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="F255" s="7">
         <v>321</v>
@@ -9650,10 +9680,10 @@
         <v>21</v>
       </c>
       <c t="s" r="I255" s="7">
-        <v>254</v>
+        <v>105</v>
       </c>
       <c t="s" r="J255" s="7">
-        <v>349</v>
+        <v>106</v>
       </c>
       <c r="K255" s="7"/>
       <c r="L255" s="7"/>
@@ -9671,7 +9701,7 @@
       </c>
       <c r="D256" s="7"/>
       <c t="s" r="E256" s="7">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="F256" s="7">
         <v>321</v>
@@ -9683,10 +9713,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I256" s="7">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c t="s" r="J256" s="7">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="K256" s="7"/>
       <c r="L256" s="7"/>
@@ -9704,7 +9734,7 @@
       </c>
       <c r="D257" s="7"/>
       <c t="s" r="E257" s="7">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="F257" s="7">
         <v>321</v>
@@ -9737,7 +9767,7 @@
       </c>
       <c r="D258" s="7"/>
       <c t="s" r="E258" s="7">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="F258" s="7">
         <v>321</v>
@@ -9749,10 +9779,10 @@
         <v>99</v>
       </c>
       <c t="s" r="I258" s="7">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c t="s" r="J258" s="7">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="K258" s="7"/>
       <c r="L258" s="7"/>
@@ -9770,7 +9800,7 @@
       </c>
       <c r="D259" s="7"/>
       <c t="s" r="E259" s="7">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="F259" s="7">
         <v>321</v>
@@ -9782,10 +9812,10 @@
         <v>21</v>
       </c>
       <c t="s" r="I259" s="7">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c t="s" r="J259" s="7">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="K259" s="7"/>
       <c r="L259" s="7"/>
@@ -9818,7 +9848,7 @@
       </c>
       <c r="D261" s="7"/>
       <c t="s" r="E261" s="7">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="F261" s="7">
         <v>321</v>
@@ -9830,15 +9860,15 @@
         <v>25</v>
       </c>
       <c t="s" r="I261" s="7">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c t="s" r="J261" s="7">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="K261" s="7"/>
       <c r="L261" s="7"/>
       <c t="s" r="M261" s="7">
-        <v>352</v>
+        <v>356</v>
       </c>
     </row>
     <row r="262" ht="14.25" customHeight="1">
@@ -9853,7 +9883,7 @@
       </c>
       <c r="D262" s="7"/>
       <c t="s" r="E262" s="7">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="F262" s="7">
         <v>321</v>
@@ -9862,13 +9892,13 @@
         <v>25</v>
       </c>
       <c t="s" r="H262" s="8">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c t="s" r="I262" s="7">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c t="s" r="J262" s="7">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="K262" s="7"/>
       <c r="L262" s="7"/>
@@ -9886,22 +9916,22 @@
       </c>
       <c r="D263" s="7"/>
       <c t="s" r="E263" s="7">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="F263" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G263" s="8">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c t="s" r="H263" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I263" s="7">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c t="s" r="J263" s="7">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="K263" s="7"/>
       <c r="L263" s="7"/>
@@ -9919,7 +9949,7 @@
       </c>
       <c r="D264" s="7"/>
       <c t="s" r="E264" s="7">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="F264" s="7">
         <v>321</v>
@@ -9931,10 +9961,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I264" s="7">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c t="s" r="J264" s="7">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="K264" s="7"/>
       <c r="L264" s="7"/>
@@ -9967,7 +9997,7 @@
       </c>
       <c r="D266" s="7"/>
       <c t="s" r="E266" s="7">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="F266" s="7">
         <v>321</v>
@@ -9976,18 +10006,18 @@
         <v>21</v>
       </c>
       <c t="s" r="H266" s="8">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c t="s" r="I266" s="7">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c t="s" r="J266" s="7">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="K266" s="7"/>
       <c r="L266" s="7"/>
       <c t="s" r="M266" s="7">
-        <v>358</v>
+        <v>362</v>
       </c>
     </row>
     <row r="267" ht="14.25" customHeight="1">
@@ -10002,13 +10032,13 @@
       </c>
       <c r="D267" s="7"/>
       <c t="s" r="E267" s="7">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="F267" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G267" s="8">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c t="s" r="H267" s="8">
         <v>21</v>
@@ -10017,7 +10047,7 @@
         <v>59</v>
       </c>
       <c t="s" r="J267" s="7">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="K267" s="7"/>
       <c r="L267" s="7"/>
@@ -10035,7 +10065,7 @@
       </c>
       <c r="D268" s="7"/>
       <c t="s" r="E268" s="7">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="F268" s="7">
         <v>321</v>
@@ -10044,13 +10074,13 @@
         <v>21</v>
       </c>
       <c t="s" r="H268" s="8">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c t="s" r="I268" s="7">
         <v>50</v>
       </c>
       <c t="s" r="J268" s="7">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="K268" s="7"/>
       <c r="L268" s="7"/>
@@ -10083,7 +10113,7 @@
       </c>
       <c r="D270" s="7"/>
       <c t="s" r="E270" s="7">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="F270" s="7">
         <v>321</v>
@@ -10092,7 +10122,7 @@
         <v>21</v>
       </c>
       <c t="s" r="H270" s="8">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c t="s" r="I270" s="7">
         <v>97</v>
@@ -10103,7 +10133,7 @@
       <c r="K270" s="7"/>
       <c r="L270" s="7"/>
       <c t="s" r="M270" s="7">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="271" ht="14.25" customHeight="1">
@@ -10118,19 +10148,19 @@
       </c>
       <c r="D271" s="7"/>
       <c t="s" r="E271" s="7">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="F271" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G271" s="8">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c t="s" r="H271" s="8">
         <v>99</v>
       </c>
       <c t="s" r="I271" s="7">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c t="s" r="J271" s="7">
         <v>91</v>
@@ -10138,7 +10168,7 @@
       <c r="K271" s="7"/>
       <c r="L271" s="7"/>
       <c t="s" r="M271" s="7">
-        <v>363</v>
+        <v>367</v>
       </c>
     </row>
     <row r="272" ht="14.25" customHeight="1">
@@ -10168,7 +10198,7 @@
       </c>
       <c r="D273" s="7"/>
       <c t="s" r="E273" s="7">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="F273" s="7">
         <v>321</v>
@@ -10177,18 +10207,18 @@
         <v>21</v>
       </c>
       <c t="s" r="H273" s="8">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c t="s" r="I273" s="7">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c t="s" r="J273" s="7">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="K273" s="7"/>
       <c r="L273" s="7"/>
       <c t="s" r="M273" s="7">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="274" ht="14.25" customHeight="1">
@@ -10203,27 +10233,27 @@
       </c>
       <c r="D274" s="7"/>
       <c t="s" r="E274" s="7">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="F274" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G274" s="8">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c t="s" r="H274" s="8">
         <v>21</v>
       </c>
       <c t="s" r="I274" s="7">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c t="s" r="J274" s="7">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="K274" s="7"/>
       <c r="L274" s="7"/>
       <c t="s" r="M274" s="7">
-        <v>365</v>
+        <v>353</v>
       </c>
     </row>
     <row r="275" ht="15" customHeight="1">
@@ -10238,7 +10268,7 @@
       </c>
       <c r="D275" s="7"/>
       <c t="s" r="E275" s="7">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="F275" s="7">
         <v>321</v>
@@ -10247,10 +10277,10 @@
         <v>21</v>
       </c>
       <c t="s" r="H275" s="8">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c t="s" r="I275" s="7">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c t="s" r="J275" s="7">
         <v>83</v>
@@ -10271,22 +10301,22 @@
       </c>
       <c r="D276" s="7"/>
       <c t="s" r="E276" s="7">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="F276" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G276" s="8">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c t="s" r="H276" s="8">
         <v>21</v>
       </c>
       <c t="s" r="I276" s="7">
-        <v>349</v>
+        <v>106</v>
       </c>
       <c t="s" r="J276" s="7">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="K276" s="7"/>
       <c r="L276" s="7"/>
@@ -10304,7 +10334,7 @@
       </c>
       <c r="D277" s="7"/>
       <c t="s" r="E277" s="7">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="F277" s="7">
         <v>321</v>
@@ -10316,7 +10346,7 @@
         <v>25</v>
       </c>
       <c t="s" r="I277" s="7">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c t="s" r="J277" s="7">
         <v>73</v>
@@ -10337,7 +10367,7 @@
       </c>
       <c r="D278" s="7"/>
       <c t="s" r="E278" s="7">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="F278" s="7">
         <v>321</v>
@@ -10349,10 +10379,10 @@
         <v>21</v>
       </c>
       <c t="s" r="I278" s="7">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c t="s" r="J278" s="7">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="K278" s="7"/>
       <c r="L278" s="7"/>
@@ -10385,7 +10415,7 @@
       </c>
       <c r="D280" s="7"/>
       <c t="s" r="E280" s="7">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="F280" s="7">
         <v>320</v>
@@ -10394,18 +10424,18 @@
         <v>21</v>
       </c>
       <c t="s" r="H280" s="8">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c t="s" r="I280" s="7">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c t="s" r="J280" s="7">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="K280" s="7"/>
       <c r="L280" s="7"/>
       <c t="s" r="M280" s="7">
-        <v>275</v>
+        <v>278</v>
       </c>
     </row>
     <row r="281" ht="14.25" customHeight="1">
@@ -10420,26 +10450,28 @@
       </c>
       <c r="D281" s="7"/>
       <c t="s" r="E281" s="7">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="F281" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G281" s="8">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c t="s" r="H281" s="8">
         <v>21</v>
       </c>
       <c t="s" r="I281" s="7">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c t="s" r="J281" s="7">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="K281" s="7"/>
       <c r="L281" s="7"/>
-      <c r="M281" s="7"/>
+      <c t="s" r="M281" s="7">
+        <v>115</v>
+      </c>
     </row>
     <row r="282" ht="14.25" customHeight="1">
       <c t="s" r="A282" s="6">
@@ -10453,7 +10485,7 @@
       </c>
       <c r="D282" s="7"/>
       <c t="s" r="E282" s="7">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="F282" s="7">
         <v>320</v>
@@ -10462,7 +10494,7 @@
         <v>21</v>
       </c>
       <c t="s" r="H282" s="8">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c t="s" r="I282" s="7">
         <v>59</v>
@@ -10486,13 +10518,13 @@
       </c>
       <c r="D283" s="7"/>
       <c t="s" r="E283" s="7">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="F283" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G283" s="8">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c t="s" r="H283" s="8">
         <v>21</v>
@@ -10501,7 +10533,7 @@
         <v>49</v>
       </c>
       <c t="s" r="J283" s="7">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="K283" s="7"/>
       <c r="L283" s="7"/>
@@ -10534,7 +10566,7 @@
       </c>
       <c r="D285" s="7"/>
       <c t="s" r="E285" s="7">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="F285" s="7">
         <v>321</v>
@@ -10543,17 +10575,19 @@
         <v>25</v>
       </c>
       <c t="s" r="H285" s="8">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c t="s" r="I285" s="7">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c t="s" r="J285" s="7">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="K285" s="7"/>
       <c r="L285" s="7"/>
-      <c r="M285" s="7"/>
+      <c t="s" r="M285" s="7">
+        <v>373</v>
+      </c>
     </row>
     <row r="286" ht="14.25" customHeight="1">
       <c t="s" r="A286" s="6">
@@ -10567,22 +10601,22 @@
       </c>
       <c r="D286" s="7"/>
       <c t="s" r="E286" s="7">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="F286" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G286" s="8">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c t="s" r="H286" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I286" s="7">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c t="s" r="J286" s="7">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="K286" s="7"/>
       <c r="L286" s="7"/>
@@ -10600,7 +10634,7 @@
       </c>
       <c r="D287" s="7"/>
       <c t="s" r="E287" s="7">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="F287" s="7">
         <v>321</v>
@@ -10633,7 +10667,7 @@
       </c>
       <c r="D288" s="7"/>
       <c t="s" r="E288" s="7">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="F288" s="7">
         <v>321</v>
@@ -10645,10 +10679,10 @@
         <v>25</v>
       </c>
       <c t="s" r="I288" s="7">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c t="s" r="J288" s="7">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="K288" s="7"/>
       <c r="L288" s="7"/>
@@ -10681,7 +10715,7 @@
       </c>
       <c r="D290" s="7"/>
       <c t="s" r="E290" s="7">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="F290" s="7">
         <v>321</v>
@@ -10693,15 +10727,15 @@
         <v>58</v>
       </c>
       <c t="s" r="I290" s="7">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c t="s" r="J290" s="7">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="K290" s="7"/>
       <c r="L290" s="7"/>
       <c t="s" r="M290" s="7">
-        <v>371</v>
+        <v>375</v>
       </c>
     </row>
     <row r="291" ht="14.25" customHeight="1">
@@ -10716,7 +10750,7 @@
       </c>
       <c r="D291" s="7"/>
       <c t="s" r="E291" s="7">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="F291" s="7">
         <v>321</v>
@@ -10728,10 +10762,10 @@
         <v>21</v>
       </c>
       <c t="s" r="I291" s="7">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c t="s" r="J291" s="7">
-        <v>254</v>
+        <v>105</v>
       </c>
       <c r="K291" s="7"/>
       <c r="L291" s="7"/>
@@ -10749,7 +10783,7 @@
       </c>
       <c r="D292" s="7"/>
       <c t="s" r="E292" s="7">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="F292" s="7">
         <v>321</v>
@@ -10758,13 +10792,13 @@
         <v>21</v>
       </c>
       <c t="s" r="H292" s="8">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c t="s" r="I292" s="7">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c t="s" r="J292" s="7">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="K292" s="7"/>
       <c r="L292" s="7"/>
@@ -10782,22 +10816,22 @@
       </c>
       <c r="D293" s="7"/>
       <c t="s" r="E293" s="7">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="F293" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G293" s="8">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c t="s" r="H293" s="8">
         <v>21</v>
       </c>
       <c t="s" r="I293" s="7">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c t="s" r="J293" s="7">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="K293" s="7"/>
       <c r="L293" s="7"/>
@@ -10815,7 +10849,7 @@
       </c>
       <c r="D294" s="7"/>
       <c t="s" r="E294" s="7">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="F294" s="7">
         <v>321</v>
@@ -10824,7 +10858,7 @@
         <v>21</v>
       </c>
       <c t="s" r="H294" s="8">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c t="s" r="I294" s="7">
         <v>50</v>
@@ -10863,7 +10897,7 @@
       </c>
       <c r="D296" s="7"/>
       <c t="s" r="E296" s="7">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="F296" s="7">
         <v>320</v>
@@ -10875,15 +10909,15 @@
         <v>25</v>
       </c>
       <c t="s" r="I296" s="7">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c t="s" r="J296" s="7">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="K296" s="7"/>
       <c r="L296" s="7"/>
       <c t="s" r="M296" s="7">
-        <v>373</v>
+        <v>377</v>
       </c>
     </row>
     <row r="297" ht="14.25" customHeight="1">
@@ -10898,7 +10932,7 @@
       </c>
       <c r="D297" s="7"/>
       <c t="s" r="E297" s="7">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="F297" s="7">
         <v>320</v>
@@ -10907,18 +10941,18 @@
         <v>25</v>
       </c>
       <c t="s" r="H297" s="8">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c t="s" r="I297" s="7">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c t="s" r="J297" s="7">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="K297" s="7"/>
       <c r="L297" s="7"/>
       <c t="s" r="M297" s="7">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="298" ht="14.25" customHeight="1">
@@ -10933,22 +10967,22 @@
       </c>
       <c r="D298" s="7"/>
       <c t="s" r="E298" s="7">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="F298" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G298" s="8">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c t="s" r="H298" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I298" s="7">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c t="s" r="J298" s="7">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="K298" s="7"/>
       <c r="L298" s="7"/>
@@ -10966,7 +11000,7 @@
       </c>
       <c r="D299" s="7"/>
       <c t="s" r="E299" s="7">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="F299" s="7">
         <v>320</v>
@@ -10978,7 +11012,7 @@
         <v>99</v>
       </c>
       <c t="s" r="I299" s="7">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c t="s" r="J299" s="7">
         <v>31</v>
@@ -10999,7 +11033,7 @@
       </c>
       <c r="D300" s="7"/>
       <c t="s" r="E300" s="7">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="F300" s="7">
         <v>320</v>
@@ -11014,7 +11048,7 @@
         <v>47</v>
       </c>
       <c t="s" r="J300" s="7">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="K300" s="7"/>
       <c r="L300" s="7"/>
@@ -11032,7 +11066,7 @@
       </c>
       <c r="D301" s="7"/>
       <c t="s" r="E301" s="7">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="F301" s="7">
         <v>320</v>
@@ -11044,10 +11078,10 @@
         <v>48</v>
       </c>
       <c t="s" r="I301" s="7">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c t="s" r="J301" s="7">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="K301" s="7"/>
       <c r="L301" s="7"/>
@@ -11065,7 +11099,7 @@
       </c>
       <c r="D302" s="7"/>
       <c t="s" r="E302" s="7">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="F302" s="7">
         <v>320</v>
@@ -11077,10 +11111,10 @@
         <v>25</v>
       </c>
       <c t="s" r="I302" s="7">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c t="s" r="J302" s="7">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="K302" s="7"/>
       <c r="L302" s="7"/>
@@ -11113,7 +11147,7 @@
       </c>
       <c r="D304" s="7"/>
       <c t="s" r="E304" s="7">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="F304" s="7">
         <v>321</v>
@@ -11125,7 +11159,7 @@
         <v>21</v>
       </c>
       <c t="s" r="I304" s="7">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c t="s" r="J304" s="7">
         <v>38</v>
@@ -11133,7 +11167,7 @@
       <c r="K304" s="7"/>
       <c r="L304" s="7"/>
       <c t="s" r="M304" s="7">
-        <v>379</v>
+        <v>383</v>
       </c>
     </row>
     <row r="305" ht="15" customHeight="1">
@@ -11148,7 +11182,7 @@
       </c>
       <c r="D305" s="7"/>
       <c t="s" r="E305" s="7">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="F305" s="7">
         <v>321</v>
@@ -11160,15 +11194,15 @@
         <v>43</v>
       </c>
       <c t="s" r="I305" s="7">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c t="s" r="J305" s="7">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="K305" s="7"/>
       <c r="L305" s="7"/>
       <c t="s" r="M305" s="7">
-        <v>381</v>
+        <v>385</v>
       </c>
     </row>
     <row r="306" ht="14.25" customHeight="1">
@@ -11183,7 +11217,7 @@
       </c>
       <c r="D306" s="7"/>
       <c t="s" r="E306" s="7">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="F306" s="7">
         <v>321</v>
@@ -11192,13 +11226,13 @@
         <v>43</v>
       </c>
       <c t="s" r="H306" s="8">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c t="s" r="I306" s="7">
-        <v>139</v>
+        <v>102</v>
       </c>
       <c t="s" r="J306" s="7">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="K306" s="7"/>
       <c r="L306" s="7"/>
@@ -11216,22 +11250,22 @@
       </c>
       <c r="D307" s="7"/>
       <c t="s" r="E307" s="7">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="F307" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G307" s="8">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c t="s" r="H307" s="8">
         <v>43</v>
       </c>
       <c t="s" r="I307" s="7">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c t="s" r="J307" s="7">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="K307" s="7"/>
       <c r="L307" s="7"/>
@@ -11249,7 +11283,7 @@
       </c>
       <c r="D308" s="7"/>
       <c t="s" r="E308" s="7">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="F308" s="7">
         <v>321</v>
@@ -11264,7 +11298,7 @@
         <v>60</v>
       </c>
       <c t="s" r="J308" s="7">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="K308" s="7"/>
       <c r="L308" s="7"/>
@@ -11297,7 +11331,7 @@
       </c>
       <c r="D310" s="7"/>
       <c t="s" r="E310" s="7">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="F310" s="7">
         <v>320</v>
@@ -11309,15 +11343,15 @@
         <v>17</v>
       </c>
       <c t="s" r="I310" s="7">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c t="s" r="J310" s="7">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="K310" s="7"/>
       <c r="L310" s="7"/>
       <c t="s" r="M310" s="7">
-        <v>384</v>
+        <v>388</v>
       </c>
     </row>
     <row r="311" ht="14.25" customHeight="1">
@@ -11332,7 +11366,7 @@
       </c>
       <c r="D311" s="7"/>
       <c t="s" r="E311" s="7">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="F311" s="7">
         <v>320</v>
@@ -11344,15 +11378,15 @@
         <v>25</v>
       </c>
       <c t="s" r="I311" s="7">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c t="s" r="J311" s="7">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="K311" s="7"/>
       <c r="L311" s="7"/>
       <c t="s" r="M311" s="7">
-        <v>385</v>
+        <v>389</v>
       </c>
     </row>
     <row r="312" ht="14.25" customHeight="1">
@@ -11367,7 +11401,7 @@
       </c>
       <c r="D312" s="7"/>
       <c t="s" r="E312" s="7">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="F312" s="7">
         <v>320</v>
@@ -11379,10 +11413,10 @@
         <v>77</v>
       </c>
       <c t="s" r="I312" s="7">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c t="s" r="J312" s="7">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="K312" s="7"/>
       <c r="L312" s="7"/>
@@ -11400,7 +11434,7 @@
       </c>
       <c r="D313" s="7"/>
       <c t="s" r="E313" s="7">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="F313" s="7">
         <v>320</v>
@@ -11412,7 +11446,7 @@
         <v>25</v>
       </c>
       <c t="s" r="I313" s="7">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c t="s" r="J313" s="7">
         <v>45</v>
@@ -11433,7 +11467,7 @@
       </c>
       <c r="D314" s="7"/>
       <c t="s" r="E314" s="7">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="F314" s="7">
         <v>320</v>
@@ -11442,13 +11476,13 @@
         <v>25</v>
       </c>
       <c t="s" r="H314" s="8">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c t="s" r="I314" s="7">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c t="s" r="J314" s="7">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="K314" s="7"/>
       <c r="L314" s="7"/>
@@ -11466,22 +11500,22 @@
       </c>
       <c r="D315" s="7"/>
       <c t="s" r="E315" s="7">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="F315" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G315" s="8">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c t="s" r="H315" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I315" s="7">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c t="s" r="J315" s="7">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="K315" s="7"/>
       <c r="L315" s="7"/>
@@ -11507,14 +11541,14 @@
         <v>13</v>
       </c>
       <c t="s" r="B317" s="7">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c t="s" r="C317" s="7">
         <v>14</v>
       </c>
       <c r="D317" s="7"/>
       <c t="s" r="E317" s="7">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="F317" s="7">
         <v>321</v>
@@ -11523,20 +11557,20 @@
         <v>21</v>
       </c>
       <c t="s" r="H317" s="8">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c t="s" r="I317" s="7">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c t="s" r="J317" s="7">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c t="s" r="K317" s="7">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="L317" s="7"/>
       <c t="s" r="M317" s="7">
-        <v>390</v>
+        <v>394</v>
       </c>
     </row>
     <row r="318" ht="14.25" customHeight="1">
@@ -11551,22 +11585,22 @@
       </c>
       <c r="D318" s="7"/>
       <c t="s" r="E318" s="7">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="F318" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G318" s="8">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c t="s" r="H318" s="8">
         <v>30</v>
       </c>
       <c t="s" r="I318" s="7">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c t="s" r="J318" s="7">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="K318" s="7"/>
       <c r="L318" s="7"/>
@@ -11586,7 +11620,7 @@
       </c>
       <c r="D319" s="7"/>
       <c t="s" r="E319" s="7">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="F319" s="7">
         <v>321</v>
@@ -11598,15 +11632,15 @@
         <v>21</v>
       </c>
       <c t="s" r="I319" s="7">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c t="s" r="J319" s="7">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="K319" s="7"/>
       <c r="L319" s="7"/>
       <c t="s" r="M319" s="7">
-        <v>392</v>
+        <v>396</v>
       </c>
     </row>
     <row r="320" ht="15" customHeight="1">
@@ -11621,7 +11655,7 @@
       </c>
       <c r="D320" s="7"/>
       <c t="s" r="E320" s="7">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="F320" s="7">
         <v>321</v>
@@ -11630,13 +11664,13 @@
         <v>21</v>
       </c>
       <c t="s" r="H320" s="8">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c t="s" r="I320" s="7">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c t="s" r="J320" s="7">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="K320" s="7"/>
       <c r="L320" s="7"/>
@@ -11654,22 +11688,22 @@
       </c>
       <c r="D321" s="7"/>
       <c t="s" r="E321" s="7">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="F321" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G321" s="8">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c t="s" r="H321" s="8">
         <v>21</v>
       </c>
       <c t="s" r="I321" s="7">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c t="s" r="J321" s="7">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="K321" s="7"/>
       <c r="L321" s="7"/>
@@ -11680,14 +11714,14 @@
         <v>13</v>
       </c>
       <c r="B322" s="7">
-        <v>262</v>
+        <v>642</v>
       </c>
       <c t="s" r="C322" s="7">
         <v>14</v>
       </c>
       <c r="D322" s="7"/>
       <c t="s" r="E322" s="7">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="F322" s="7">
         <v>321</v>
@@ -11696,13 +11730,13 @@
         <v>21</v>
       </c>
       <c t="s" r="H322" s="8">
-        <v>36</v>
+        <v>99</v>
       </c>
       <c t="s" r="I322" s="7">
-        <v>354</v>
+        <v>338</v>
       </c>
       <c t="s" r="J322" s="7">
-        <v>327</v>
+        <v>211</v>
       </c>
       <c r="K322" s="7"/>
       <c r="L322" s="7"/>
@@ -11713,29 +11747,29 @@
         <v>13</v>
       </c>
       <c r="B323" s="7">
-        <v>263</v>
+        <v>643</v>
       </c>
       <c t="s" r="C323" s="7">
         <v>14</v>
       </c>
       <c r="D323" s="7"/>
       <c t="s" r="E323" s="7">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="F323" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G323" s="8">
-        <v>36</v>
+        <v>99</v>
       </c>
       <c t="s" r="H323" s="8">
         <v>21</v>
       </c>
       <c t="s" r="I323" s="7">
-        <v>304</v>
+        <v>62</v>
       </c>
       <c t="s" r="J323" s="7">
-        <v>335</v>
+        <v>251</v>
       </c>
       <c r="K323" s="7"/>
       <c r="L323" s="7"/>
@@ -11768,7 +11802,7 @@
       </c>
       <c r="D325" s="7"/>
       <c t="s" r="E325" s="7">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="F325" s="7">
         <v>320</v>
@@ -11777,18 +11811,18 @@
         <v>25</v>
       </c>
       <c t="s" r="H325" s="8">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c t="s" r="I325" s="7">
         <v>97</v>
       </c>
       <c t="s" r="J325" s="7">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="K325" s="7"/>
       <c r="L325" s="7"/>
       <c t="s" r="M325" s="7">
-        <v>394</v>
+        <v>398</v>
       </c>
     </row>
     <row r="326" ht="14.25" customHeight="1">
@@ -11803,27 +11837,27 @@
       </c>
       <c r="D326" s="7"/>
       <c t="s" r="E326" s="7">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="F326" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G326" s="8">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c t="s" r="H326" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I326" s="7">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c t="s" r="J326" s="7">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="K326" s="7"/>
       <c r="L326" s="7"/>
       <c t="s" r="M326" s="7">
-        <v>396</v>
+        <v>400</v>
       </c>
     </row>
     <row r="327" ht="14.25" customHeight="1">
@@ -11838,7 +11872,7 @@
       </c>
       <c r="D327" s="7"/>
       <c t="s" r="E327" s="7">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="F327" s="7">
         <v>320</v>
@@ -11850,7 +11884,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I327" s="7">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c t="s" r="J327" s="7">
         <v>44</v>
@@ -11871,7 +11905,7 @@
       </c>
       <c r="D328" s="7"/>
       <c t="s" r="E328" s="7">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="F328" s="7">
         <v>320</v>
@@ -11883,10 +11917,10 @@
         <v>25</v>
       </c>
       <c t="s" r="I328" s="7">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c t="s" r="J328" s="7">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="K328" s="7"/>
       <c r="L328" s="7"/>
@@ -11904,7 +11938,7 @@
       </c>
       <c r="D329" s="7"/>
       <c t="s" r="E329" s="7">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="F329" s="7">
         <v>320</v>
@@ -11916,10 +11950,10 @@
         <v>30</v>
       </c>
       <c t="s" r="I329" s="7">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c t="s" r="J329" s="7">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="K329" s="7"/>
       <c r="L329" s="7"/>
@@ -11937,7 +11971,7 @@
       </c>
       <c r="D330" s="7"/>
       <c t="s" r="E330" s="7">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="F330" s="7">
         <v>320</v>
@@ -11949,10 +11983,10 @@
         <v>25</v>
       </c>
       <c t="s" r="I330" s="7">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c t="s" r="J330" s="7">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="K330" s="7"/>
       <c r="L330" s="7"/>
@@ -11985,7 +12019,7 @@
       </c>
       <c r="D332" s="7"/>
       <c t="s" r="E332" s="7">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="F332" s="7">
         <v>320</v>
@@ -11997,15 +12031,15 @@
         <v>99</v>
       </c>
       <c t="s" r="I332" s="7">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c t="s" r="J332" s="7">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="K332" s="7"/>
       <c r="L332" s="7"/>
       <c t="s" r="M332" s="7">
-        <v>399</v>
+        <v>403</v>
       </c>
     </row>
     <row r="333" ht="14.25" customHeight="1">
@@ -12020,7 +12054,7 @@
       </c>
       <c r="D333" s="7"/>
       <c t="s" r="E333" s="7">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="F333" s="7">
         <v>320</v>
@@ -12032,7 +12066,7 @@
         <v>21</v>
       </c>
       <c t="s" r="I333" s="7">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c t="s" r="J333" s="7">
         <v>41</v>
@@ -12040,7 +12074,7 @@
       <c r="K333" s="7"/>
       <c r="L333" s="7"/>
       <c t="s" r="M333" s="7">
-        <v>400</v>
+        <v>404</v>
       </c>
     </row>
     <row r="334" ht="14.25" customHeight="1">
@@ -12055,7 +12089,7 @@
       </c>
       <c r="D334" s="7"/>
       <c t="s" r="E334" s="7">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="F334" s="7">
         <v>320</v>
@@ -12070,7 +12104,7 @@
         <v>27</v>
       </c>
       <c t="s" r="J334" s="7">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="K334" s="7"/>
       <c r="L334" s="7"/>
@@ -12088,7 +12122,7 @@
       </c>
       <c r="D335" s="7"/>
       <c t="s" r="E335" s="7">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="F335" s="7">
         <v>320</v>
@@ -12100,7 +12134,7 @@
         <v>21</v>
       </c>
       <c t="s" r="I335" s="7">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c t="s" r="J335" s="7">
         <v>72</v>
@@ -12121,7 +12155,7 @@
       </c>
       <c r="D336" s="7"/>
       <c t="s" r="E336" s="7">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="F336" s="7">
         <v>320</v>
@@ -12136,7 +12170,7 @@
         <v>49</v>
       </c>
       <c t="s" r="J336" s="7">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="K336" s="7"/>
       <c r="L336" s="7"/>
@@ -12169,7 +12203,7 @@
       </c>
       <c r="D338" s="7"/>
       <c t="s" r="E338" s="7">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="F338" s="7">
         <v>320</v>
@@ -12184,12 +12218,12 @@
         <v>67</v>
       </c>
       <c t="s" r="J338" s="7">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="K338" s="7"/>
       <c r="L338" s="7"/>
       <c t="s" r="M338" s="7">
-        <v>404</v>
+        <v>408</v>
       </c>
     </row>
     <row r="339" ht="14.25" customHeight="1">
@@ -12204,7 +12238,7 @@
       </c>
       <c r="D339" s="7"/>
       <c t="s" r="E339" s="7">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="F339" s="7">
         <v>320</v>
@@ -12216,10 +12250,10 @@
         <v>21</v>
       </c>
       <c t="s" r="I339" s="7">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c t="s" r="J339" s="7">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="K339" s="7"/>
       <c r="L339" s="7"/>
@@ -12237,7 +12271,7 @@
       </c>
       <c r="D340" s="7"/>
       <c t="s" r="E340" s="7">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="F340" s="7">
         <v>320</v>
@@ -12246,13 +12280,13 @@
         <v>21</v>
       </c>
       <c t="s" r="H340" s="8">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c t="s" r="I340" s="7">
         <v>83</v>
       </c>
       <c t="s" r="J340" s="7">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="K340" s="7"/>
       <c r="L340" s="7"/>
@@ -12270,19 +12304,19 @@
       </c>
       <c r="D341" s="7"/>
       <c t="s" r="E341" s="7">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="F341" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G341" s="8">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c t="s" r="H341" s="8">
         <v>21</v>
       </c>
       <c t="s" r="I341" s="7">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c t="s" r="J341" s="7">
         <v>61</v>
@@ -12303,7 +12337,7 @@
       </c>
       <c r="D342" s="7"/>
       <c t="s" r="E342" s="7">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="F342" s="7">
         <v>320</v>
@@ -12312,13 +12346,13 @@
         <v>21</v>
       </c>
       <c t="s" r="H342" s="8">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c t="s" r="I342" s="7">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c t="s" r="J342" s="7">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="K342" s="7"/>
       <c r="L342" s="7"/>
@@ -12336,19 +12370,19 @@
       </c>
       <c r="D343" s="7"/>
       <c t="s" r="E343" s="7">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="F343" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G343" s="8">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c t="s" r="H343" s="8">
         <v>21</v>
       </c>
       <c t="s" r="I343" s="7">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c t="s" r="J343" s="7">
         <v>74</v>
@@ -12384,7 +12418,7 @@
       </c>
       <c r="D345" s="7"/>
       <c t="s" r="E345" s="7">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="F345" s="7">
         <v>321</v>
@@ -12396,15 +12430,15 @@
         <v>43</v>
       </c>
       <c t="s" r="I345" s="7">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c t="s" r="J345" s="7">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="K345" s="7"/>
       <c r="L345" s="7"/>
       <c t="s" r="M345" s="7">
-        <v>137</v>
+        <v>140</v>
       </c>
     </row>
     <row r="346" ht="14.25" customHeight="1">
@@ -12419,7 +12453,7 @@
       </c>
       <c r="D346" s="7"/>
       <c t="s" r="E346" s="7">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="F346" s="7">
         <v>321</v>
@@ -12428,10 +12462,10 @@
         <v>43</v>
       </c>
       <c t="s" r="H346" s="8">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c t="s" r="I346" s="7">
-        <v>349</v>
+        <v>106</v>
       </c>
       <c t="s" r="J346" s="7">
         <v>31</v>
@@ -12452,13 +12486,13 @@
       </c>
       <c r="D347" s="7"/>
       <c t="s" r="E347" s="7">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="F347" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G347" s="8">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c t="s" r="H347" s="8">
         <v>43</v>
@@ -12467,7 +12501,7 @@
         <v>47</v>
       </c>
       <c t="s" r="J347" s="7">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="K347" s="7"/>
       <c r="L347" s="7"/>
@@ -12485,7 +12519,7 @@
       </c>
       <c r="D348" s="7"/>
       <c t="s" r="E348" s="7">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="F348" s="7">
         <v>321</v>
@@ -12497,10 +12531,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I348" s="7">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c t="s" r="J348" s="7">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="K348" s="7"/>
       <c r="L348" s="7"/>
@@ -12533,7 +12567,7 @@
       </c>
       <c r="D350" s="7"/>
       <c t="s" r="E350" s="7">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="F350" s="7">
         <v>320</v>
@@ -12542,10 +12576,10 @@
         <v>21</v>
       </c>
       <c t="s" r="H350" s="8">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c t="s" r="I350" s="7">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c t="s" r="J350" s="7">
         <v>78</v>
@@ -12553,7 +12587,7 @@
       <c r="K350" s="7"/>
       <c r="L350" s="7"/>
       <c t="s" r="M350" s="7">
-        <v>412</v>
+        <v>416</v>
       </c>
     </row>
     <row r="351" ht="14.25" customHeight="1">
@@ -12568,27 +12602,27 @@
       </c>
       <c r="D351" s="7"/>
       <c t="s" r="E351" s="7">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="F351" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G351" s="8">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c t="s" r="H351" s="8">
         <v>21</v>
       </c>
       <c t="s" r="I351" s="7">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c t="s" r="J351" s="7">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c r="K351" s="7"/>
       <c r="L351" s="7"/>
       <c t="s" r="M351" s="7">
-        <v>414</v>
+        <v>418</v>
       </c>
     </row>
     <row r="352" ht="14.25" customHeight="1">
@@ -12603,7 +12637,7 @@
       </c>
       <c r="D352" s="7"/>
       <c t="s" r="E352" s="7">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="F352" s="7">
         <v>320</v>
@@ -12612,10 +12646,10 @@
         <v>21</v>
       </c>
       <c t="s" r="H352" s="8">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c t="s" r="I352" s="7">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c t="s" r="J352" s="7">
         <v>41</v>
@@ -12623,7 +12657,7 @@
       <c r="K352" s="7"/>
       <c r="L352" s="7"/>
       <c t="s" r="M352" s="7">
-        <v>415</v>
+        <v>419</v>
       </c>
     </row>
     <row r="353" ht="14.25" customHeight="1">
@@ -12638,13 +12672,13 @@
       </c>
       <c r="D353" s="7"/>
       <c t="s" r="E353" s="7">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="F353" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G353" s="8">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c t="s" r="H353" s="8">
         <v>21</v>
@@ -12671,7 +12705,7 @@
       </c>
       <c r="D354" s="7"/>
       <c t="s" r="E354" s="7">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="F354" s="7">
         <v>320</v>
@@ -12680,20 +12714,20 @@
         <v>21</v>
       </c>
       <c t="s" r="H354" s="8">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c t="s" r="I354" s="7">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c t="s" r="J354" s="7">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c t="s" r="K354" s="7">
         <v>44</v>
       </c>
       <c r="L354" s="7"/>
       <c t="s" r="M354" s="7">
-        <v>237</v>
+        <v>241</v>
       </c>
     </row>
     <row r="355" ht="15" customHeight="1">
@@ -12708,29 +12742,29 @@
       </c>
       <c r="D355" s="7"/>
       <c t="s" r="E355" s="7">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="F355" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G355" s="8">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c t="s" r="H355" s="8">
         <v>21</v>
       </c>
       <c t="s" r="I355" s="7">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c t="s" r="J355" s="7">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c t="s" r="K355" s="7">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="L355" s="7"/>
       <c t="s" r="M355" s="7">
-        <v>417</v>
+        <v>421</v>
       </c>
     </row>
     <row r="356" ht="14.25" customHeight="1">
@@ -12745,7 +12779,7 @@
       </c>
       <c r="D356" s="7"/>
       <c t="s" r="E356" s="7">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="F356" s="7">
         <v>320</v>
@@ -12754,13 +12788,13 @@
         <v>21</v>
       </c>
       <c t="s" r="H356" s="8">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c t="s" r="I356" s="7">
         <v>49</v>
       </c>
       <c t="s" r="J356" s="7">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="K356" s="7"/>
       <c r="L356" s="7"/>
@@ -12778,22 +12812,22 @@
       </c>
       <c r="D357" s="7"/>
       <c t="s" r="E357" s="7">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="F357" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G357" s="8">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c t="s" r="H357" s="8">
         <v>21</v>
       </c>
       <c t="s" r="I357" s="7">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c t="s" r="J357" s="7">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="K357" s="7"/>
       <c r="L357" s="7"/>
@@ -12826,7 +12860,7 @@
       </c>
       <c r="D359" s="7"/>
       <c t="s" r="E359" s="7">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="F359" s="7">
         <v>320</v>
@@ -12835,10 +12869,10 @@
         <v>21</v>
       </c>
       <c t="s" r="H359" s="8">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c t="s" r="I359" s="7">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c t="s" r="J359" s="7">
         <v>23</v>
@@ -12846,7 +12880,7 @@
       <c r="K359" s="7"/>
       <c r="L359" s="7"/>
       <c t="s" r="M359" s="7">
-        <v>420</v>
+        <v>424</v>
       </c>
     </row>
     <row r="360" ht="15" customHeight="1">
@@ -12861,27 +12895,27 @@
       </c>
       <c r="D360" s="7"/>
       <c t="s" r="E360" s="7">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="F360" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G360" s="8">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c t="s" r="H360" s="8">
         <v>21</v>
       </c>
       <c t="s" r="I360" s="7">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c t="s" r="J360" s="7">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="K360" s="7"/>
       <c r="L360" s="7"/>
       <c t="s" r="M360" s="7">
-        <v>421</v>
+        <v>425</v>
       </c>
     </row>
     <row r="361" ht="14.25" customHeight="1">
@@ -12896,7 +12930,7 @@
       </c>
       <c r="D361" s="7"/>
       <c t="s" r="E361" s="7">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="F361" s="7">
         <v>320</v>
@@ -12905,13 +12939,13 @@
         <v>21</v>
       </c>
       <c t="s" r="H361" s="8">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c t="s" r="I361" s="7">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c t="s" r="J361" s="7">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="K361" s="7"/>
       <c r="L361" s="7"/>
@@ -12929,22 +12963,22 @@
       </c>
       <c r="D362" s="7"/>
       <c t="s" r="E362" s="7">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="F362" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G362" s="8">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c t="s" r="H362" s="8">
         <v>21</v>
       </c>
       <c t="s" r="I362" s="7">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c t="s" r="J362" s="7">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="K362" s="7"/>
       <c r="L362" s="7"/>
@@ -12962,7 +12996,7 @@
       </c>
       <c r="D363" s="7"/>
       <c t="s" r="E363" s="7">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="F363" s="7">
         <v>320</v>
@@ -12971,17 +13005,21 @@
         <v>21</v>
       </c>
       <c t="s" r="H363" s="8">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c t="s" r="I363" s="7">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c t="s" r="J363" s="7">
         <v>71</v>
       </c>
-      <c r="K363" s="7"/>
+      <c t="s" r="K363" s="7">
+        <v>224</v>
+      </c>
       <c r="L363" s="7"/>
-      <c r="M363" s="7"/>
+      <c t="s" r="M363" s="7">
+        <v>194</v>
+      </c>
     </row>
     <row r="364" ht="14.25" customHeight="1">
       <c t="s" r="A364" s="6">
@@ -12995,26 +13033,30 @@
       </c>
       <c r="D364" s="7"/>
       <c t="s" r="E364" s="7">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="F364" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G364" s="8">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c t="s" r="H364" s="8">
         <v>21</v>
       </c>
       <c t="s" r="I364" s="7">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c t="s" r="J364" s="7">
-        <v>327</v>
-      </c>
-      <c r="K364" s="7"/>
+        <v>331</v>
+      </c>
+      <c t="s" r="K364" s="7">
+        <v>109</v>
+      </c>
       <c r="L364" s="7"/>
-      <c r="M364" s="7"/>
+      <c t="s" r="M364" s="7">
+        <v>211</v>
+      </c>
     </row>
     <row r="365" ht="15" customHeight="1">
       <c t="s" r="A365" s="6">
@@ -13028,7 +13070,7 @@
       </c>
       <c r="D365" s="7"/>
       <c t="s" r="E365" s="7">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="F365" s="7">
         <v>320</v>
@@ -13040,10 +13082,10 @@
         <v>25</v>
       </c>
       <c t="s" r="I365" s="7">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c t="s" r="J365" s="7">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="K365" s="7"/>
       <c r="L365" s="7"/>
@@ -13061,7 +13103,7 @@
       </c>
       <c r="D366" s="7"/>
       <c t="s" r="E366" s="7">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="F366" s="7">
         <v>320</v>
@@ -13073,10 +13115,10 @@
         <v>21</v>
       </c>
       <c t="s" r="I366" s="7">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c t="s" r="J366" s="7">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="K366" s="7"/>
       <c r="L366" s="7"/>
@@ -13109,7 +13151,7 @@
       </c>
       <c r="D368" s="7"/>
       <c t="s" r="E368" s="7">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="F368" s="7">
         <v>321</v>
@@ -13121,28 +13163,30 @@
         <v>21</v>
       </c>
       <c t="s" r="I368" s="7">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c t="s" r="J368" s="7">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="K368" s="7"/>
       <c r="L368" s="7"/>
-      <c r="M368" s="7"/>
+      <c t="s" r="M368" s="7">
+        <v>169</v>
+      </c>
     </row>
     <row r="369" ht="14.25" customHeight="1">
       <c t="s" r="A369" s="6">
         <v>13</v>
       </c>
       <c r="B369" s="7">
-        <v>642</v>
+        <v>262</v>
       </c>
       <c t="s" r="C369" s="7">
         <v>14</v>
       </c>
       <c r="D369" s="7"/>
       <c t="s" r="E369" s="7">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="F369" s="7">
         <v>321</v>
@@ -13151,13 +13195,13 @@
         <v>21</v>
       </c>
       <c t="s" r="H369" s="8">
-        <v>99</v>
+        <v>36</v>
       </c>
       <c t="s" r="I369" s="7">
-        <v>334</v>
+        <v>358</v>
       </c>
       <c t="s" r="J369" s="7">
-        <v>207</v>
+        <v>331</v>
       </c>
       <c r="K369" s="7"/>
       <c r="L369" s="7"/>
@@ -13168,29 +13212,29 @@
         <v>13</v>
       </c>
       <c r="B370" s="7">
-        <v>643</v>
+        <v>263</v>
       </c>
       <c t="s" r="C370" s="7">
         <v>14</v>
       </c>
       <c r="D370" s="7"/>
       <c t="s" r="E370" s="7">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="F370" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G370" s="8">
-        <v>99</v>
+        <v>36</v>
       </c>
       <c t="s" r="H370" s="8">
         <v>21</v>
       </c>
       <c t="s" r="I370" s="7">
-        <v>62</v>
+        <v>308</v>
       </c>
       <c t="s" r="J370" s="7">
-        <v>247</v>
+        <v>339</v>
       </c>
       <c r="K370" s="7"/>
       <c r="L370" s="7"/>
@@ -13223,7 +13267,7 @@
       </c>
       <c r="D372" s="7"/>
       <c t="s" r="E372" s="7">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c r="F372" s="7">
         <v>320</v>
@@ -13235,15 +13279,15 @@
         <v>25</v>
       </c>
       <c t="s" r="I372" s="7">
-        <v>425</v>
+        <v>429</v>
       </c>
       <c t="s" r="J372" s="7">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="K372" s="7"/>
       <c r="L372" s="7"/>
       <c t="s" r="M372" s="7">
-        <v>426</v>
+        <v>430</v>
       </c>
     </row>
     <row r="373" ht="14.25" customHeight="1">
@@ -13258,7 +13302,7 @@
       </c>
       <c r="D373" s="7"/>
       <c t="s" r="E373" s="7">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c r="F373" s="7">
         <v>320</v>
@@ -13270,15 +13314,15 @@
         <v>21</v>
       </c>
       <c t="s" r="I373" s="7">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c t="s" r="J373" s="7">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="K373" s="7"/>
       <c r="L373" s="7"/>
       <c t="s" r="M373" s="7">
-        <v>155</v>
+        <v>157</v>
       </c>
     </row>
     <row r="374" ht="14.25" customHeight="1">
@@ -13293,7 +13337,7 @@
       </c>
       <c r="D374" s="7"/>
       <c t="s" r="E374" s="7">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c r="F374" s="7">
         <v>320</v>
@@ -13305,10 +13349,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I374" s="7">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c t="s" r="J374" s="7">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="K374" s="7"/>
       <c r="L374" s="7"/>
@@ -13326,7 +13370,7 @@
       </c>
       <c r="D375" s="7"/>
       <c t="s" r="E375" s="7">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c r="F375" s="7">
         <v>320</v>
@@ -13338,7 +13382,7 @@
         <v>43</v>
       </c>
       <c t="s" r="I375" s="7">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c t="s" r="J375" s="7">
         <v>81</v>
@@ -13348,7 +13392,7 @@
       </c>
       <c r="L375" s="7"/>
       <c t="s" r="M375" s="7">
-        <v>302</v>
+        <v>306</v>
       </c>
     </row>
     <row r="376" ht="14.25" customHeight="1">
@@ -13363,7 +13407,7 @@
       </c>
       <c r="D376" s="7"/>
       <c t="s" r="E376" s="7">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c r="F376" s="7">
         <v>320</v>
@@ -13378,7 +13422,7 @@
         <v>83</v>
       </c>
       <c t="s" r="J376" s="7">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c t="s" r="K376" s="7">
         <v>45</v>
@@ -13400,7 +13444,7 @@
       </c>
       <c r="D377" s="7"/>
       <c t="s" r="E377" s="7">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c r="F377" s="7">
         <v>320</v>
@@ -13412,17 +13456,17 @@
         <v>21</v>
       </c>
       <c t="s" r="I377" s="7">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c t="s" r="J377" s="7">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c t="s" r="K377" s="7">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="L377" s="7"/>
       <c t="s" r="M377" s="7">
-        <v>296</v>
+        <v>299</v>
       </c>
     </row>
     <row r="378" ht="14.25" customHeight="1">
@@ -13452,7 +13496,7 @@
       </c>
       <c r="D379" s="7"/>
       <c t="s" r="E379" s="7">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="F379" s="7">
         <v>320</v>
@@ -13461,13 +13505,13 @@
         <v>21</v>
       </c>
       <c t="s" r="H379" s="8">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c t="s" r="I379" s="7">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c t="s" r="J379" s="7">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="K379" s="7"/>
       <c r="L379" s="7"/>
@@ -13487,26 +13531,28 @@
       </c>
       <c r="D380" s="7"/>
       <c t="s" r="E380" s="7">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="F380" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G380" s="8">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c t="s" r="H380" s="8">
         <v>21</v>
       </c>
       <c t="s" r="I380" s="7">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c t="s" r="J380" s="7">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="K380" s="7"/>
       <c r="L380" s="7"/>
-      <c r="M380" s="7"/>
+      <c t="s" r="M380" s="7">
+        <v>433</v>
+      </c>
     </row>
     <row r="381" ht="14.25" customHeight="1">
       <c t="s" r="A381" s="6">
@@ -13520,7 +13566,7 @@
       </c>
       <c r="D381" s="7"/>
       <c t="s" r="E381" s="7">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="F381" s="7">
         <v>320</v>
@@ -13529,13 +13575,13 @@
         <v>21</v>
       </c>
       <c t="s" r="H381" s="8">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c t="s" r="I381" s="7">
         <v>59</v>
       </c>
       <c t="s" r="J381" s="7">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="K381" s="7"/>
       <c r="L381" s="7"/>
@@ -13553,22 +13599,22 @@
       </c>
       <c r="D382" s="7"/>
       <c t="s" r="E382" s="7">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="F382" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G382" s="8">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c t="s" r="H382" s="8">
         <v>21</v>
       </c>
       <c t="s" r="I382" s="7">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c t="s" r="J382" s="7">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="K382" s="7"/>
       <c r="L382" s="7"/>
@@ -13586,7 +13632,7 @@
       </c>
       <c r="D383" s="7"/>
       <c t="s" r="E383" s="7">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="F383" s="7">
         <v>320</v>
@@ -13595,13 +13641,13 @@
         <v>21</v>
       </c>
       <c t="s" r="H383" s="8">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c t="s" r="I383" s="7">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c t="s" r="J383" s="7">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="K383" s="7"/>
       <c r="L383" s="7"/>
@@ -13619,22 +13665,22 @@
       </c>
       <c r="D384" s="7"/>
       <c t="s" r="E384" s="7">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="F384" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G384" s="8">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c t="s" r="H384" s="8">
         <v>21</v>
       </c>
       <c t="s" r="I384" s="7">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c t="s" r="J384" s="7">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="K384" s="7"/>
       <c r="L384" s="7"/>
@@ -13667,7 +13713,7 @@
       </c>
       <c r="D386" s="7"/>
       <c t="s" r="E386" s="7">
-        <v>429</v>
+        <v>434</v>
       </c>
       <c r="F386" s="7">
         <v>321</v>
@@ -13676,17 +13722,19 @@
         <v>21</v>
       </c>
       <c t="s" r="H386" s="8">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c t="s" r="I386" s="7">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c t="s" r="J386" s="7">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="K386" s="7"/>
       <c r="L386" s="7"/>
-      <c r="M386" s="7"/>
+      <c t="s" r="M386" s="7">
+        <v>435</v>
+      </c>
     </row>
     <row r="387" ht="14.25" customHeight="1">
       <c t="s" r="A387" s="6">
@@ -13700,22 +13748,22 @@
       </c>
       <c r="D387" s="7"/>
       <c t="s" r="E387" s="7">
-        <v>429</v>
+        <v>434</v>
       </c>
       <c r="F387" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G387" s="8">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c t="s" r="H387" s="8">
         <v>21</v>
       </c>
       <c t="s" r="I387" s="7">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c t="s" r="J387" s="7">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="K387" s="7"/>
       <c r="L387" s="7"/>
@@ -13733,7 +13781,7 @@
       </c>
       <c r="D388" s="7"/>
       <c t="s" r="E388" s="7">
-        <v>429</v>
+        <v>434</v>
       </c>
       <c r="F388" s="7">
         <v>321</v>
@@ -13742,7 +13790,7 @@
         <v>21</v>
       </c>
       <c t="s" r="H388" s="8">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c t="s" r="I388" s="7">
         <v>71</v>
@@ -13766,22 +13814,22 @@
       </c>
       <c r="D389" s="7"/>
       <c t="s" r="E389" s="7">
-        <v>429</v>
+        <v>434</v>
       </c>
       <c r="F389" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G389" s="8">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c t="s" r="H389" s="8">
         <v>21</v>
       </c>
       <c t="s" r="I389" s="7">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c t="s" r="J389" s="7">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="K389" s="7"/>
       <c r="L389" s="7"/>
@@ -13799,7 +13847,7 @@
       </c>
       <c r="D390" s="7"/>
       <c t="s" r="E390" s="7">
-        <v>429</v>
+        <v>434</v>
       </c>
       <c r="F390" s="7">
         <v>321</v>
@@ -13811,10 +13859,10 @@
         <v>25</v>
       </c>
       <c t="s" r="I390" s="7">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c t="s" r="J390" s="7">
-        <v>430</v>
+        <v>436</v>
       </c>
       <c r="K390" s="7"/>
       <c r="L390" s="7"/>
@@ -13832,7 +13880,7 @@
       </c>
       <c r="D391" s="7"/>
       <c t="s" r="E391" s="7">
-        <v>429</v>
+        <v>434</v>
       </c>
       <c r="F391" s="7">
         <v>321</v>
@@ -13841,13 +13889,13 @@
         <v>25</v>
       </c>
       <c t="s" r="H391" s="8">
-        <v>431</v>
+        <v>437</v>
       </c>
       <c t="s" r="I391" s="7">
         <v>85</v>
       </c>
       <c t="s" r="J391" s="7">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="K391" s="7"/>
       <c r="L391" s="7"/>
@@ -13880,7 +13928,7 @@
       </c>
       <c r="D393" s="7"/>
       <c t="s" r="E393" s="7">
-        <v>432</v>
+        <v>438</v>
       </c>
       <c r="F393" s="7">
         <v>320</v>
@@ -13889,13 +13937,13 @@
         <v>25</v>
       </c>
       <c t="s" r="H393" s="8">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c t="s" r="I393" s="7">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c t="s" r="J393" s="7">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="K393" s="7"/>
       <c r="L393" s="7"/>
@@ -13913,22 +13961,22 @@
       </c>
       <c r="D394" s="7"/>
       <c t="s" r="E394" s="7">
-        <v>432</v>
+        <v>438</v>
       </c>
       <c r="F394" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G394" s="8">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c t="s" r="H394" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I394" s="7">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c t="s" r="J394" s="7">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="K394" s="7"/>
       <c r="L394" s="7"/>
@@ -13946,7 +13994,7 @@
       </c>
       <c r="D395" s="7"/>
       <c t="s" r="E395" s="7">
-        <v>432</v>
+        <v>438</v>
       </c>
       <c r="F395" s="7">
         <v>320</v>
@@ -13955,10 +14003,10 @@
         <v>25</v>
       </c>
       <c t="s" r="H395" s="8">
-        <v>433</v>
+        <v>439</v>
       </c>
       <c t="s" r="I395" s="7">
-        <v>434</v>
+        <v>440</v>
       </c>
       <c t="s" r="J395" s="7">
         <v>67</v>
@@ -13994,7 +14042,7 @@
       </c>
       <c r="D397" s="7"/>
       <c t="s" r="E397" s="7">
-        <v>435</v>
+        <v>441</v>
       </c>
       <c r="F397" s="7">
         <v>320</v>
@@ -14006,7 +14054,7 @@
         <v>77</v>
       </c>
       <c t="s" r="I397" s="7">
-        <v>436</v>
+        <v>442</v>
       </c>
       <c t="s" r="J397" s="7">
         <v>19</v>
@@ -14014,7 +14062,7 @@
       <c r="K397" s="7"/>
       <c r="L397" s="7"/>
       <c t="s" r="M397" s="7">
-        <v>437</v>
+        <v>443</v>
       </c>
     </row>
     <row r="398" ht="14.25" customHeight="1">
@@ -14029,7 +14077,7 @@
       </c>
       <c r="D398" s="7"/>
       <c t="s" r="E398" s="7">
-        <v>435</v>
+        <v>441</v>
       </c>
       <c r="F398" s="7">
         <v>320</v>
@@ -14044,12 +14092,12 @@
         <v>88</v>
       </c>
       <c t="s" r="J398" s="7">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="K398" s="7"/>
       <c r="L398" s="7"/>
       <c t="s" r="M398" s="7">
-        <v>438</v>
+        <v>444</v>
       </c>
     </row>
     <row r="399" ht="14.25" customHeight="1">
@@ -14064,7 +14112,7 @@
       </c>
       <c r="D399" s="7"/>
       <c t="s" r="E399" s="7">
-        <v>435</v>
+        <v>441</v>
       </c>
       <c r="F399" s="7">
         <v>320</v>
@@ -14073,17 +14121,19 @@
         <v>25</v>
       </c>
       <c t="s" r="H399" s="8">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c t="s" r="I399" s="7">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c t="s" r="J399" s="7">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="K399" s="7"/>
       <c r="L399" s="7"/>
-      <c r="M399" s="7"/>
+      <c t="s" r="M399" s="7">
+        <v>445</v>
+      </c>
     </row>
     <row r="400" ht="15" customHeight="1">
       <c t="s" r="A400" s="6">
@@ -14097,22 +14147,22 @@
       </c>
       <c r="D400" s="7"/>
       <c t="s" r="E400" s="7">
-        <v>435</v>
+        <v>441</v>
       </c>
       <c r="F400" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G400" s="8">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c t="s" r="H400" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I400" s="7">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c t="s" r="J400" s="7">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="K400" s="7"/>
       <c r="L400" s="7"/>
@@ -14130,7 +14180,7 @@
       </c>
       <c r="D401" s="7"/>
       <c t="s" r="E401" s="7">
-        <v>435</v>
+        <v>441</v>
       </c>
       <c r="F401" s="7">
         <v>320</v>
@@ -14139,13 +14189,13 @@
         <v>25</v>
       </c>
       <c t="s" r="H401" s="8">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c t="s" r="I401" s="7">
         <v>83</v>
       </c>
       <c t="s" r="J401" s="7">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="K401" s="7"/>
       <c r="L401" s="7"/>
@@ -14163,19 +14213,19 @@
       </c>
       <c r="D402" s="7"/>
       <c t="s" r="E402" s="7">
-        <v>435</v>
+        <v>441</v>
       </c>
       <c r="F402" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G402" s="8">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c t="s" r="H402" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I402" s="7">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c t="s" r="J402" s="7">
         <v>33</v>
@@ -14211,7 +14261,7 @@
       </c>
       <c r="D404" s="7"/>
       <c t="s" r="E404" s="7">
-        <v>439</v>
+        <v>446</v>
       </c>
       <c r="F404" s="7">
         <v>321</v>
@@ -14223,15 +14273,15 @@
         <v>87</v>
       </c>
       <c t="s" r="I404" s="7">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c t="s" r="J404" s="7">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="K404" s="7"/>
       <c r="L404" s="7"/>
       <c t="s" r="M404" s="7">
-        <v>122</v>
+        <v>125</v>
       </c>
     </row>
     <row r="405" ht="15" customHeight="1">
@@ -14246,7 +14296,7 @@
       </c>
       <c r="D405" s="7"/>
       <c t="s" r="E405" s="7">
-        <v>439</v>
+        <v>446</v>
       </c>
       <c r="F405" s="7">
         <v>321</v>
@@ -14258,10 +14308,10 @@
         <v>21</v>
       </c>
       <c t="s" r="I405" s="7">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c t="s" r="J405" s="7">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="K405" s="7"/>
       <c r="L405" s="7"/>
@@ -14279,7 +14329,7 @@
       </c>
       <c r="D406" s="7"/>
       <c t="s" r="E406" s="7">
-        <v>439</v>
+        <v>446</v>
       </c>
       <c r="F406" s="7">
         <v>321</v>
@@ -14288,13 +14338,13 @@
         <v>21</v>
       </c>
       <c t="s" r="H406" s="8">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c t="s" r="I406" s="7">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c t="s" r="J406" s="7">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="K406" s="7"/>
       <c r="L406" s="7"/>
@@ -14312,22 +14362,22 @@
       </c>
       <c r="D407" s="7"/>
       <c t="s" r="E407" s="7">
-        <v>439</v>
+        <v>446</v>
       </c>
       <c r="F407" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G407" s="8">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c t="s" r="H407" s="8">
         <v>21</v>
       </c>
       <c t="s" r="I407" s="7">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c t="s" r="J407" s="7">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="K407" s="7"/>
       <c r="L407" s="7"/>
@@ -14345,7 +14395,7 @@
       </c>
       <c r="D408" s="7"/>
       <c t="s" r="E408" s="7">
-        <v>439</v>
+        <v>446</v>
       </c>
       <c r="F408" s="7">
         <v>321</v>
@@ -14354,13 +14404,13 @@
         <v>21</v>
       </c>
       <c t="s" r="H408" s="8">
-        <v>440</v>
+        <v>447</v>
       </c>
       <c t="s" r="I408" s="7">
-        <v>441</v>
+        <v>448</v>
       </c>
       <c t="s" r="J408" s="7">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="K408" s="7"/>
       <c r="L408" s="7"/>
@@ -14378,22 +14428,22 @@
       </c>
       <c r="D409" s="7"/>
       <c t="s" r="E409" s="7">
-        <v>439</v>
+        <v>446</v>
       </c>
       <c r="F409" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G409" s="8">
-        <v>440</v>
+        <v>447</v>
       </c>
       <c t="s" r="H409" s="8">
         <v>21</v>
       </c>
       <c t="s" r="I409" s="7">
-        <v>442</v>
+        <v>449</v>
       </c>
       <c t="s" r="J409" s="7">
-        <v>443</v>
+        <v>450</v>
       </c>
       <c r="K409" s="7"/>
       <c r="L409" s="7"/>
@@ -14426,7 +14476,7 @@
       </c>
       <c r="D411" s="7"/>
       <c t="s" r="E411" s="7">
-        <v>444</v>
+        <v>451</v>
       </c>
       <c r="F411" s="7">
         <v>321</v>
@@ -14438,15 +14488,15 @@
         <v>77</v>
       </c>
       <c t="s" r="I411" s="7">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c t="s" r="J411" s="7">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="K411" s="7"/>
       <c r="L411" s="7"/>
       <c t="s" r="M411" s="7">
-        <v>445</v>
+        <v>452</v>
       </c>
     </row>
     <row r="412" ht="14.25" customHeight="1">
@@ -14461,7 +14511,7 @@
       </c>
       <c r="D412" s="7"/>
       <c t="s" r="E412" s="7">
-        <v>444</v>
+        <v>451</v>
       </c>
       <c r="F412" s="7">
         <v>321</v>
@@ -14476,12 +14526,12 @@
         <v>56</v>
       </c>
       <c t="s" r="J412" s="7">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="K412" s="7"/>
       <c r="L412" s="7"/>
       <c t="s" r="M412" s="7">
-        <v>446</v>
+        <v>453</v>
       </c>
     </row>
     <row r="413" ht="14.25" customHeight="1">
@@ -14496,7 +14546,7 @@
       </c>
       <c r="D413" s="7"/>
       <c t="s" r="E413" s="7">
-        <v>444</v>
+        <v>451</v>
       </c>
       <c r="F413" s="7">
         <v>321</v>
@@ -14508,10 +14558,10 @@
         <v>21</v>
       </c>
       <c t="s" r="I413" s="7">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c t="s" r="J413" s="7">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="K413" s="7"/>
       <c r="L413" s="7"/>
@@ -14529,7 +14579,7 @@
       </c>
       <c r="D414" s="7"/>
       <c t="s" r="E414" s="7">
-        <v>444</v>
+        <v>451</v>
       </c>
       <c r="F414" s="7">
         <v>321</v>
@@ -14541,7 +14591,7 @@
         <v>25</v>
       </c>
       <c t="s" r="I414" s="7">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c t="s" r="J414" s="7">
         <v>47</v>
@@ -14562,7 +14612,7 @@
       </c>
       <c r="D415" s="7"/>
       <c t="s" r="E415" s="7">
-        <v>444</v>
+        <v>451</v>
       </c>
       <c r="F415" s="7">
         <v>321</v>
@@ -14577,7 +14627,7 @@
         <v>33</v>
       </c>
       <c t="s" r="J415" s="7">
-        <v>447</v>
+        <v>454</v>
       </c>
       <c r="K415" s="7"/>
       <c r="L415" s="7"/>
@@ -14610,7 +14660,7 @@
       </c>
       <c r="D417" s="7"/>
       <c t="s" r="E417" s="7">
-        <v>448</v>
+        <v>455</v>
       </c>
       <c r="F417" s="7">
         <v>321</v>
@@ -14622,15 +14672,15 @@
         <v>77</v>
       </c>
       <c t="s" r="I417" s="7">
-        <v>449</v>
+        <v>456</v>
       </c>
       <c t="s" r="J417" s="7">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="K417" s="7"/>
       <c r="L417" s="7"/>
       <c t="s" r="M417" s="7">
-        <v>450</v>
+        <v>457</v>
       </c>
     </row>
     <row r="418" ht="14.25" customHeight="1">
@@ -14645,7 +14695,7 @@
       </c>
       <c r="D418" s="7"/>
       <c t="s" r="E418" s="7">
-        <v>448</v>
+        <v>455</v>
       </c>
       <c r="F418" s="7">
         <v>321</v>
@@ -14657,15 +14707,15 @@
         <v>99</v>
       </c>
       <c t="s" r="I418" s="7">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c t="s" r="J418" s="7">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="K418" s="7"/>
       <c r="L418" s="7"/>
       <c t="s" r="M418" s="7">
-        <v>451</v>
+        <v>458</v>
       </c>
     </row>
     <row r="419" ht="14.25" customHeight="1">
@@ -14680,7 +14730,7 @@
       </c>
       <c r="D419" s="7"/>
       <c t="s" r="E419" s="7">
-        <v>448</v>
+        <v>455</v>
       </c>
       <c r="F419" s="7">
         <v>321</v>
@@ -14695,12 +14745,12 @@
         <v>67</v>
       </c>
       <c t="s" r="J419" s="7">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="K419" s="7"/>
       <c r="L419" s="7"/>
       <c t="s" r="M419" s="7">
-        <v>452</v>
+        <v>459</v>
       </c>
     </row>
     <row r="420" ht="15" customHeight="1">
@@ -14715,7 +14765,7 @@
       </c>
       <c r="D420" s="7"/>
       <c t="s" r="E420" s="7">
-        <v>448</v>
+        <v>455</v>
       </c>
       <c r="F420" s="7">
         <v>321</v>
@@ -14727,10 +14777,10 @@
         <v>99</v>
       </c>
       <c t="s" r="I420" s="7">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c t="s" r="J420" s="7">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="K420" s="7"/>
       <c r="L420" s="7"/>
@@ -14748,7 +14798,7 @@
       </c>
       <c r="D421" s="7"/>
       <c t="s" r="E421" s="7">
-        <v>448</v>
+        <v>455</v>
       </c>
       <c r="F421" s="7">
         <v>321</v>
@@ -14757,13 +14807,13 @@
         <v>99</v>
       </c>
       <c t="s" r="H421" s="8">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c t="s" r="I421" s="7">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c t="s" r="J421" s="7">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="K421" s="7"/>
       <c r="L421" s="7"/>
@@ -14781,19 +14831,19 @@
       </c>
       <c r="D422" s="7"/>
       <c t="s" r="E422" s="7">
-        <v>448</v>
+        <v>455</v>
       </c>
       <c r="F422" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G422" s="8">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c t="s" r="H422" s="8">
         <v>21</v>
       </c>
       <c t="s" r="I422" s="7">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c t="s" r="J422" s="7">
         <v>33</v>
@@ -14814,7 +14864,7 @@
       </c>
       <c r="D423" s="7"/>
       <c t="s" r="E423" s="7">
-        <v>448</v>
+        <v>455</v>
       </c>
       <c r="F423" s="7">
         <v>321</v>
@@ -14826,10 +14876,10 @@
         <v>99</v>
       </c>
       <c t="s" r="I423" s="7">
-        <v>453</v>
+        <v>460</v>
       </c>
       <c t="s" r="J423" s="7">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="K423" s="7"/>
       <c r="L423" s="7"/>
@@ -14862,7 +14912,7 @@
       </c>
       <c r="D425" s="7"/>
       <c t="s" r="E425" s="7">
-        <v>454</v>
+        <v>461</v>
       </c>
       <c r="F425" s="7">
         <v>321</v>
@@ -14871,18 +14921,18 @@
         <v>21</v>
       </c>
       <c t="s" r="H425" s="8">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c t="s" r="I425" s="7">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c t="s" r="J425" s="7">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="K425" s="7"/>
       <c r="L425" s="7"/>
       <c t="s" r="M425" s="7">
-        <v>455</v>
+        <v>462</v>
       </c>
     </row>
     <row r="426" ht="14.25" customHeight="1">
@@ -14897,19 +14947,19 @@
       </c>
       <c r="D426" s="7"/>
       <c t="s" r="E426" s="7">
-        <v>454</v>
+        <v>461</v>
       </c>
       <c r="F426" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G426" s="8">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c t="s" r="H426" s="8">
         <v>21</v>
       </c>
       <c t="s" r="I426" s="7">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c t="s" r="J426" s="7">
         <v>67</v>
@@ -14917,7 +14967,7 @@
       <c r="K426" s="7"/>
       <c r="L426" s="7"/>
       <c t="s" r="M426" s="7">
-        <v>456</v>
+        <v>463</v>
       </c>
     </row>
     <row r="427" ht="14.25" customHeight="1">
@@ -14932,7 +14982,7 @@
       </c>
       <c r="D427" s="7"/>
       <c t="s" r="E427" s="7">
-        <v>454</v>
+        <v>461</v>
       </c>
       <c r="F427" s="7">
         <v>321</v>
@@ -14944,17 +14994,17 @@
         <v>43</v>
       </c>
       <c t="s" r="I427" s="7">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c t="s" r="J427" s="7">
         <v>26</v>
       </c>
       <c t="s" r="K427" s="7">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="L427" s="7"/>
       <c t="s" r="M427" s="7">
-        <v>403</v>
+        <v>407</v>
       </c>
     </row>
     <row r="428" ht="14.25" customHeight="1">
@@ -14969,7 +15019,7 @@
       </c>
       <c r="D428" s="7"/>
       <c t="s" r="E428" s="7">
-        <v>454</v>
+        <v>461</v>
       </c>
       <c r="F428" s="7">
         <v>321</v>
@@ -14981,17 +15031,17 @@
         <v>21</v>
       </c>
       <c t="s" r="I428" s="7">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c t="s" r="J428" s="7">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c t="s" r="K428" s="7">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="L428" s="7"/>
       <c t="s" r="M428" s="7">
-        <v>262</v>
+        <v>265</v>
       </c>
     </row>
     <row r="429" ht="14.25" customHeight="1">
@@ -15006,7 +15056,7 @@
       </c>
       <c r="D429" s="7"/>
       <c t="s" r="E429" s="7">
-        <v>454</v>
+        <v>461</v>
       </c>
       <c r="F429" s="7">
         <v>321</v>
@@ -15021,7 +15071,7 @@
         <v>45</v>
       </c>
       <c t="s" r="J429" s="7">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="K429" s="7"/>
       <c r="L429" s="7"/>
@@ -15054,7 +15104,7 @@
       </c>
       <c r="D431" s="7"/>
       <c t="s" r="E431" s="7">
-        <v>457</v>
+        <v>464</v>
       </c>
       <c r="F431" s="7">
         <v>320</v>
@@ -15063,18 +15113,18 @@
         <v>25</v>
       </c>
       <c t="s" r="H431" s="8">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c t="s" r="I431" s="7">
-        <v>425</v>
+        <v>429</v>
       </c>
       <c t="s" r="J431" s="7">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="K431" s="7"/>
       <c r="L431" s="7"/>
       <c t="s" r="M431" s="7">
-        <v>458</v>
+        <v>465</v>
       </c>
     </row>
     <row r="432" ht="14.25" customHeight="1">
@@ -15089,13 +15139,13 @@
       </c>
       <c r="D432" s="7"/>
       <c t="s" r="E432" s="7">
-        <v>457</v>
+        <v>464</v>
       </c>
       <c r="F432" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G432" s="8">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c t="s" r="H432" s="8">
         <v>25</v>
@@ -15104,12 +15154,12 @@
         <v>38</v>
       </c>
       <c t="s" r="J432" s="7">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="K432" s="7"/>
       <c r="L432" s="7"/>
       <c t="s" r="M432" s="7">
-        <v>459</v>
+        <v>466</v>
       </c>
     </row>
     <row r="433" ht="14.25" customHeight="1">
@@ -15124,7 +15174,7 @@
       </c>
       <c r="D433" s="7"/>
       <c t="s" r="E433" s="7">
-        <v>457</v>
+        <v>464</v>
       </c>
       <c r="F433" s="7">
         <v>320</v>
@@ -15133,18 +15183,18 @@
         <v>25</v>
       </c>
       <c t="s" r="H433" s="8">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c t="s" r="I433" s="7">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c t="s" r="J433" s="7">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="K433" s="7"/>
       <c r="L433" s="7"/>
       <c t="s" r="M433" s="7">
-        <v>460</v>
+        <v>467</v>
       </c>
     </row>
     <row r="434" ht="14.25" customHeight="1">
@@ -15159,22 +15209,22 @@
       </c>
       <c r="D434" s="7"/>
       <c t="s" r="E434" s="7">
-        <v>457</v>
+        <v>464</v>
       </c>
       <c r="F434" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G434" s="8">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c t="s" r="H434" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I434" s="7">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c t="s" r="J434" s="7">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="K434" s="7"/>
       <c r="L434" s="7"/>
@@ -15192,7 +15242,7 @@
       </c>
       <c r="D435" s="7"/>
       <c t="s" r="E435" s="7">
-        <v>457</v>
+        <v>464</v>
       </c>
       <c r="F435" s="7">
         <v>320</v>
@@ -15201,13 +15251,13 @@
         <v>25</v>
       </c>
       <c t="s" r="H435" s="8">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c t="s" r="I435" s="7">
         <v>45</v>
       </c>
       <c t="s" r="J435" s="7">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="K435" s="7"/>
       <c r="L435" s="7"/>
@@ -15225,19 +15275,19 @@
       </c>
       <c r="D436" s="7"/>
       <c t="s" r="E436" s="7">
-        <v>457</v>
+        <v>464</v>
       </c>
       <c r="F436" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G436" s="8">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c t="s" r="H436" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I436" s="7">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c t="s" r="J436" s="7">
         <v>32</v>
@@ -15258,7 +15308,7 @@
       </c>
       <c r="D437" s="7"/>
       <c t="s" r="E437" s="7">
-        <v>457</v>
+        <v>464</v>
       </c>
       <c r="F437" s="7">
         <v>320</v>
@@ -15270,10 +15320,10 @@
         <v>99</v>
       </c>
       <c t="s" r="I437" s="7">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c t="s" r="J437" s="7">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="K437" s="7"/>
       <c r="L437" s="7"/>
@@ -15291,7 +15341,7 @@
       </c>
       <c r="D438" s="7"/>
       <c t="s" r="E438" s="7">
-        <v>457</v>
+        <v>464</v>
       </c>
       <c r="F438" s="7">
         <v>320</v>
@@ -15303,10 +15353,10 @@
         <v>25</v>
       </c>
       <c t="s" r="I438" s="7">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c t="s" r="J438" s="7">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="K438" s="7"/>
       <c r="L438" s="7"/>
@@ -15339,7 +15389,7 @@
       </c>
       <c r="D440" s="7"/>
       <c t="s" r="E440" s="7">
-        <v>461</v>
+        <v>468</v>
       </c>
       <c r="F440" s="7">
         <v>321</v>
@@ -15348,18 +15398,18 @@
         <v>21</v>
       </c>
       <c t="s" r="H440" s="8">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c t="s" r="I440" s="7">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c t="s" r="J440" s="7">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="K440" s="7"/>
       <c r="L440" s="7"/>
       <c t="s" r="M440" s="7">
-        <v>254</v>
+        <v>105</v>
       </c>
     </row>
     <row r="441" ht="14.25" customHeight="1">
@@ -15374,19 +15424,19 @@
       </c>
       <c r="D441" s="7"/>
       <c t="s" r="E441" s="7">
-        <v>461</v>
+        <v>468</v>
       </c>
       <c r="F441" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G441" s="8">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c t="s" r="H441" s="8">
         <v>21</v>
       </c>
       <c t="s" r="I441" s="7">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c t="s" r="J441" s="7">
         <v>71</v>
@@ -15407,7 +15457,7 @@
       </c>
       <c r="D442" s="7"/>
       <c t="s" r="E442" s="7">
-        <v>461</v>
+        <v>468</v>
       </c>
       <c r="F442" s="7">
         <v>321</v>
@@ -15416,13 +15466,13 @@
         <v>21</v>
       </c>
       <c t="s" r="H442" s="8">
-        <v>462</v>
+        <v>469</v>
       </c>
       <c t="s" r="I442" s="7">
         <v>33</v>
       </c>
       <c t="s" r="J442" s="7">
-        <v>463</v>
+        <v>470</v>
       </c>
       <c r="K442" s="7"/>
       <c r="L442" s="7"/>
@@ -15440,19 +15490,19 @@
       </c>
       <c r="D443" s="7"/>
       <c t="s" r="E443" s="7">
-        <v>461</v>
+        <v>468</v>
       </c>
       <c r="F443" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G443" s="8">
-        <v>462</v>
+        <v>469</v>
       </c>
       <c t="s" r="H443" s="8">
         <v>21</v>
       </c>
       <c t="s" r="I443" s="7">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c t="s" r="J443" s="7">
         <v>37</v>
@@ -15488,13 +15538,13 @@
       </c>
       <c r="D445" s="7"/>
       <c t="s" r="E445" s="7">
-        <v>464</v>
+        <v>471</v>
       </c>
       <c r="F445" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G445" s="8">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c t="s" r="H445" s="8">
         <v>25</v>
@@ -15503,12 +15553,12 @@
         <v>38</v>
       </c>
       <c t="s" r="J445" s="7">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="K445" s="7"/>
       <c r="L445" s="7"/>
       <c t="s" r="M445" s="7">
-        <v>274</v>
+        <v>277</v>
       </c>
     </row>
     <row r="446" ht="14.25" customHeight="1">
@@ -15523,7 +15573,7 @@
       </c>
       <c r="D446" s="7"/>
       <c t="s" r="E446" s="7">
-        <v>464</v>
+        <v>471</v>
       </c>
       <c r="F446" s="7">
         <v>321</v>
@@ -15535,7 +15585,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I446" s="7">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c t="s" r="J446" s="7">
         <v>81</v>
@@ -15556,7 +15606,7 @@
       </c>
       <c r="D447" s="7"/>
       <c t="s" r="E447" s="7">
-        <v>464</v>
+        <v>471</v>
       </c>
       <c r="F447" s="7">
         <v>321</v>
@@ -15571,7 +15621,7 @@
         <v>83</v>
       </c>
       <c t="s" r="J447" s="7">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="K447" s="7"/>
       <c r="L447" s="7"/>
@@ -15589,7 +15639,7 @@
       </c>
       <c r="D448" s="7"/>
       <c t="s" r="E448" s="7">
-        <v>464</v>
+        <v>471</v>
       </c>
       <c r="F448" s="7">
         <v>321</v>
@@ -15601,7 +15651,7 @@
         <v>77</v>
       </c>
       <c t="s" r="I448" s="7">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c t="s" r="J448" s="7">
         <v>94</v>
@@ -15622,7 +15672,7 @@
       </c>
       <c r="D449" s="7"/>
       <c t="s" r="E449" s="7">
-        <v>464</v>
+        <v>471</v>
       </c>
       <c r="F449" s="7">
         <v>321</v>
@@ -15637,7 +15687,7 @@
         <v>62</v>
       </c>
       <c t="s" r="J449" s="7">
-        <v>441</v>
+        <v>448</v>
       </c>
       <c r="K449" s="7"/>
       <c r="L449" s="7"/>
@@ -15670,7 +15720,7 @@
       </c>
       <c r="D451" s="7"/>
       <c t="s" r="E451" s="7">
-        <v>465</v>
+        <v>472</v>
       </c>
       <c r="F451" s="7">
         <v>320</v>
@@ -15682,17 +15732,17 @@
         <v>21</v>
       </c>
       <c t="s" r="I451" s="7">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c t="s" r="J451" s="7">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c t="s" r="K451" s="7">
         <v>88</v>
       </c>
       <c r="L451" s="7"/>
       <c t="s" r="M451" s="7">
-        <v>138</v>
+        <v>141</v>
       </c>
     </row>
     <row r="452" ht="14.25" customHeight="1">
@@ -15707,7 +15757,7 @@
       </c>
       <c r="D452" s="7"/>
       <c t="s" r="E452" s="7">
-        <v>465</v>
+        <v>472</v>
       </c>
       <c r="F452" s="7">
         <v>320</v>
@@ -15719,13 +15769,13 @@
         <v>25</v>
       </c>
       <c t="s" r="I452" s="7">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c t="s" r="J452" s="7">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c t="s" r="K452" s="7">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="L452" s="7"/>
       <c t="s" r="M452" s="7">
@@ -15759,7 +15809,7 @@
       </c>
       <c r="D454" s="7"/>
       <c t="s" r="E454" s="7">
-        <v>466</v>
+        <v>473</v>
       </c>
       <c r="F454" s="7">
         <v>330</v>
@@ -15771,10 +15821,10 @@
         <v>99</v>
       </c>
       <c t="s" r="I454" s="7">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c t="s" r="J454" s="7">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="K454" s="7"/>
       <c r="L454" s="7"/>
@@ -15792,7 +15842,7 @@
       </c>
       <c r="D455" s="7"/>
       <c t="s" r="E455" s="7">
-        <v>466</v>
+        <v>473</v>
       </c>
       <c r="F455" s="7">
         <v>330</v>
@@ -15801,13 +15851,13 @@
         <v>99</v>
       </c>
       <c t="s" r="H455" s="8">
-        <v>467</v>
+        <v>474</v>
       </c>
       <c t="s" r="I455" s="7">
         <v>45</v>
       </c>
       <c t="s" r="J455" s="7">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="K455" s="7"/>
       <c r="L455" s="7"/>
@@ -15825,13 +15875,13 @@
       </c>
       <c r="D456" s="7"/>
       <c t="s" r="E456" s="7">
-        <v>466</v>
+        <v>473</v>
       </c>
       <c r="F456" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G456" s="8">
-        <v>467</v>
+        <v>474</v>
       </c>
       <c t="s" r="H456" s="8">
         <v>99</v>
@@ -15840,7 +15890,7 @@
         <v>84</v>
       </c>
       <c t="s" r="J456" s="7">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="K456" s="7"/>
       <c r="L456" s="7"/>
@@ -15873,19 +15923,19 @@
       </c>
       <c r="D458" s="7"/>
       <c t="s" r="E458" s="7">
-        <v>468</v>
+        <v>475</v>
       </c>
       <c r="F458" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G458" s="8">
-        <v>469</v>
+        <v>476</v>
       </c>
       <c t="s" r="H458" s="8">
         <v>77</v>
       </c>
       <c t="s" r="I458" s="7">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c t="s" r="J458" s="7">
         <v>28</v>
@@ -15893,7 +15943,7 @@
       <c r="K458" s="7"/>
       <c r="L458" s="7"/>
       <c t="s" r="M458" s="7">
-        <v>470</v>
+        <v>435</v>
       </c>
     </row>
     <row r="459" ht="14.25" customHeight="1">
@@ -15908,7 +15958,7 @@
       </c>
       <c r="D459" s="7"/>
       <c t="s" r="E459" s="7">
-        <v>468</v>
+        <v>475</v>
       </c>
       <c r="F459" s="7">
         <v>330</v>
@@ -15920,10 +15970,10 @@
         <v>21</v>
       </c>
       <c t="s" r="I459" s="7">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c t="s" r="J459" s="7">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="K459" s="7"/>
       <c r="L459" s="7"/>
@@ -15941,7 +15991,7 @@
       </c>
       <c r="D460" s="7"/>
       <c t="s" r="E460" s="7">
-        <v>468</v>
+        <v>475</v>
       </c>
       <c r="F460" s="7">
         <v>330</v>
@@ -15950,13 +16000,13 @@
         <v>21</v>
       </c>
       <c t="s" r="H460" s="8">
-        <v>471</v>
+        <v>477</v>
       </c>
       <c t="s" r="I460" s="7">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c t="s" r="J460" s="7">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="K460" s="7"/>
       <c r="L460" s="7"/>
@@ -15989,7 +16039,7 @@
       </c>
       <c r="D462" s="7"/>
       <c t="s" r="E462" s="7">
-        <v>472</v>
+        <v>478</v>
       </c>
       <c r="F462" s="7">
         <v>330</v>
@@ -16001,15 +16051,15 @@
         <v>99</v>
       </c>
       <c t="s" r="I462" s="7">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c t="s" r="J462" s="7">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="K462" s="7"/>
       <c r="L462" s="7"/>
       <c t="s" r="M462" s="7">
-        <v>473</v>
+        <v>479</v>
       </c>
     </row>
     <row r="463" ht="14.25" customHeight="1">
@@ -16024,7 +16074,7 @@
       </c>
       <c r="D463" s="7"/>
       <c t="s" r="E463" s="7">
-        <v>472</v>
+        <v>478</v>
       </c>
       <c r="F463" s="7">
         <v>330</v>
@@ -16033,13 +16083,13 @@
         <v>99</v>
       </c>
       <c t="s" r="H463" s="8">
-        <v>474</v>
+        <v>480</v>
       </c>
       <c t="s" r="I463" s="7">
         <v>92</v>
       </c>
       <c t="s" r="J463" s="7">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="K463" s="7"/>
       <c r="L463" s="7"/>
@@ -16057,13 +16107,13 @@
       </c>
       <c r="D464" s="7"/>
       <c t="s" r="E464" s="7">
-        <v>472</v>
+        <v>478</v>
       </c>
       <c r="F464" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G464" s="8">
-        <v>474</v>
+        <v>480</v>
       </c>
       <c t="s" r="H464" s="8">
         <v>99</v>
@@ -16105,7 +16155,7 @@
       </c>
       <c r="D466" s="7"/>
       <c t="s" r="E466" s="7">
-        <v>475</v>
+        <v>481</v>
       </c>
       <c r="F466" s="7">
         <v>330</v>
@@ -16114,18 +16164,18 @@
         <v>99</v>
       </c>
       <c t="s" r="H466" s="8">
-        <v>476</v>
+        <v>482</v>
       </c>
       <c t="s" r="I466" s="7">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c t="s" r="J466" s="7">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="K466" s="7"/>
       <c r="L466" s="7"/>
       <c t="s" r="M466" s="7">
-        <v>477</v>
+        <v>483</v>
       </c>
     </row>
     <row r="467" ht="14.25" customHeight="1">
@@ -16140,22 +16190,22 @@
       </c>
       <c r="D467" s="7"/>
       <c t="s" r="E467" s="7">
-        <v>475</v>
+        <v>481</v>
       </c>
       <c r="F467" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G467" s="8">
-        <v>476</v>
+        <v>482</v>
       </c>
       <c t="s" r="H467" s="8">
         <v>99</v>
       </c>
       <c t="s" r="I467" s="7">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c t="s" r="J467" s="7">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="K467" s="7"/>
       <c r="L467" s="7"/>
@@ -16188,13 +16238,13 @@
       </c>
       <c r="D469" s="7"/>
       <c t="s" r="E469" s="7">
-        <v>478</v>
+        <v>484</v>
       </c>
       <c r="F469" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G469" s="8">
-        <v>471</v>
+        <v>477</v>
       </c>
       <c t="s" r="H469" s="8">
         <v>21</v>
@@ -16203,12 +16253,12 @@
         <v>41</v>
       </c>
       <c t="s" r="J469" s="7">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="K469" s="7"/>
       <c r="L469" s="7"/>
       <c t="s" r="M469" s="7">
-        <v>220</v>
+        <v>224</v>
       </c>
     </row>
     <row r="470" ht="15" customHeight="1">
@@ -16223,7 +16273,7 @@
       </c>
       <c r="D470" s="7"/>
       <c t="s" r="E470" s="7">
-        <v>478</v>
+        <v>484</v>
       </c>
       <c r="F470" s="7">
         <v>330</v>
@@ -16235,17 +16285,17 @@
         <v>77</v>
       </c>
       <c t="s" r="I470" s="7">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c t="s" r="J470" s="7">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c t="s" r="K470" s="7">
         <v>71</v>
       </c>
       <c r="L470" s="7"/>
       <c t="s" r="M470" s="7">
-        <v>355</v>
+        <v>359</v>
       </c>
     </row>
     <row r="471" ht="14.25" customHeight="1">
@@ -16275,7 +16325,7 @@
       </c>
       <c r="D472" s="7"/>
       <c t="s" r="E472" s="7">
-        <v>479</v>
+        <v>485</v>
       </c>
       <c r="F472" s="7">
         <v>330</v>
@@ -16284,18 +16334,18 @@
         <v>21</v>
       </c>
       <c t="s" r="H472" s="8">
-        <v>480</v>
+        <v>486</v>
       </c>
       <c t="s" r="I472" s="7">
         <v>41</v>
       </c>
       <c t="s" r="J472" s="7">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="K472" s="7"/>
       <c r="L472" s="7"/>
       <c t="s" r="M472" s="7">
-        <v>481</v>
+        <v>487</v>
       </c>
     </row>
     <row r="473" ht="14.25" customHeight="1">
@@ -16310,22 +16360,22 @@
       </c>
       <c r="D473" s="7"/>
       <c t="s" r="E473" s="7">
-        <v>479</v>
+        <v>485</v>
       </c>
       <c r="F473" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G473" s="8">
-        <v>480</v>
+        <v>486</v>
       </c>
       <c t="s" r="H473" s="8">
         <v>21</v>
       </c>
       <c t="s" r="I473" s="7">
-        <v>482</v>
+        <v>488</v>
       </c>
       <c t="s" r="J473" s="7">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="K473" s="7"/>
       <c r="L473" s="7"/>
@@ -16333,7 +16383,7 @@
     </row>
     <row r="474" ht="15.75" customHeight="1">
       <c t="s" r="A474" s="9">
-        <v>483</v>
+        <v>489</v>
       </c>
       <c r="B474" s="9"/>
       <c r="C474" s="9"/>
@@ -16353,7 +16403,7 @@
     <row r="475" ht="66" customHeight="1"/>
     <row r="476" ht="16.5" customHeight="1">
       <c t="s" r="A476" s="10">
-        <v>484</v>
+        <v>490</v>
       </c>
       <c r="B476" s="10"/>
       <c r="C476" s="10"/>
@@ -16366,7 +16416,7 @@
       <c r="J476" s="10"/>
       <c r="K476" s="10"/>
       <c t="s" r="L476" s="11">
-        <v>485</v>
+        <v>491</v>
       </c>
       <c r="M476" s="11"/>
       <c r="N476" s="11"/>
